--- a/kronshtatsky/пол/пол таблицы.xlsx
+++ b/kronshtatsky/пол/пол таблицы.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8520" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8520" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="7.6Плнтс" sheetId="61" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2593" uniqueCount="759">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2597" uniqueCount="762">
   <si>
     <t>№ пом.</t>
   </si>
@@ -2365,6 +2365,15 @@
   </si>
   <si>
     <t>пог.м.</t>
+  </si>
+  <si>
+    <t>Пог.м.</t>
+  </si>
+  <si>
+    <t>Устройство покрытия пола СКБ из керамогранитной плитки / Керамогранит Грани Таганая моноколор, арт. GT100, цвет бежевый, толщина 10мм, матовый</t>
+  </si>
+  <si>
+    <t>Устройство плинтуса из керамогранитной плитки СКБ / Керамогранит Грани Таганая моноколор, арт. GT100, цвет бежевый, толщина 10мм, матовый</t>
   </si>
 </sst>
 </file>
@@ -2820,7 +2829,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="280">
+  <cellXfs count="283">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3332,6 +3341,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3425,11 +3443,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3441,18 +3459,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3484,6 +3490,18 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3536,9 +3554,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3548,6 +3563,9 @@
     <xf numFmtId="2" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3556,6 +3574,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3581,12 +3605,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3605,9 +3623,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3616,6 +3631,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4091,24 +4109,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="188" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="186"/>
-      <c r="D2" s="187"/>
+      <c r="C2" s="189"/>
+      <c r="D2" s="190"/>
       <c r="E2" s="179" t="s">
         <v>392</v>
       </c>
@@ -4120,11 +4138,11 @@
       <c r="A3" s="177">
         <v>1</v>
       </c>
-      <c r="B3" s="188" t="s">
+      <c r="B3" s="191" t="s">
         <v>757</v>
       </c>
-      <c r="C3" s="189"/>
-      <c r="D3" s="190"/>
+      <c r="C3" s="192"/>
+      <c r="D3" s="193"/>
       <c r="E3" s="177" t="s">
         <v>754</v>
       </c>
@@ -4134,10 +4152,10 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C4" s="191"/>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
+      <c r="C4" s="194"/>
+      <c r="D4" s="195"/>
+      <c r="E4" s="195"/>
+      <c r="F4" s="195"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="183" t="s">
@@ -4146,10 +4164,10 @@
       <c r="B5" s="169" t="s">
         <v>393</v>
       </c>
-      <c r="C5" s="193"/>
-      <c r="D5" s="194"/>
-      <c r="E5" s="194"/>
-      <c r="F5" s="194"/>
+      <c r="C5" s="196"/>
+      <c r="D5" s="197"/>
+      <c r="E5" s="197"/>
+      <c r="F5" s="197"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="170" t="s">
@@ -4158,10 +4176,10 @@
       <c r="B6" s="171">
         <v>74.959999999999994</v>
       </c>
-      <c r="C6" s="193"/>
-      <c r="D6" s="194"/>
-      <c r="E6" s="194"/>
-      <c r="F6" s="194"/>
+      <c r="C6" s="196"/>
+      <c r="D6" s="197"/>
+      <c r="E6" s="197"/>
+      <c r="F6" s="197"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="170" t="s">
@@ -4170,10 +4188,10 @@
       <c r="B7" s="171">
         <v>124.78</v>
       </c>
-      <c r="C7" s="193"/>
-      <c r="D7" s="194"/>
-      <c r="E7" s="194"/>
-      <c r="F7" s="194"/>
+      <c r="C7" s="196"/>
+      <c r="D7" s="197"/>
+      <c r="E7" s="197"/>
+      <c r="F7" s="197"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="170" t="s">
@@ -4182,10 +4200,10 @@
       <c r="B8" s="171">
         <v>147.96</v>
       </c>
-      <c r="C8" s="193"/>
-      <c r="D8" s="194"/>
-      <c r="E8" s="194"/>
-      <c r="F8" s="194"/>
+      <c r="C8" s="196"/>
+      <c r="D8" s="197"/>
+      <c r="E8" s="197"/>
+      <c r="F8" s="197"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="172" t="s">
@@ -4195,10 +4213,10 @@
         <f>SUM(B6:B8)</f>
         <v>347.70000000000005</v>
       </c>
-      <c r="C9" s="193"/>
-      <c r="D9" s="194"/>
-      <c r="E9" s="194"/>
-      <c r="F9" s="194"/>
+      <c r="C9" s="196"/>
+      <c r="D9" s="197"/>
+      <c r="E9" s="197"/>
+      <c r="F9" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -6940,13 +6958,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -7026,13 +7044,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -7095,13 +7113,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -7164,13 +7182,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -7233,13 +7251,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -7302,13 +7320,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -7371,13 +7389,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -7457,13 +7475,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -7581,36 +7599,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
+      <c r="J1" s="187"/>
+      <c r="K1" s="187"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="214" t="s">
+      <c r="B2" s="217" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="214"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="215" t="s">
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="218" t="s">
         <v>391</v>
       </c>
-      <c r="G2" s="215"/>
-      <c r="H2" s="215"/>
-      <c r="I2" s="215"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="218"/>
+      <c r="I2" s="218"/>
       <c r="J2" s="16" t="s">
         <v>392</v>
       </c>
@@ -7622,18 +7640,18 @@
       <c r="A3" s="129">
         <v>1</v>
       </c>
-      <c r="B3" s="212" t="s">
+      <c r="B3" s="215" t="s">
         <v>707</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="213" t="s">
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="216" t="s">
         <v>710</v>
       </c>
-      <c r="G3" s="213"/>
-      <c r="H3" s="213"/>
-      <c r="I3" s="213"/>
+      <c r="G3" s="216"/>
+      <c r="H3" s="216"/>
+      <c r="I3" s="216"/>
       <c r="J3" s="129" t="s">
         <v>394</v>
       </c>
@@ -7645,18 +7663,18 @@
       <c r="A4" s="129">
         <v>2</v>
       </c>
-      <c r="B4" s="212" t="s">
+      <c r="B4" s="215" t="s">
         <v>707</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="213" t="s">
+      <c r="C4" s="215"/>
+      <c r="D4" s="215"/>
+      <c r="E4" s="215"/>
+      <c r="F4" s="216" t="s">
         <v>711</v>
       </c>
-      <c r="G4" s="213"/>
-      <c r="H4" s="213"/>
-      <c r="I4" s="213"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
       <c r="J4" s="129" t="s">
         <v>394</v>
       </c>
@@ -7698,25 +7716,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="188" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="186"/>
-      <c r="D2" s="187"/>
+      <c r="C2" s="189"/>
+      <c r="D2" s="190"/>
       <c r="E2" s="179" t="s">
         <v>391</v>
       </c>
@@ -7731,11 +7749,11 @@
       <c r="A3" s="177">
         <v>1</v>
       </c>
-      <c r="B3" s="188" t="s">
+      <c r="B3" s="191" t="s">
         <v>679</v>
       </c>
-      <c r="C3" s="189"/>
-      <c r="D3" s="190"/>
+      <c r="C3" s="192"/>
+      <c r="D3" s="193"/>
       <c r="E3" s="181" t="s">
         <v>753</v>
       </c>
@@ -7751,11 +7769,11 @@
       <c r="A4" s="177">
         <v>2</v>
       </c>
-      <c r="B4" s="188" t="s">
+      <c r="B4" s="191" t="s">
         <v>679</v>
       </c>
-      <c r="C4" s="189"/>
-      <c r="D4" s="190"/>
+      <c r="C4" s="192"/>
+      <c r="D4" s="193"/>
       <c r="E4" s="181" t="s">
         <v>755</v>
       </c>
@@ -7768,13 +7786,13 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="191"/>
-      <c r="B5" s="192"/>
-      <c r="C5" s="192"/>
-      <c r="D5" s="192"/>
-      <c r="E5" s="192"/>
-      <c r="F5" s="192"/>
-      <c r="G5" s="192"/>
+      <c r="A5" s="194"/>
+      <c r="B5" s="195"/>
+      <c r="C5" s="195"/>
+      <c r="D5" s="195"/>
+      <c r="E5" s="195"/>
+      <c r="F5" s="195"/>
+      <c r="G5" s="195"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="168" t="s">
@@ -7783,9 +7801,9 @@
       <c r="B6" s="169" t="s">
         <v>393</v>
       </c>
-      <c r="C6" s="193"/>
-      <c r="D6" s="194"/>
-      <c r="E6" s="194"/>
+      <c r="C6" s="196"/>
+      <c r="D6" s="197"/>
+      <c r="E6" s="197"/>
       <c r="F6" s="168" t="s">
         <v>593</v>
       </c>
@@ -7800,9 +7818,9 @@
       <c r="B7" s="171">
         <v>20.5</v>
       </c>
-      <c r="C7" s="193"/>
-      <c r="D7" s="194"/>
-      <c r="E7" s="194"/>
+      <c r="C7" s="196"/>
+      <c r="D7" s="197"/>
+      <c r="E7" s="197"/>
       <c r="F7" s="170" t="s">
         <v>485</v>
       </c>
@@ -7817,9 +7835,9 @@
       <c r="B8" s="171">
         <v>15.1</v>
       </c>
-      <c r="C8" s="193"/>
-      <c r="D8" s="194"/>
-      <c r="E8" s="194"/>
+      <c r="C8" s="196"/>
+      <c r="D8" s="197"/>
+      <c r="E8" s="197"/>
       <c r="F8" s="170" t="s">
         <v>457</v>
       </c>
@@ -7834,9 +7852,9 @@
       <c r="B9" s="171">
         <v>74.900000000000006</v>
       </c>
-      <c r="C9" s="193"/>
-      <c r="D9" s="194"/>
-      <c r="E9" s="194"/>
+      <c r="C9" s="196"/>
+      <c r="D9" s="197"/>
+      <c r="E9" s="197"/>
       <c r="F9" s="172" t="s">
         <v>474</v>
       </c>
@@ -7852,11 +7870,11 @@
       <c r="B10" s="171">
         <v>18.600000000000001</v>
       </c>
-      <c r="C10" s="193"/>
-      <c r="D10" s="194"/>
-      <c r="E10" s="194"/>
-      <c r="F10" s="195"/>
-      <c r="G10" s="195"/>
+      <c r="C10" s="196"/>
+      <c r="D10" s="197"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="198"/>
+      <c r="G10" s="198"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="170" t="s">
@@ -7865,11 +7883,11 @@
       <c r="B11" s="171">
         <v>186.6</v>
       </c>
-      <c r="C11" s="193"/>
-      <c r="D11" s="194"/>
-      <c r="E11" s="194"/>
-      <c r="F11" s="196"/>
-      <c r="G11" s="196"/>
+      <c r="C11" s="196"/>
+      <c r="D11" s="197"/>
+      <c r="E11" s="197"/>
+      <c r="F11" s="199"/>
+      <c r="G11" s="199"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="170" t="s">
@@ -7878,11 +7896,11 @@
       <c r="B12" s="171">
         <v>105.8</v>
       </c>
-      <c r="C12" s="193"/>
-      <c r="D12" s="194"/>
-      <c r="E12" s="194"/>
-      <c r="F12" s="196"/>
-      <c r="G12" s="196"/>
+      <c r="C12" s="196"/>
+      <c r="D12" s="197"/>
+      <c r="E12" s="197"/>
+      <c r="F12" s="199"/>
+      <c r="G12" s="199"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="170" t="s">
@@ -7891,11 +7909,11 @@
       <c r="B13" s="171">
         <v>78.900000000000006</v>
       </c>
-      <c r="C13" s="193"/>
-      <c r="D13" s="194"/>
-      <c r="E13" s="194"/>
-      <c r="F13" s="196"/>
-      <c r="G13" s="196"/>
+      <c r="C13" s="196"/>
+      <c r="D13" s="197"/>
+      <c r="E13" s="197"/>
+      <c r="F13" s="199"/>
+      <c r="G13" s="199"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="170" t="s">
@@ -7904,11 +7922,11 @@
       <c r="B14" s="171">
         <v>37.5</v>
       </c>
-      <c r="C14" s="193"/>
-      <c r="D14" s="194"/>
-      <c r="E14" s="194"/>
-      <c r="F14" s="196"/>
-      <c r="G14" s="196"/>
+      <c r="C14" s="196"/>
+      <c r="D14" s="197"/>
+      <c r="E14" s="197"/>
+      <c r="F14" s="199"/>
+      <c r="G14" s="199"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="170" t="s">
@@ -7917,11 +7935,11 @@
       <c r="B15" s="171">
         <v>60.1</v>
       </c>
-      <c r="C15" s="193"/>
-      <c r="D15" s="194"/>
-      <c r="E15" s="194"/>
-      <c r="F15" s="196"/>
-      <c r="G15" s="196"/>
+      <c r="C15" s="196"/>
+      <c r="D15" s="197"/>
+      <c r="E15" s="197"/>
+      <c r="F15" s="199"/>
+      <c r="G15" s="199"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="170" t="s">
@@ -7930,11 +7948,11 @@
       <c r="B16" s="171">
         <v>86.2</v>
       </c>
-      <c r="C16" s="193"/>
-      <c r="D16" s="194"/>
-      <c r="E16" s="194"/>
-      <c r="F16" s="196"/>
-      <c r="G16" s="196"/>
+      <c r="C16" s="196"/>
+      <c r="D16" s="197"/>
+      <c r="E16" s="197"/>
+      <c r="F16" s="199"/>
+      <c r="G16" s="199"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="170" t="s">
@@ -7943,11 +7961,11 @@
       <c r="B17" s="171">
         <v>21.4</v>
       </c>
-      <c r="C17" s="193"/>
-      <c r="D17" s="194"/>
-      <c r="E17" s="194"/>
-      <c r="F17" s="196"/>
-      <c r="G17" s="196"/>
+      <c r="C17" s="196"/>
+      <c r="D17" s="197"/>
+      <c r="E17" s="197"/>
+      <c r="F17" s="199"/>
+      <c r="G17" s="199"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="170" t="s">
@@ -7956,11 +7974,11 @@
       <c r="B18" s="171">
         <v>106.1</v>
       </c>
-      <c r="C18" s="193"/>
-      <c r="D18" s="194"/>
-      <c r="E18" s="194"/>
-      <c r="F18" s="196"/>
-      <c r="G18" s="196"/>
+      <c r="C18" s="196"/>
+      <c r="D18" s="197"/>
+      <c r="E18" s="197"/>
+      <c r="F18" s="199"/>
+      <c r="G18" s="199"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="170" t="s">
@@ -7969,11 +7987,11 @@
       <c r="B19" s="171">
         <v>106.8</v>
       </c>
-      <c r="C19" s="193"/>
-      <c r="D19" s="194"/>
-      <c r="E19" s="194"/>
-      <c r="F19" s="196"/>
-      <c r="G19" s="196"/>
+      <c r="C19" s="196"/>
+      <c r="D19" s="197"/>
+      <c r="E19" s="197"/>
+      <c r="F19" s="199"/>
+      <c r="G19" s="199"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="170" t="s">
@@ -7982,11 +8000,11 @@
       <c r="B20" s="171">
         <v>36.4</v>
       </c>
-      <c r="C20" s="193"/>
-      <c r="D20" s="194"/>
-      <c r="E20" s="194"/>
-      <c r="F20" s="196"/>
-      <c r="G20" s="196"/>
+      <c r="C20" s="196"/>
+      <c r="D20" s="197"/>
+      <c r="E20" s="197"/>
+      <c r="F20" s="199"/>
+      <c r="G20" s="199"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="170" t="s">
@@ -7995,11 +8013,11 @@
       <c r="B21" s="171">
         <v>59.6</v>
       </c>
-      <c r="C21" s="193"/>
-      <c r="D21" s="194"/>
-      <c r="E21" s="194"/>
-      <c r="F21" s="196"/>
-      <c r="G21" s="196"/>
+      <c r="C21" s="196"/>
+      <c r="D21" s="197"/>
+      <c r="E21" s="197"/>
+      <c r="F21" s="199"/>
+      <c r="G21" s="199"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="172" t="s">
@@ -8009,11 +8027,11 @@
         <f>SUM(B7:B21)</f>
         <v>1014.5</v>
       </c>
-      <c r="C22" s="193"/>
-      <c r="D22" s="194"/>
-      <c r="E22" s="194"/>
-      <c r="F22" s="196"/>
-      <c r="G22" s="196"/>
+      <c r="C22" s="196"/>
+      <c r="D22" s="197"/>
+      <c r="E22" s="197"/>
+      <c r="F22" s="199"/>
+      <c r="G22" s="199"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -8055,36 +8073,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
+      <c r="J1" s="187"/>
+      <c r="K1" s="187"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="214" t="s">
+      <c r="B2" s="217" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="214"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="215" t="s">
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="218" t="s">
         <v>391</v>
       </c>
-      <c r="G2" s="215"/>
-      <c r="H2" s="215"/>
-      <c r="I2" s="215"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="218"/>
+      <c r="I2" s="218"/>
       <c r="J2" s="16" t="s">
         <v>392</v>
       </c>
@@ -8096,18 +8114,18 @@
       <c r="A3" s="129">
         <v>1</v>
       </c>
-      <c r="B3" s="212" t="s">
+      <c r="B3" s="215" t="s">
         <v>707</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="213" t="s">
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="216" t="s">
         <v>708</v>
       </c>
-      <c r="G3" s="213"/>
-      <c r="H3" s="213"/>
-      <c r="I3" s="213"/>
+      <c r="G3" s="216"/>
+      <c r="H3" s="216"/>
+      <c r="I3" s="216"/>
       <c r="J3" s="129" t="s">
         <v>394</v>
       </c>
@@ -8119,18 +8137,18 @@
       <c r="A4" s="129">
         <v>2</v>
       </c>
-      <c r="B4" s="212" t="s">
+      <c r="B4" s="215" t="s">
         <v>707</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="213" t="s">
+      <c r="C4" s="215"/>
+      <c r="D4" s="215"/>
+      <c r="E4" s="215"/>
+      <c r="F4" s="216" t="s">
         <v>709</v>
       </c>
-      <c r="G4" s="213"/>
-      <c r="H4" s="213"/>
-      <c r="I4" s="213"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
       <c r="J4" s="129" t="s">
         <v>394</v>
       </c>
@@ -8175,36 +8193,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
+      <c r="J1" s="187"/>
+      <c r="K1" s="187"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="214" t="s">
+      <c r="B2" s="217" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="214"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="215" t="s">
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="218" t="s">
         <v>391</v>
       </c>
-      <c r="G2" s="215"/>
-      <c r="H2" s="215"/>
-      <c r="I2" s="215"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="218"/>
+      <c r="I2" s="218"/>
       <c r="J2" s="16" t="s">
         <v>392</v>
       </c>
@@ -8216,18 +8234,18 @@
       <c r="A3" s="129">
         <v>1</v>
       </c>
-      <c r="B3" s="212" t="s">
+      <c r="B3" s="215" t="s">
         <v>704</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="213" t="s">
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="216" t="s">
         <v>705</v>
       </c>
-      <c r="G3" s="213"/>
-      <c r="H3" s="213"/>
-      <c r="I3" s="213"/>
+      <c r="G3" s="216"/>
+      <c r="H3" s="216"/>
+      <c r="I3" s="216"/>
       <c r="J3" s="129" t="s">
         <v>706</v>
       </c>
@@ -8270,36 +8288,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
+      <c r="J1" s="187"/>
+      <c r="K1" s="187"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="214" t="s">
+      <c r="B2" s="217" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="214"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="215" t="s">
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="218" t="s">
         <v>391</v>
       </c>
-      <c r="G2" s="215"/>
-      <c r="H2" s="215"/>
-      <c r="I2" s="215"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="218"/>
+      <c r="I2" s="218"/>
       <c r="J2" s="16" t="s">
         <v>392</v>
       </c>
@@ -8311,18 +8329,18 @@
       <c r="A3" s="129">
         <v>1</v>
       </c>
-      <c r="B3" s="212" t="s">
+      <c r="B3" s="215" t="s">
         <v>701</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="213" t="s">
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="216" t="s">
         <v>702</v>
       </c>
-      <c r="G3" s="213"/>
-      <c r="H3" s="213"/>
-      <c r="I3" s="213"/>
+      <c r="G3" s="216"/>
+      <c r="H3" s="216"/>
+      <c r="I3" s="216"/>
       <c r="J3" s="129" t="s">
         <v>703</v>
       </c>
@@ -8365,36 +8383,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
+      <c r="J1" s="187"/>
+      <c r="K1" s="187"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="214" t="s">
+      <c r="B2" s="217" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="214"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="215" t="s">
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="218" t="s">
         <v>391</v>
       </c>
-      <c r="G2" s="215"/>
-      <c r="H2" s="215"/>
-      <c r="I2" s="215"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="218"/>
+      <c r="I2" s="218"/>
       <c r="J2" s="16" t="s">
         <v>392</v>
       </c>
@@ -8406,18 +8424,18 @@
       <c r="A3" s="129">
         <v>1</v>
       </c>
-      <c r="B3" s="212" t="s">
+      <c r="B3" s="215" t="s">
         <v>701</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="213" t="s">
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="216" t="s">
         <v>702</v>
       </c>
-      <c r="G3" s="213"/>
-      <c r="H3" s="213"/>
-      <c r="I3" s="213"/>
+      <c r="G3" s="216"/>
+      <c r="H3" s="216"/>
+      <c r="I3" s="216"/>
       <c r="J3" s="129" t="s">
         <v>703</v>
       </c>
@@ -8460,36 +8478,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
+      <c r="J1" s="187"/>
+      <c r="K1" s="187"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="214" t="s">
+      <c r="B2" s="217" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="214"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="215" t="s">
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="218" t="s">
         <v>391</v>
       </c>
-      <c r="G2" s="215"/>
-      <c r="H2" s="215"/>
-      <c r="I2" s="215"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="218"/>
+      <c r="I2" s="218"/>
       <c r="J2" s="16" t="s">
         <v>392</v>
       </c>
@@ -8501,18 +8519,18 @@
       <c r="A3" s="129">
         <v>1</v>
       </c>
-      <c r="B3" s="212" t="s">
+      <c r="B3" s="215" t="s">
         <v>699</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="213" t="s">
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="216" t="s">
         <v>700</v>
       </c>
-      <c r="G3" s="213"/>
-      <c r="H3" s="213"/>
-      <c r="I3" s="213"/>
+      <c r="G3" s="216"/>
+      <c r="H3" s="216"/>
+      <c r="I3" s="216"/>
       <c r="J3" s="129" t="s">
         <v>394</v>
       </c>
@@ -8555,36 +8573,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
+      <c r="J1" s="187"/>
+      <c r="K1" s="187"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="214" t="s">
+      <c r="B2" s="217" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="214"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="215" t="s">
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="218" t="s">
         <v>391</v>
       </c>
-      <c r="G2" s="215"/>
-      <c r="H2" s="215"/>
-      <c r="I2" s="215"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="218"/>
+      <c r="I2" s="218"/>
       <c r="J2" s="149" t="s">
         <v>392</v>
       </c>
@@ -8596,18 +8614,18 @@
       <c r="A3" s="148">
         <v>1</v>
       </c>
-      <c r="B3" s="212" t="s">
+      <c r="B3" s="215" t="s">
         <v>690</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="216" t="s">
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="220" t="s">
         <v>694</v>
       </c>
-      <c r="G3" s="216"/>
-      <c r="H3" s="216"/>
-      <c r="I3" s="216"/>
+      <c r="G3" s="220"/>
+      <c r="H3" s="220"/>
+      <c r="I3" s="220"/>
       <c r="J3" s="148" t="s">
         <v>394</v>
       </c>
@@ -8619,18 +8637,18 @@
       <c r="A4" s="148">
         <v>2</v>
       </c>
-      <c r="B4" s="212" t="s">
+      <c r="B4" s="215" t="s">
         <v>690</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="213" t="s">
+      <c r="C4" s="215"/>
+      <c r="D4" s="215"/>
+      <c r="E4" s="215"/>
+      <c r="F4" s="216" t="s">
         <v>698</v>
       </c>
-      <c r="G4" s="213"/>
-      <c r="H4" s="213"/>
-      <c r="I4" s="213"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
       <c r="J4" s="148" t="s">
         <v>394</v>
       </c>
@@ -8648,7 +8666,7 @@
       <c r="C5" s="141" t="s">
         <v>673</v>
       </c>
-      <c r="D5" s="195"/>
+      <c r="D5" s="198"/>
       <c r="E5" s="140" t="s">
         <v>593</v>
       </c>
@@ -8658,7 +8676,7 @@
       <c r="G5" s="141" t="s">
         <v>673</v>
       </c>
-      <c r="H5" s="195"/>
+      <c r="H5" s="198"/>
       <c r="I5" s="140" t="s">
         <v>593</v>
       </c>
@@ -8679,7 +8697,7 @@
       <c r="C6" s="118">
         <v>1.0711073292923112</v>
       </c>
-      <c r="D6" s="196"/>
+      <c r="D6" s="199"/>
       <c r="E6" s="104" t="s">
         <v>498</v>
       </c>
@@ -8689,7 +8707,7 @@
       <c r="G6" s="117">
         <v>1.0913169015431097</v>
       </c>
-      <c r="H6" s="196"/>
+      <c r="H6" s="199"/>
       <c r="I6" s="104" t="s">
         <v>510</v>
       </c>
@@ -8710,7 +8728,7 @@
       <c r="C7" s="117">
         <v>1.2327839072986979</v>
       </c>
-      <c r="D7" s="196"/>
+      <c r="D7" s="199"/>
       <c r="E7" s="106" t="s">
         <v>499</v>
       </c>
@@ -8720,7 +8738,7 @@
       <c r="G7" s="118">
         <v>2.3241008088418078</v>
       </c>
-      <c r="H7" s="196"/>
+      <c r="H7" s="199"/>
       <c r="I7" s="106" t="s">
         <v>511</v>
       </c>
@@ -8741,7 +8759,7 @@
       <c r="C8" s="118">
         <v>3.152693271124539</v>
       </c>
-      <c r="D8" s="196"/>
+      <c r="D8" s="199"/>
       <c r="E8" s="104" t="s">
         <v>500</v>
       </c>
@@ -8751,7 +8769,7 @@
       <c r="G8" s="117">
         <v>2.344310381092606</v>
       </c>
-      <c r="H8" s="196"/>
+      <c r="H8" s="199"/>
       <c r="I8" s="104" t="s">
         <v>512</v>
       </c>
@@ -8772,7 +8790,7 @@
       <c r="C9" s="117">
         <v>1.0913169015431097</v>
       </c>
-      <c r="D9" s="196"/>
+      <c r="D9" s="199"/>
       <c r="E9" s="106" t="s">
         <v>501</v>
       </c>
@@ -8782,7 +8800,7 @@
       <c r="G9" s="118">
         <v>2.7485018261085723</v>
       </c>
-      <c r="H9" s="196"/>
+      <c r="H9" s="199"/>
       <c r="I9" s="106" t="s">
         <v>506</v>
       </c>
@@ -8803,7 +8821,7 @@
       <c r="C10" s="118">
         <v>3.1324836988737408</v>
       </c>
-      <c r="D10" s="196"/>
+      <c r="D10" s="199"/>
       <c r="E10" s="104" t="s">
         <v>502</v>
       </c>
@@ -8813,7 +8831,7 @@
       <c r="G10" s="117">
         <v>1.7178136413178577</v>
       </c>
-      <c r="H10" s="196"/>
+      <c r="H10" s="199"/>
       <c r="I10" s="104" t="s">
         <v>507</v>
       </c>
@@ -8834,7 +8852,7 @@
       <c r="C11" s="117">
         <v>0.48502973401915983</v>
       </c>
-      <c r="D11" s="196"/>
+      <c r="D11" s="199"/>
       <c r="E11" s="106" t="s">
         <v>503</v>
       </c>
@@ -8844,7 +8862,7 @@
       <c r="G11" s="118">
         <v>2.1624242308354207</v>
       </c>
-      <c r="H11" s="196"/>
+      <c r="H11" s="199"/>
       <c r="I11" s="106" t="s">
         <v>659</v>
       </c>
@@ -8865,7 +8883,7 @@
       <c r="C12" s="118">
         <v>1.2125743350478997</v>
       </c>
-      <c r="D12" s="196"/>
+      <c r="D12" s="199"/>
       <c r="E12" s="104" t="s">
         <v>504</v>
       </c>
@@ -8875,7 +8893,7 @@
       <c r="G12" s="117">
         <v>2.4655678145973958</v>
       </c>
-      <c r="H12" s="196"/>
+      <c r="H12" s="199"/>
       <c r="I12" s="104" t="s">
         <v>508</v>
       </c>
@@ -8896,7 +8914,7 @@
       <c r="C13" s="117">
         <v>0.80838289003193309</v>
       </c>
-      <c r="D13" s="196"/>
+      <c r="D13" s="199"/>
       <c r="E13" s="106" t="s">
         <v>639</v>
       </c>
@@ -8906,7 +8924,7 @@
       <c r="G13" s="118">
         <v>4.7290399066868085</v>
       </c>
-      <c r="H13" s="196"/>
+      <c r="H13" s="199"/>
       <c r="I13" s="106" t="s">
         <v>660</v>
       </c>
@@ -8927,7 +8945,7 @@
       <c r="C14" s="118">
         <v>1.0104786125399163</v>
       </c>
-      <c r="D14" s="196"/>
+      <c r="D14" s="199"/>
       <c r="E14" s="104" t="s">
         <v>640</v>
       </c>
@@ -8937,7 +8955,7 @@
       <c r="G14" s="117">
         <v>1.0913169015431097</v>
       </c>
-      <c r="H14" s="196"/>
+      <c r="H14" s="199"/>
       <c r="I14" s="104" t="s">
         <v>661</v>
       </c>
@@ -8958,7 +8976,7 @@
       <c r="C15" s="117">
         <v>2.2230529475878158</v>
       </c>
-      <c r="D15" s="196"/>
+      <c r="D15" s="199"/>
       <c r="E15" s="106" t="s">
         <v>641</v>
       </c>
@@ -8968,7 +8986,7 @@
       <c r="G15" s="118">
         <v>1.9805380805782362</v>
       </c>
-      <c r="H15" s="196"/>
+      <c r="H15" s="199"/>
       <c r="I15" s="108" t="s">
         <v>666</v>
       </c>
@@ -8989,7 +9007,7 @@
       <c r="C16" s="118">
         <v>1.3540413408034879</v>
       </c>
-      <c r="D16" s="196"/>
+      <c r="D16" s="199"/>
       <c r="E16" s="104" t="s">
         <v>497</v>
       </c>
@@ -8999,11 +9017,11 @@
       <c r="G16" s="117">
         <v>3.152693271124539</v>
       </c>
-      <c r="H16" s="196"/>
-      <c r="I16" s="217" t="s">
+      <c r="H16" s="199"/>
+      <c r="I16" s="219" t="s">
         <v>696</v>
       </c>
-      <c r="J16" s="217"/>
+      <c r="J16" s="219"/>
       <c r="K16" s="145">
         <f>SUM(K6:K15)</f>
         <v>26.858521521310973</v>
@@ -9019,7 +9037,7 @@
       <c r="C17" s="117">
         <v>4.2985760177448045</v>
       </c>
-      <c r="D17" s="196"/>
+      <c r="D17" s="199"/>
       <c r="E17" s="106" t="s">
         <v>495</v>
       </c>
@@ -9029,10 +9047,10 @@
       <c r="G17" s="118">
         <v>3.1324836988737408</v>
       </c>
-      <c r="H17" s="196"/>
-      <c r="I17" s="196"/>
-      <c r="J17" s="196"/>
-      <c r="K17" s="196"/>
+      <c r="H17" s="199"/>
+      <c r="I17" s="199"/>
+      <c r="J17" s="199"/>
+      <c r="K17" s="199"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="106" t="s">
@@ -9044,7 +9062,7 @@
       <c r="C18" s="118">
         <v>0.97005946803831966</v>
       </c>
-      <c r="D18" s="196"/>
+      <c r="D18" s="199"/>
       <c r="E18" s="104" t="s">
         <v>496</v>
       </c>
@@ -9054,10 +9072,10 @@
       <c r="G18" s="117">
         <v>1.0913169015431097</v>
       </c>
-      <c r="H18" s="196"/>
-      <c r="I18" s="196"/>
-      <c r="J18" s="196"/>
-      <c r="K18" s="196"/>
+      <c r="H18" s="199"/>
+      <c r="I18" s="199"/>
+      <c r="J18" s="199"/>
+      <c r="K18" s="199"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="104" t="s">
@@ -9069,7 +9087,7 @@
       <c r="C19" s="117">
         <v>1.3540413408034879</v>
       </c>
-      <c r="D19" s="196"/>
+      <c r="D19" s="199"/>
       <c r="E19" s="106" t="s">
         <v>647</v>
       </c>
@@ -9079,10 +9097,10 @@
       <c r="G19" s="118">
         <v>1.3540413408034879</v>
       </c>
-      <c r="H19" s="196"/>
-      <c r="I19" s="196"/>
-      <c r="J19" s="196"/>
-      <c r="K19" s="196"/>
+      <c r="H19" s="199"/>
+      <c r="I19" s="199"/>
+      <c r="J19" s="199"/>
+      <c r="K19" s="199"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="106" t="s">
@@ -9094,7 +9112,7 @@
       <c r="C20" s="118">
         <v>6.0628716752394984</v>
       </c>
-      <c r="D20" s="196"/>
+      <c r="D20" s="199"/>
       <c r="E20" s="104" t="s">
         <v>648</v>
       </c>
@@ -9104,10 +9122,10 @@
       <c r="G20" s="117">
         <v>6.0022429584871029</v>
       </c>
-      <c r="H20" s="196"/>
-      <c r="I20" s="196"/>
-      <c r="J20" s="196"/>
-      <c r="K20" s="196"/>
+      <c r="H20" s="199"/>
+      <c r="I20" s="199"/>
+      <c r="J20" s="199"/>
+      <c r="K20" s="199"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="104" t="s">
@@ -9119,7 +9137,7 @@
       <c r="C21" s="117">
         <v>1.293412624051093</v>
       </c>
-      <c r="D21" s="196"/>
+      <c r="D21" s="199"/>
       <c r="E21" s="106" t="s">
         <v>649</v>
       </c>
@@ -9129,10 +9147,10 @@
       <c r="G21" s="118">
         <v>1.3540413408034879</v>
       </c>
-      <c r="H21" s="196"/>
-      <c r="I21" s="196"/>
-      <c r="J21" s="196"/>
-      <c r="K21" s="196"/>
+      <c r="H21" s="199"/>
+      <c r="I21" s="199"/>
+      <c r="J21" s="199"/>
+      <c r="K21" s="199"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="106" t="s">
@@ -9144,7 +9162,7 @@
       <c r="C22" s="118">
         <v>2.1624242308354207</v>
       </c>
-      <c r="D22" s="196"/>
+      <c r="D22" s="199"/>
       <c r="E22" s="104" t="s">
         <v>650</v>
       </c>
@@ -9154,21 +9172,21 @@
       <c r="G22" s="117">
         <v>6.0022429584871029</v>
       </c>
-      <c r="H22" s="196"/>
-      <c r="I22" s="196"/>
-      <c r="J22" s="196"/>
-      <c r="K22" s="196"/>
+      <c r="H22" s="199"/>
+      <c r="I22" s="199"/>
+      <c r="J22" s="199"/>
+      <c r="K22" s="199"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="217" t="s">
+      <c r="A23" s="219" t="s">
         <v>696</v>
       </c>
-      <c r="B23" s="217"/>
+      <c r="B23" s="219"/>
       <c r="C23" s="145">
         <f>SUM(C6:C22)</f>
         <v>32.915330324875235</v>
       </c>
-      <c r="D23" s="196"/>
+      <c r="D23" s="199"/>
       <c r="E23" s="106" t="s">
         <v>651</v>
       </c>
@@ -9178,7 +9196,7 @@
       <c r="G23" s="118">
         <v>1.172155190546303</v>
       </c>
-      <c r="H23" s="196"/>
+      <c r="H23" s="199"/>
       <c r="I23" s="140" t="s">
         <v>593</v>
       </c>
@@ -9190,19 +9208,19 @@
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="196"/>
-      <c r="B24" s="196"/>
-      <c r="C24" s="196"/>
-      <c r="D24" s="196"/>
-      <c r="E24" s="217" t="s">
+      <c r="A24" s="199"/>
+      <c r="B24" s="199"/>
+      <c r="C24" s="199"/>
+      <c r="D24" s="199"/>
+      <c r="E24" s="219" t="s">
         <v>696</v>
       </c>
-      <c r="F24" s="217"/>
+      <c r="F24" s="219"/>
       <c r="G24" s="145">
         <f>SUM(G6:G23)</f>
         <v>45.916148153813801</v>
       </c>
-      <c r="H24" s="196"/>
+      <c r="H24" s="199"/>
       <c r="I24" s="104" t="s">
         <v>598</v>
       </c>
@@ -9215,6 +9233,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:I3"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="I17:K22"/>
     <mergeCell ref="B4:E4"/>
@@ -9224,11 +9247,6 @@
     <mergeCell ref="I16:J16"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -9256,36 +9274,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
+      <c r="J1" s="187"/>
+      <c r="K1" s="187"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="214" t="s">
+      <c r="B2" s="217" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="214"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="215" t="s">
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="218" t="s">
         <v>391</v>
       </c>
-      <c r="G2" s="215"/>
-      <c r="H2" s="215"/>
-      <c r="I2" s="215"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="218"/>
+      <c r="I2" s="218"/>
       <c r="J2" s="16" t="s">
         <v>392</v>
       </c>
@@ -9297,18 +9315,18 @@
       <c r="A3" s="129">
         <v>1</v>
       </c>
-      <c r="B3" s="212" t="s">
+      <c r="B3" s="215" t="s">
         <v>690</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="213" t="s">
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="216" t="s">
         <v>695</v>
       </c>
-      <c r="G3" s="213"/>
-      <c r="H3" s="213"/>
-      <c r="I3" s="213"/>
+      <c r="G3" s="216"/>
+      <c r="H3" s="216"/>
+      <c r="I3" s="216"/>
       <c r="J3" s="129" t="s">
         <v>394</v>
       </c>
@@ -9321,18 +9339,18 @@
       <c r="A4" s="129">
         <v>2</v>
       </c>
-      <c r="B4" s="212" t="s">
+      <c r="B4" s="215" t="s">
         <v>690</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="216" t="s">
+      <c r="C4" s="215"/>
+      <c r="D4" s="215"/>
+      <c r="E4" s="215"/>
+      <c r="F4" s="220" t="s">
         <v>697</v>
       </c>
-      <c r="G4" s="216"/>
-      <c r="H4" s="216"/>
-      <c r="I4" s="216"/>
+      <c r="G4" s="220"/>
+      <c r="H4" s="220"/>
+      <c r="I4" s="220"/>
       <c r="J4" s="129" t="s">
         <v>394</v>
       </c>
@@ -9350,7 +9368,7 @@
       <c r="C5" s="141" t="s">
         <v>673</v>
       </c>
-      <c r="D5" s="195"/>
+      <c r="D5" s="198"/>
       <c r="E5" s="140" t="s">
         <v>593</v>
       </c>
@@ -9360,7 +9378,7 @@
       <c r="G5" s="141" t="s">
         <v>673</v>
       </c>
-      <c r="H5" s="195"/>
+      <c r="H5" s="198"/>
       <c r="I5" s="140" t="s">
         <v>593</v>
       </c>
@@ -9381,7 +9399,7 @@
       <c r="C6" s="105">
         <v>13.2</v>
       </c>
-      <c r="D6" s="196"/>
+      <c r="D6" s="199"/>
       <c r="E6" s="104" t="s">
         <v>498</v>
       </c>
@@ -9391,7 +9409,7 @@
       <c r="G6" s="105">
         <v>5.4</v>
       </c>
-      <c r="H6" s="196"/>
+      <c r="H6" s="199"/>
       <c r="I6" s="104" t="s">
         <v>510</v>
       </c>
@@ -9412,7 +9430,7 @@
       <c r="C7" s="107">
         <v>5.3</v>
       </c>
-      <c r="D7" s="196"/>
+      <c r="D7" s="199"/>
       <c r="E7" s="106" t="s">
         <v>499</v>
       </c>
@@ -9422,7 +9440,7 @@
       <c r="G7" s="107">
         <v>11.5</v>
       </c>
-      <c r="H7" s="196"/>
+      <c r="H7" s="199"/>
       <c r="I7" s="106" t="s">
         <v>511</v>
       </c>
@@ -9443,7 +9461,7 @@
       <c r="C8" s="105">
         <v>6.1</v>
       </c>
-      <c r="D8" s="196"/>
+      <c r="D8" s="199"/>
       <c r="E8" s="104" t="s">
         <v>500</v>
       </c>
@@ -9453,7 +9471,7 @@
       <c r="G8" s="105">
         <v>11.6</v>
       </c>
-      <c r="H8" s="196"/>
+      <c r="H8" s="199"/>
       <c r="I8" s="104" t="s">
         <v>512</v>
       </c>
@@ -9474,7 +9492,7 @@
       <c r="C9" s="107">
         <v>15.6</v>
       </c>
-      <c r="D9" s="196"/>
+      <c r="D9" s="199"/>
       <c r="E9" s="106" t="s">
         <v>501</v>
       </c>
@@ -9484,7 +9502,7 @@
       <c r="G9" s="107">
         <v>13.6</v>
       </c>
-      <c r="H9" s="196"/>
+      <c r="H9" s="199"/>
       <c r="I9" s="106" t="s">
         <v>506</v>
       </c>
@@ -9505,7 +9523,7 @@
       <c r="C10" s="105">
         <v>5.4</v>
       </c>
-      <c r="D10" s="196"/>
+      <c r="D10" s="199"/>
       <c r="E10" s="104" t="s">
         <v>502</v>
       </c>
@@ -9515,7 +9533,7 @@
       <c r="G10" s="105">
         <v>8.5</v>
       </c>
-      <c r="H10" s="196"/>
+      <c r="H10" s="199"/>
       <c r="I10" s="104" t="s">
         <v>507</v>
       </c>
@@ -9536,7 +9554,7 @@
       <c r="C11" s="107">
         <v>15.5</v>
       </c>
-      <c r="D11" s="196"/>
+      <c r="D11" s="199"/>
       <c r="E11" s="106" t="s">
         <v>503</v>
       </c>
@@ -9546,7 +9564,7 @@
       <c r="G11" s="107">
         <v>10.7</v>
       </c>
-      <c r="H11" s="196"/>
+      <c r="H11" s="199"/>
       <c r="I11" s="106" t="s">
         <v>659</v>
       </c>
@@ -9567,7 +9585,7 @@
       <c r="C12" s="105">
         <v>2.4</v>
       </c>
-      <c r="D12" s="196"/>
+      <c r="D12" s="199"/>
       <c r="E12" s="104" t="s">
         <v>504</v>
       </c>
@@ -9577,7 +9595,7 @@
       <c r="G12" s="105">
         <v>12.2</v>
       </c>
-      <c r="H12" s="196"/>
+      <c r="H12" s="199"/>
       <c r="I12" s="104" t="s">
         <v>508</v>
       </c>
@@ -9598,7 +9616,7 @@
       <c r="C13" s="107">
         <v>6</v>
       </c>
-      <c r="D13" s="196"/>
+      <c r="D13" s="199"/>
       <c r="E13" s="106" t="s">
         <v>639</v>
       </c>
@@ -9608,7 +9626,7 @@
       <c r="G13" s="107">
         <v>23.4</v>
       </c>
-      <c r="H13" s="196"/>
+      <c r="H13" s="199"/>
       <c r="I13" s="106" t="s">
         <v>660</v>
       </c>
@@ -9629,7 +9647,7 @@
       <c r="C14" s="105">
         <v>4</v>
       </c>
-      <c r="D14" s="196"/>
+      <c r="D14" s="199"/>
       <c r="E14" s="104" t="s">
         <v>640</v>
       </c>
@@ -9639,7 +9657,7 @@
       <c r="G14" s="105">
         <v>5.4</v>
       </c>
-      <c r="H14" s="196"/>
+      <c r="H14" s="199"/>
       <c r="I14" s="104" t="s">
         <v>661</v>
       </c>
@@ -9660,7 +9678,7 @@
       <c r="C15" s="107">
         <v>5</v>
       </c>
-      <c r="D15" s="196"/>
+      <c r="D15" s="199"/>
       <c r="E15" s="106" t="s">
         <v>641</v>
       </c>
@@ -9670,7 +9688,7 @@
       <c r="G15" s="107">
         <v>9.8000000000000007</v>
       </c>
-      <c r="H15" s="196"/>
+      <c r="H15" s="199"/>
       <c r="I15" s="108" t="s">
         <v>666</v>
       </c>
@@ -9691,7 +9709,7 @@
       <c r="C16" s="105">
         <v>11</v>
       </c>
-      <c r="D16" s="196"/>
+      <c r="D16" s="199"/>
       <c r="E16" s="104" t="s">
         <v>497</v>
       </c>
@@ -9701,11 +9719,11 @@
       <c r="G16" s="105">
         <v>15.6</v>
       </c>
-      <c r="H16" s="196"/>
-      <c r="I16" s="217" t="s">
+      <c r="H16" s="199"/>
+      <c r="I16" s="219" t="s">
         <v>696</v>
       </c>
-      <c r="J16" s="217"/>
+      <c r="J16" s="219"/>
       <c r="K16" s="134">
         <f>SUM(K6:K15)</f>
         <v>132.9</v>
@@ -9721,7 +9739,7 @@
       <c r="C17" s="107">
         <v>6.7</v>
       </c>
-      <c r="D17" s="196"/>
+      <c r="D17" s="199"/>
       <c r="E17" s="106" t="s">
         <v>495</v>
       </c>
@@ -9731,10 +9749,10 @@
       <c r="G17" s="107">
         <v>15.5</v>
       </c>
-      <c r="H17" s="196"/>
-      <c r="I17" s="196"/>
-      <c r="J17" s="196"/>
-      <c r="K17" s="196"/>
+      <c r="H17" s="199"/>
+      <c r="I17" s="199"/>
+      <c r="J17" s="199"/>
+      <c r="K17" s="199"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="104" t="s">
@@ -9746,7 +9764,7 @@
       <c r="C18" s="105">
         <v>21.27</v>
       </c>
-      <c r="D18" s="196"/>
+      <c r="D18" s="199"/>
       <c r="E18" s="104" t="s">
         <v>496</v>
       </c>
@@ -9756,10 +9774,10 @@
       <c r="G18" s="105">
         <v>5.4</v>
       </c>
-      <c r="H18" s="196"/>
-      <c r="I18" s="196"/>
-      <c r="J18" s="196"/>
-      <c r="K18" s="196"/>
+      <c r="H18" s="199"/>
+      <c r="I18" s="199"/>
+      <c r="J18" s="199"/>
+      <c r="K18" s="199"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="106" t="s">
@@ -9771,7 +9789,7 @@
       <c r="C19" s="107">
         <v>4.8</v>
       </c>
-      <c r="D19" s="196"/>
+      <c r="D19" s="199"/>
       <c r="E19" s="106" t="s">
         <v>647</v>
       </c>
@@ -9781,10 +9799,10 @@
       <c r="G19" s="107">
         <v>6.7</v>
       </c>
-      <c r="H19" s="196"/>
-      <c r="I19" s="196"/>
-      <c r="J19" s="196"/>
-      <c r="K19" s="196"/>
+      <c r="H19" s="199"/>
+      <c r="I19" s="199"/>
+      <c r="J19" s="199"/>
+      <c r="K19" s="199"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="104" t="s">
@@ -9796,7 +9814,7 @@
       <c r="C20" s="105">
         <v>6.7</v>
       </c>
-      <c r="D20" s="196"/>
+      <c r="D20" s="199"/>
       <c r="E20" s="104" t="s">
         <v>648</v>
       </c>
@@ -9806,10 +9824,10 @@
       <c r="G20" s="105">
         <v>29.7</v>
       </c>
-      <c r="H20" s="196"/>
-      <c r="I20" s="196"/>
-      <c r="J20" s="196"/>
-      <c r="K20" s="196"/>
+      <c r="H20" s="199"/>
+      <c r="I20" s="199"/>
+      <c r="J20" s="199"/>
+      <c r="K20" s="199"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="106" t="s">
@@ -9821,7 +9839,7 @@
       <c r="C21" s="107">
         <v>30</v>
       </c>
-      <c r="D21" s="196"/>
+      <c r="D21" s="199"/>
       <c r="E21" s="106" t="s">
         <v>649</v>
       </c>
@@ -9831,10 +9849,10 @@
       <c r="G21" s="107">
         <v>6.7</v>
       </c>
-      <c r="H21" s="196"/>
-      <c r="I21" s="196"/>
-      <c r="J21" s="196"/>
-      <c r="K21" s="196"/>
+      <c r="H21" s="199"/>
+      <c r="I21" s="199"/>
+      <c r="J21" s="199"/>
+      <c r="K21" s="199"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="104" t="s">
@@ -9846,7 +9864,7 @@
       <c r="C22" s="105">
         <v>6.4</v>
       </c>
-      <c r="D22" s="196"/>
+      <c r="D22" s="199"/>
       <c r="E22" s="104" t="s">
         <v>650</v>
       </c>
@@ -9856,10 +9874,10 @@
       <c r="G22" s="105">
         <v>29.7</v>
       </c>
-      <c r="H22" s="196"/>
-      <c r="I22" s="196"/>
-      <c r="J22" s="196"/>
-      <c r="K22" s="196"/>
+      <c r="H22" s="199"/>
+      <c r="I22" s="199"/>
+      <c r="J22" s="199"/>
+      <c r="K22" s="199"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="106" t="s">
@@ -9871,7 +9889,7 @@
       <c r="C23" s="107">
         <v>10.7</v>
       </c>
-      <c r="D23" s="196"/>
+      <c r="D23" s="199"/>
       <c r="E23" s="106" t="s">
         <v>651</v>
       </c>
@@ -9881,36 +9899,41 @@
       <c r="G23" s="107">
         <v>5.8</v>
       </c>
-      <c r="H23" s="196"/>
-      <c r="I23" s="196"/>
-      <c r="J23" s="196"/>
-      <c r="K23" s="196"/>
+      <c r="H23" s="199"/>
+      <c r="I23" s="199"/>
+      <c r="J23" s="199"/>
+      <c r="K23" s="199"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="217" t="s">
+      <c r="A24" s="219" t="s">
         <v>696</v>
       </c>
-      <c r="B24" s="217"/>
+      <c r="B24" s="219"/>
       <c r="C24" s="134">
         <f>SUM(C6:C23)</f>
         <v>176.07</v>
       </c>
-      <c r="D24" s="196"/>
-      <c r="E24" s="217" t="s">
+      <c r="D24" s="199"/>
+      <c r="E24" s="219" t="s">
         <v>696</v>
       </c>
-      <c r="F24" s="217"/>
+      <c r="F24" s="219"/>
       <c r="G24" s="146">
         <f>SUM(G6:G23)</f>
         <v>227.19999999999996</v>
       </c>
-      <c r="H24" s="196"/>
-      <c r="I24" s="196"/>
-      <c r="J24" s="196"/>
-      <c r="K24" s="196"/>
+      <c r="H24" s="199"/>
+      <c r="I24" s="199"/>
+      <c r="J24" s="199"/>
+      <c r="K24" s="199"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:I2"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="F4:I4"/>
     <mergeCell ref="D5:D24"/>
@@ -9919,11 +9942,6 @@
     <mergeCell ref="I17:K24"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -9947,13 +9965,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -10015,13 +10033,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -10083,13 +10101,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -10153,25 +10171,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="188" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="186"/>
-      <c r="D2" s="187"/>
+      <c r="C2" s="189"/>
+      <c r="D2" s="190"/>
       <c r="E2" s="179" t="s">
         <v>391</v>
       </c>
@@ -10186,11 +10204,11 @@
       <c r="A3" s="177">
         <v>1</v>
       </c>
-      <c r="B3" s="188" t="s">
+      <c r="B3" s="191" t="s">
         <v>749</v>
       </c>
-      <c r="C3" s="189"/>
-      <c r="D3" s="190"/>
+      <c r="C3" s="192"/>
+      <c r="D3" s="193"/>
       <c r="E3" s="178" t="s">
         <v>750</v>
       </c>
@@ -10206,11 +10224,11 @@
       <c r="A4" s="177">
         <v>2</v>
       </c>
-      <c r="B4" s="188" t="s">
+      <c r="B4" s="191" t="s">
         <v>712</v>
       </c>
-      <c r="C4" s="189"/>
-      <c r="D4" s="190"/>
+      <c r="C4" s="192"/>
+      <c r="D4" s="193"/>
       <c r="E4" s="178" t="s">
         <v>752</v>
       </c>
@@ -10228,11 +10246,11 @@
       <c r="B5" s="169" t="s">
         <v>393</v>
       </c>
-      <c r="C5" s="191"/>
-      <c r="D5" s="192"/>
-      <c r="E5" s="192"/>
-      <c r="F5" s="192"/>
-      <c r="G5" s="192"/>
+      <c r="C5" s="194"/>
+      <c r="D5" s="195"/>
+      <c r="E5" s="195"/>
+      <c r="F5" s="195"/>
+      <c r="G5" s="195"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="170" t="s">
@@ -10241,11 +10259,11 @@
       <c r="B6" s="171">
         <v>5.63</v>
       </c>
-      <c r="C6" s="193"/>
-      <c r="D6" s="194"/>
-      <c r="E6" s="194"/>
-      <c r="F6" s="194"/>
-      <c r="G6" s="194"/>
+      <c r="C6" s="196"/>
+      <c r="D6" s="197"/>
+      <c r="E6" s="197"/>
+      <c r="F6" s="197"/>
+      <c r="G6" s="197"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="170" t="s">
@@ -10254,11 +10272,11 @@
       <c r="B7" s="171">
         <v>4.92</v>
       </c>
-      <c r="C7" s="193"/>
-      <c r="D7" s="194"/>
-      <c r="E7" s="194"/>
-      <c r="F7" s="194"/>
-      <c r="G7" s="194"/>
+      <c r="C7" s="196"/>
+      <c r="D7" s="197"/>
+      <c r="E7" s="197"/>
+      <c r="F7" s="197"/>
+      <c r="G7" s="197"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="170" t="s">
@@ -10267,11 +10285,11 @@
       <c r="B8" s="171">
         <v>4.7</v>
       </c>
-      <c r="C8" s="193"/>
-      <c r="D8" s="194"/>
-      <c r="E8" s="194"/>
-      <c r="F8" s="194"/>
-      <c r="G8" s="194"/>
+      <c r="C8" s="196"/>
+      <c r="D8" s="197"/>
+      <c r="E8" s="197"/>
+      <c r="F8" s="197"/>
+      <c r="G8" s="197"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="172" t="s">
@@ -10281,11 +10299,11 @@
         <f>SUM(B6:B8)</f>
         <v>15.25</v>
       </c>
-      <c r="C9" s="193"/>
-      <c r="D9" s="194"/>
-      <c r="E9" s="194"/>
-      <c r="F9" s="194"/>
-      <c r="G9" s="194"/>
+      <c r="C9" s="196"/>
+      <c r="D9" s="197"/>
+      <c r="E9" s="197"/>
+      <c r="F9" s="197"/>
+      <c r="G9" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -10317,13 +10335,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -10385,13 +10403,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -10453,13 +10471,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -10525,32 +10543,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="214" t="s">
+      <c r="B2" s="217" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="214"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="207" t="s">
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="210" t="s">
         <v>391</v>
       </c>
-      <c r="G2" s="218"/>
+      <c r="G2" s="221"/>
       <c r="H2" s="16" t="s">
         <v>392</v>
       </c>
@@ -10562,16 +10580,16 @@
       <c r="A3" s="124">
         <v>1</v>
       </c>
-      <c r="B3" s="212" t="s">
+      <c r="B3" s="215" t="s">
         <v>680</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="219" t="s">
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="222" t="s">
         <v>681</v>
       </c>
-      <c r="G3" s="220"/>
+      <c r="G3" s="223"/>
       <c r="H3" s="124" t="s">
         <v>394</v>
       </c>
@@ -10708,11 +10726,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="I1" s="221" t="s">
+      <c r="I1" s="224" t="s">
         <v>195</v>
       </c>
-      <c r="J1" s="221"/>
-      <c r="K1" s="221"/>
+      <c r="J1" s="224"/>
+      <c r="K1" s="224"/>
       <c r="O1" s="1" t="s">
         <v>378</v>
       </c>
@@ -20486,7 +20504,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="54" x14ac:dyDescent="0.3">
       <c r="A3" s="17">
         <v>1</v>
       </c>
@@ -20533,35 +20551,35 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="90"/>
-      <c r="B1" s="226" t="s">
+      <c r="B1" s="225" t="s">
         <v>594</v>
       </c>
-      <c r="C1" s="227"/>
-      <c r="D1" s="227"/>
-      <c r="E1" s="227"/>
-      <c r="F1" s="227"/>
-      <c r="G1" s="227"/>
-      <c r="H1" s="227"/>
-      <c r="I1" s="227"/>
-      <c r="J1" s="227"/>
-      <c r="K1" s="228"/>
+      <c r="C1" s="226"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="226"/>
+      <c r="F1" s="226"/>
+      <c r="G1" s="226"/>
+      <c r="H1" s="226"/>
+      <c r="I1" s="226"/>
+      <c r="J1" s="226"/>
+      <c r="K1" s="227"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="35" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="232" t="s">
+      <c r="B2" s="231" t="s">
         <v>595</v>
       </c>
-      <c r="C2" s="233"/>
-      <c r="D2" s="230" t="s">
+      <c r="C2" s="232"/>
+      <c r="D2" s="229" t="s">
         <v>391</v>
       </c>
-      <c r="E2" s="230"/>
-      <c r="F2" s="230"/>
-      <c r="G2" s="230"/>
-      <c r="H2" s="230"/>
-      <c r="I2" s="230"/>
+      <c r="E2" s="229"/>
+      <c r="F2" s="229"/>
+      <c r="G2" s="229"/>
+      <c r="H2" s="229"/>
+      <c r="I2" s="229"/>
       <c r="J2" s="91" t="s">
         <v>392</v>
       </c>
@@ -20573,18 +20591,18 @@
       <c r="A3" s="35">
         <v>1</v>
       </c>
-      <c r="B3" s="234" t="s">
+      <c r="B3" s="233" t="s">
         <v>596</v>
       </c>
-      <c r="C3" s="235"/>
-      <c r="D3" s="231" t="s">
+      <c r="C3" s="234"/>
+      <c r="D3" s="230" t="s">
         <v>671</v>
       </c>
-      <c r="E3" s="231"/>
-      <c r="F3" s="231"/>
-      <c r="G3" s="231"/>
-      <c r="H3" s="231"/>
-      <c r="I3" s="231"/>
+      <c r="E3" s="230"/>
+      <c r="F3" s="230"/>
+      <c r="G3" s="230"/>
+      <c r="H3" s="230"/>
+      <c r="I3" s="230"/>
       <c r="J3" s="91" t="s">
         <v>394</v>
       </c>
@@ -20594,17 +20612,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="229"/>
-      <c r="B4" s="229"/>
-      <c r="C4" s="229"/>
-      <c r="D4" s="229"/>
-      <c r="E4" s="229"/>
-      <c r="F4" s="229"/>
-      <c r="G4" s="229"/>
-      <c r="H4" s="229"/>
-      <c r="I4" s="229"/>
-      <c r="J4" s="229"/>
-      <c r="K4" s="229"/>
+      <c r="A4" s="228"/>
+      <c r="B4" s="228"/>
+      <c r="C4" s="228"/>
+      <c r="D4" s="228"/>
+      <c r="E4" s="228"/>
+      <c r="F4" s="228"/>
+      <c r="G4" s="228"/>
+      <c r="H4" s="228"/>
+      <c r="I4" s="228"/>
+      <c r="J4" s="228"/>
+      <c r="K4" s="228"/>
     </row>
     <row r="5" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="151" t="s">
@@ -20616,7 +20634,7 @@
       <c r="C5" s="151" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="223"/>
+      <c r="D5" s="236"/>
       <c r="E5" s="151" t="s">
         <v>0</v>
       </c>
@@ -20626,7 +20644,7 @@
       <c r="G5" s="151" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="223"/>
+      <c r="H5" s="236"/>
       <c r="I5" s="151" t="s">
         <v>0</v>
       </c>
@@ -20647,7 +20665,7 @@
       <c r="C6" s="153">
         <v>22.1</v>
       </c>
-      <c r="D6" s="223"/>
+      <c r="D6" s="236"/>
       <c r="E6" s="154">
         <v>2.0099999999999998</v>
       </c>
@@ -20657,7 +20675,7 @@
       <c r="G6" s="155">
         <v>62.2</v>
       </c>
-      <c r="H6" s="223"/>
+      <c r="H6" s="236"/>
       <c r="I6" s="154">
         <v>3.01</v>
       </c>
@@ -20678,7 +20696,7 @@
       <c r="C7" s="155">
         <v>62.9</v>
       </c>
-      <c r="D7" s="223"/>
+      <c r="D7" s="236"/>
       <c r="E7" s="152">
         <v>2.02</v>
       </c>
@@ -20688,7 +20706,7 @@
       <c r="G7" s="153">
         <v>89</v>
       </c>
-      <c r="H7" s="223"/>
+      <c r="H7" s="236"/>
       <c r="I7" s="152">
         <v>3.02</v>
       </c>
@@ -20709,7 +20727,7 @@
       <c r="C8" s="153">
         <v>64.3</v>
       </c>
-      <c r="D8" s="223"/>
+      <c r="D8" s="236"/>
       <c r="E8" s="154">
         <v>2.0299999999999998</v>
       </c>
@@ -20719,7 +20737,7 @@
       <c r="G8" s="155">
         <v>39.4</v>
       </c>
-      <c r="H8" s="223"/>
+      <c r="H8" s="236"/>
       <c r="I8" s="154">
         <v>3.03</v>
       </c>
@@ -20740,7 +20758,7 @@
       <c r="C9" s="155">
         <v>64.400000000000006</v>
       </c>
-      <c r="D9" s="223"/>
+      <c r="D9" s="236"/>
       <c r="E9" s="152">
         <v>2.04</v>
       </c>
@@ -20750,7 +20768,7 @@
       <c r="G9" s="153">
         <v>63</v>
       </c>
-      <c r="H9" s="223"/>
+      <c r="H9" s="236"/>
       <c r="I9" s="152">
         <v>3.04</v>
       </c>
@@ -20771,7 +20789,7 @@
       <c r="C10" s="153">
         <v>131.19999999999999</v>
       </c>
-      <c r="D10" s="223"/>
+      <c r="D10" s="236"/>
       <c r="E10" s="154">
         <v>2.0499999999999998</v>
       </c>
@@ -20781,7 +20799,7 @@
       <c r="G10" s="155">
         <v>64.400000000000006</v>
       </c>
-      <c r="H10" s="223"/>
+      <c r="H10" s="236"/>
       <c r="I10" s="154">
         <v>3.05</v>
       </c>
@@ -20802,7 +20820,7 @@
       <c r="C11" s="155">
         <v>20.7</v>
       </c>
-      <c r="D11" s="223"/>
+      <c r="D11" s="236"/>
       <c r="E11" s="152">
         <v>2.06</v>
       </c>
@@ -20812,7 +20830,7 @@
       <c r="G11" s="153">
         <v>63.3</v>
       </c>
-      <c r="H11" s="223"/>
+      <c r="H11" s="236"/>
       <c r="I11" s="152">
         <v>3.06</v>
       </c>
@@ -20833,7 +20851,7 @@
       <c r="C12" s="153">
         <v>20.399999999999999</v>
       </c>
-      <c r="D12" s="223"/>
+      <c r="D12" s="236"/>
       <c r="E12" s="154">
         <v>2.0699999999999998</v>
       </c>
@@ -20843,7 +20861,7 @@
       <c r="G12" s="155">
         <v>63.3</v>
       </c>
-      <c r="H12" s="223"/>
+      <c r="H12" s="236"/>
       <c r="I12" s="154">
         <v>3.07</v>
       </c>
@@ -20864,7 +20882,7 @@
       <c r="C13" s="155">
         <v>10.1</v>
       </c>
-      <c r="D13" s="223"/>
+      <c r="D13" s="236"/>
       <c r="E13" s="152">
         <v>2.08</v>
       </c>
@@ -20874,7 +20892,7 @@
       <c r="G13" s="153">
         <v>78.2</v>
       </c>
-      <c r="H13" s="223"/>
+      <c r="H13" s="236"/>
       <c r="I13" s="152">
         <v>3.08</v>
       </c>
@@ -20895,7 +20913,7 @@
       <c r="C14" s="153">
         <v>10.3</v>
       </c>
-      <c r="D14" s="223"/>
+      <c r="D14" s="236"/>
       <c r="E14" s="154">
         <v>2.12</v>
       </c>
@@ -20905,7 +20923,7 @@
       <c r="G14" s="155">
         <v>27</v>
       </c>
-      <c r="H14" s="223"/>
+      <c r="H14" s="236"/>
       <c r="I14" s="154">
         <v>3.12</v>
       </c>
@@ -20926,7 +20944,7 @@
       <c r="C15" s="155">
         <v>10.7</v>
       </c>
-      <c r="D15" s="223"/>
+      <c r="D15" s="236"/>
       <c r="E15" s="152">
         <v>2.15</v>
       </c>
@@ -20936,7 +20954,7 @@
       <c r="G15" s="153">
         <v>28</v>
       </c>
-      <c r="H15" s="223"/>
+      <c r="H15" s="236"/>
       <c r="I15" s="152">
         <v>3.13</v>
       </c>
@@ -20957,7 +20975,7 @@
       <c r="C16" s="153">
         <v>25.9</v>
       </c>
-      <c r="D16" s="223"/>
+      <c r="D16" s="236"/>
       <c r="E16" s="154">
         <v>2.1800000000000002</v>
       </c>
@@ -20967,7 +20985,7 @@
       <c r="G16" s="155">
         <v>31.5</v>
       </c>
-      <c r="H16" s="223"/>
+      <c r="H16" s="236"/>
       <c r="I16" s="154">
         <v>3.18</v>
       </c>
@@ -20988,7 +21006,7 @@
       <c r="C17" s="155">
         <v>22.1</v>
       </c>
-      <c r="D17" s="223"/>
+      <c r="D17" s="236"/>
       <c r="E17" s="152">
         <v>2.19</v>
       </c>
@@ -20998,7 +21016,7 @@
       <c r="G17" s="153">
         <v>359.3</v>
       </c>
-      <c r="H17" s="223"/>
+      <c r="H17" s="236"/>
       <c r="I17" s="152">
         <v>3.19</v>
       </c>
@@ -21019,7 +21037,7 @@
       <c r="C18" s="154">
         <v>28.125999999999998</v>
       </c>
-      <c r="D18" s="223"/>
+      <c r="D18" s="236"/>
       <c r="E18" s="154">
         <v>2.21</v>
       </c>
@@ -21029,7 +21047,7 @@
       <c r="G18" s="155">
         <v>14</v>
       </c>
-      <c r="H18" s="223"/>
+      <c r="H18" s="236"/>
       <c r="I18" s="154">
         <v>3.23</v>
       </c>
@@ -21050,7 +21068,7 @@
       <c r="C19" s="153">
         <v>92.2</v>
       </c>
-      <c r="D19" s="223"/>
+      <c r="D19" s="236"/>
       <c r="E19" s="152">
         <v>2.27</v>
       </c>
@@ -21060,7 +21078,7 @@
       <c r="G19" s="153">
         <v>19.100000000000001</v>
       </c>
-      <c r="H19" s="223"/>
+      <c r="H19" s="236"/>
       <c r="I19" s="152">
         <v>3.25</v>
       </c>
@@ -21081,7 +21099,7 @@
       <c r="C20" s="155">
         <v>113</v>
       </c>
-      <c r="D20" s="223"/>
+      <c r="D20" s="236"/>
       <c r="E20" s="154">
         <v>2.2799999999999998</v>
       </c>
@@ -21091,7 +21109,7 @@
       <c r="G20" s="155">
         <v>192.9</v>
       </c>
-      <c r="H20" s="223"/>
+      <c r="H20" s="236"/>
       <c r="I20" s="154">
         <v>3.26</v>
       </c>
@@ -21112,7 +21130,7 @@
       <c r="C21" s="153">
         <v>9.3000000000000007</v>
       </c>
-      <c r="D21" s="223"/>
+      <c r="D21" s="236"/>
       <c r="E21" s="152">
         <v>2.29</v>
       </c>
@@ -21122,7 +21140,7 @@
       <c r="G21" s="153">
         <v>14.3</v>
       </c>
-      <c r="H21" s="223"/>
+      <c r="H21" s="236"/>
       <c r="I21" s="152">
         <v>3.28</v>
       </c>
@@ -21143,7 +21161,7 @@
       <c r="C22" s="155">
         <v>58.9</v>
       </c>
-      <c r="D22" s="223"/>
+      <c r="D22" s="236"/>
       <c r="E22" s="154">
         <v>2.2999999999999998</v>
       </c>
@@ -21153,7 +21171,7 @@
       <c r="G22" s="155">
         <v>115.5</v>
       </c>
-      <c r="H22" s="223"/>
+      <c r="H22" s="236"/>
       <c r="I22" s="154">
         <v>3.29</v>
       </c>
@@ -21174,7 +21192,7 @@
       <c r="C23" s="153">
         <v>16.8</v>
       </c>
-      <c r="D23" s="223"/>
+      <c r="D23" s="236"/>
       <c r="E23" s="152">
         <v>2.37</v>
       </c>
@@ -21184,7 +21202,7 @@
       <c r="G23" s="153">
         <v>21.6</v>
       </c>
-      <c r="H23" s="223"/>
+      <c r="H23" s="236"/>
       <c r="I23" s="152">
         <v>3.3</v>
       </c>
@@ -21205,7 +21223,7 @@
       <c r="C24" s="155">
         <v>24</v>
       </c>
-      <c r="D24" s="223"/>
+      <c r="D24" s="236"/>
       <c r="E24" s="154">
         <v>2.4</v>
       </c>
@@ -21215,7 +21233,7 @@
       <c r="G24" s="155">
         <v>51.3</v>
       </c>
-      <c r="H24" s="223"/>
+      <c r="H24" s="236"/>
       <c r="I24" s="154">
         <v>3.33</v>
       </c>
@@ -21236,7 +21254,7 @@
       <c r="C25" s="153">
         <v>51.3</v>
       </c>
-      <c r="D25" s="223"/>
+      <c r="D25" s="236"/>
       <c r="E25" s="152">
         <v>2.41</v>
       </c>
@@ -21246,7 +21264,7 @@
       <c r="G25" s="153">
         <v>56.6</v>
       </c>
-      <c r="H25" s="223"/>
+      <c r="H25" s="236"/>
       <c r="I25" s="152">
         <v>3.34</v>
       </c>
@@ -21267,7 +21285,7 @@
       <c r="C26" s="155">
         <v>56.6</v>
       </c>
-      <c r="D26" s="223"/>
+      <c r="D26" s="236"/>
       <c r="E26" s="154">
         <v>2.42</v>
       </c>
@@ -21277,7 +21295,7 @@
       <c r="G26" s="155">
         <v>21.5</v>
       </c>
-      <c r="H26" s="223"/>
+      <c r="H26" s="236"/>
       <c r="I26" s="154">
         <v>3.35</v>
       </c>
@@ -21298,7 +21316,7 @@
       <c r="C27" s="153">
         <v>18.5</v>
       </c>
-      <c r="D27" s="223"/>
+      <c r="D27" s="236"/>
       <c r="E27" s="152">
         <v>2.44</v>
       </c>
@@ -21308,7 +21326,7 @@
       <c r="G27" s="153">
         <v>51.3</v>
       </c>
-      <c r="H27" s="223"/>
+      <c r="H27" s="236"/>
       <c r="I27" s="152">
         <v>3.41</v>
       </c>
@@ -21329,7 +21347,7 @@
       <c r="C28" s="155">
         <v>51.2</v>
       </c>
-      <c r="D28" s="223"/>
+      <c r="D28" s="236"/>
       <c r="E28" s="154">
         <v>2.4500000000000002</v>
       </c>
@@ -21339,7 +21357,7 @@
       <c r="G28" s="155">
         <v>56.3</v>
       </c>
-      <c r="H28" s="223"/>
+      <c r="H28" s="236"/>
       <c r="I28" s="154">
         <v>3.42</v>
       </c>
@@ -21360,7 +21378,7 @@
       <c r="C29" s="153">
         <v>56.3</v>
       </c>
-      <c r="D29" s="223"/>
+      <c r="D29" s="236"/>
       <c r="E29" s="152">
         <v>2.4700000000000002</v>
       </c>
@@ -21370,7 +21388,7 @@
       <c r="G29" s="153">
         <v>75.599999999999994</v>
       </c>
-      <c r="H29" s="223"/>
+      <c r="H29" s="236"/>
       <c r="I29" s="152">
         <v>3.44</v>
       </c>
@@ -21391,7 +21409,7 @@
       <c r="C30" s="155">
         <v>6.3</v>
       </c>
-      <c r="D30" s="223"/>
+      <c r="D30" s="236"/>
       <c r="E30" s="154">
         <v>2.48</v>
       </c>
@@ -21401,7 +21419,7 @@
       <c r="G30" s="155">
         <v>7</v>
       </c>
-      <c r="H30" s="223"/>
+      <c r="H30" s="236"/>
       <c r="I30" s="156">
         <v>3.45</v>
       </c>
@@ -21422,7 +21440,7 @@
       <c r="C31" s="153">
         <v>41.2</v>
       </c>
-      <c r="D31" s="223"/>
+      <c r="D31" s="236"/>
       <c r="E31" s="152">
         <v>2.4900000000000002</v>
       </c>
@@ -21432,11 +21450,11 @@
       <c r="G31" s="153">
         <v>75.2</v>
       </c>
-      <c r="H31" s="223"/>
-      <c r="I31" s="222" t="s">
+      <c r="H31" s="236"/>
+      <c r="I31" s="235" t="s">
         <v>396</v>
       </c>
-      <c r="J31" s="222"/>
+      <c r="J31" s="235"/>
       <c r="K31" s="158">
         <f>SUM(K6:K30)</f>
         <v>1601.7000000000003</v>
@@ -21452,7 +21470,7 @@
       <c r="C32" s="155">
         <v>60</v>
       </c>
-      <c r="D32" s="223"/>
+      <c r="D32" s="236"/>
       <c r="E32" s="154">
         <v>2.5</v>
       </c>
@@ -21462,10 +21480,10 @@
       <c r="G32" s="155">
         <v>6.2</v>
       </c>
-      <c r="H32" s="223"/>
-      <c r="I32" s="224"/>
-      <c r="J32" s="224"/>
-      <c r="K32" s="224"/>
+      <c r="H32" s="236"/>
+      <c r="I32" s="237"/>
+      <c r="J32" s="237"/>
+      <c r="K32" s="237"/>
     </row>
     <row r="33" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="152">
@@ -21477,7 +21495,7 @@
       <c r="C33" s="153">
         <v>24.5</v>
       </c>
-      <c r="D33" s="223"/>
+      <c r="D33" s="236"/>
       <c r="E33" s="152">
         <v>2.5099999999999998</v>
       </c>
@@ -21487,21 +21505,21 @@
       <c r="G33" s="153">
         <v>38.700000000000003</v>
       </c>
-      <c r="H33" s="223"/>
-      <c r="I33" s="225"/>
-      <c r="J33" s="225"/>
-      <c r="K33" s="225"/>
+      <c r="H33" s="236"/>
+      <c r="I33" s="238"/>
+      <c r="J33" s="238"/>
+      <c r="K33" s="238"/>
     </row>
     <row r="34" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="222" t="s">
+      <c r="A34" s="235" t="s">
         <v>396</v>
       </c>
-      <c r="B34" s="222"/>
+      <c r="B34" s="235"/>
       <c r="C34" s="158">
         <f>SUM(C6:C33)</f>
         <v>1173.3259999999998</v>
       </c>
-      <c r="D34" s="223"/>
+      <c r="D34" s="236"/>
       <c r="E34" s="154">
         <v>2.56</v>
       </c>
@@ -21511,16 +21529,16 @@
       <c r="G34" s="155">
         <v>63.1</v>
       </c>
-      <c r="H34" s="223"/>
-      <c r="I34" s="225"/>
-      <c r="J34" s="225"/>
-      <c r="K34" s="225"/>
+      <c r="H34" s="236"/>
+      <c r="I34" s="238"/>
+      <c r="J34" s="238"/>
+      <c r="K34" s="238"/>
     </row>
     <row r="35" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="224"/>
-      <c r="B35" s="224"/>
-      <c r="C35" s="224"/>
-      <c r="D35" s="223"/>
+      <c r="A35" s="237"/>
+      <c r="B35" s="237"/>
+      <c r="C35" s="237"/>
+      <c r="D35" s="236"/>
       <c r="E35" s="152">
         <v>2.58</v>
       </c>
@@ -21530,37 +21548,31 @@
       <c r="G35" s="153">
         <v>76.2</v>
       </c>
-      <c r="H35" s="223"/>
-      <c r="I35" s="225"/>
-      <c r="J35" s="225"/>
-      <c r="K35" s="225"/>
+      <c r="H35" s="236"/>
+      <c r="I35" s="238"/>
+      <c r="J35" s="238"/>
+      <c r="K35" s="238"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="225"/>
-      <c r="B36" s="225"/>
-      <c r="C36" s="225"/>
-      <c r="D36" s="223"/>
-      <c r="E36" s="222" t="s">
+      <c r="A36" s="238"/>
+      <c r="B36" s="238"/>
+      <c r="C36" s="238"/>
+      <c r="D36" s="236"/>
+      <c r="E36" s="235" t="s">
         <v>396</v>
       </c>
-      <c r="F36" s="222"/>
+      <c r="F36" s="235"/>
       <c r="G36" s="158">
         <f>SUM(G6:G35)</f>
         <v>1924.9999999999998</v>
       </c>
-      <c r="H36" s="223"/>
-      <c r="I36" s="225"/>
-      <c r="J36" s="225"/>
-      <c r="K36" s="225"/>
+      <c r="H36" s="236"/>
+      <c r="I36" s="238"/>
+      <c r="J36" s="238"/>
+      <c r="K36" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B1:K1"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="E36:F36"/>
     <mergeCell ref="I31:J31"/>
@@ -21568,6 +21580,12 @@
     <mergeCell ref="D5:D36"/>
     <mergeCell ref="A35:C36"/>
     <mergeCell ref="I32:K36"/>
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -21589,11 +21607,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="236" t="s">
+      <c r="A1" s="239" t="s">
         <v>395</v>
       </c>
-      <c r="B1" s="237"/>
-      <c r="C1" s="238"/>
+      <c r="B1" s="240"/>
+      <c r="C1" s="241"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
@@ -21761,11 +21779,11 @@
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="7.21875" style="180" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" style="180" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.21875" style="180" customWidth="1"/>
     <col min="4" max="4" width="37.77734375" style="180" customWidth="1"/>
     <col min="5" max="5" width="11.88671875" style="180" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.21875" style="180" bestFit="1" customWidth="1"/>
@@ -21775,25 +21793,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="188" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="186"/>
-      <c r="D2" s="187"/>
+      <c r="C2" s="189"/>
+      <c r="D2" s="190"/>
       <c r="E2" s="179" t="s">
         <v>391</v>
       </c>
@@ -21804,15 +21822,15 @@
         <v>393</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="177">
         <v>1</v>
       </c>
-      <c r="B3" s="188" t="s">
-        <v>749</v>
-      </c>
-      <c r="C3" s="189"/>
-      <c r="D3" s="190"/>
+      <c r="B3" s="191" t="s">
+        <v>760</v>
+      </c>
+      <c r="C3" s="192"/>
+      <c r="D3" s="193"/>
       <c r="E3" s="178" t="s">
         <v>750</v>
       </c>
@@ -21820,69 +21838,99 @@
         <v>394</v>
       </c>
       <c r="G3" s="76">
-        <f>B7</f>
+        <f>B8</f>
         <v>102.6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="168" t="s">
+    <row r="4" spans="1:7" s="185" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="184">
+        <v>2</v>
+      </c>
+      <c r="B4" s="191" t="s">
+        <v>761</v>
+      </c>
+      <c r="C4" s="192"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="186" t="s">
+        <v>752</v>
+      </c>
+      <c r="F4" s="184" t="s">
+        <v>394</v>
+      </c>
+      <c r="G4" s="76">
+        <f>C8</f>
+        <v>51.900000000000006</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="168" t="s">
         <v>593</v>
       </c>
-      <c r="B4" s="169" t="s">
+      <c r="B5" s="169" t="s">
         <v>393</v>
       </c>
-      <c r="C4" s="191"/>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="170" t="s">
-        <v>751</v>
-      </c>
-      <c r="B5" s="171">
-        <v>41.8</v>
-      </c>
-      <c r="C5" s="193"/>
+      <c r="C5" s="169" t="s">
+        <v>759</v>
+      </c>
       <c r="D5" s="194"/>
-      <c r="E5" s="194"/>
-      <c r="F5" s="194"/>
-      <c r="G5" s="194"/>
+      <c r="E5" s="195"/>
+      <c r="F5" s="195"/>
+      <c r="G5" s="195"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="170" t="s">
+        <v>751</v>
+      </c>
+      <c r="B6" s="171">
+        <v>41.8</v>
+      </c>
+      <c r="C6" s="171">
+        <v>21.12</v>
+      </c>
+      <c r="D6" s="196"/>
+      <c r="E6" s="197"/>
+      <c r="F6" s="197"/>
+      <c r="G6" s="197"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="170" t="s">
         <v>553</v>
       </c>
-      <c r="B6" s="171">
+      <c r="B7" s="171">
         <v>60.8</v>
       </c>
-      <c r="C6" s="193"/>
-      <c r="D6" s="194"/>
-      <c r="E6" s="194"/>
-      <c r="F6" s="194"/>
-      <c r="G6" s="194"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="172" t="s">
+      <c r="C7" s="171">
+        <v>30.78</v>
+      </c>
+      <c r="D7" s="196"/>
+      <c r="E7" s="197"/>
+      <c r="F7" s="197"/>
+      <c r="G7" s="197"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="172" t="s">
         <v>474</v>
       </c>
-      <c r="B7" s="171">
-        <f>SUM(B5:B6)</f>
+      <c r="B8" s="171">
+        <f>SUM(B6:B7)</f>
         <v>102.6</v>
       </c>
-      <c r="C7" s="193"/>
-      <c r="D7" s="194"/>
-      <c r="E7" s="194"/>
-      <c r="F7" s="194"/>
-      <c r="G7" s="194"/>
+      <c r="C8" s="171">
+        <f>SUM(C6:C7)</f>
+        <v>51.900000000000006</v>
+      </c>
+      <c r="D8" s="196"/>
+      <c r="E8" s="197"/>
+      <c r="F8" s="197"/>
+      <c r="G8" s="197"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="C4:G7"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="D5:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -21927,7 +21975,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="54" x14ac:dyDescent="0.3">
       <c r="A3" s="17">
         <v>1</v>
       </c>
@@ -21972,34 +22020,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
+      <c r="J1" s="187"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="214" t="s">
+      <c r="B2" s="217" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="214"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="207" t="s">
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="210" t="s">
         <v>391</v>
       </c>
-      <c r="G2" s="218"/>
-      <c r="H2" s="208"/>
+      <c r="G2" s="221"/>
+      <c r="H2" s="211"/>
       <c r="I2" s="16" t="s">
         <v>392</v>
       </c>
@@ -22011,17 +22059,17 @@
       <c r="A3" s="75">
         <v>1</v>
       </c>
-      <c r="B3" s="212" t="s">
+      <c r="B3" s="215" t="s">
         <v>597</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="219" t="s">
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="222" t="s">
         <v>672</v>
       </c>
-      <c r="G3" s="220"/>
-      <c r="H3" s="243"/>
+      <c r="G3" s="223"/>
+      <c r="H3" s="246"/>
       <c r="I3" s="75" t="s">
         <v>394</v>
       </c>
@@ -22031,16 +22079,16 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="195"/>
-      <c r="B4" s="195"/>
-      <c r="C4" s="195"/>
-      <c r="D4" s="195"/>
-      <c r="E4" s="195"/>
-      <c r="F4" s="195"/>
-      <c r="G4" s="195"/>
-      <c r="H4" s="195"/>
-      <c r="I4" s="195"/>
-      <c r="J4" s="195"/>
+      <c r="A4" s="198"/>
+      <c r="B4" s="198"/>
+      <c r="C4" s="198"/>
+      <c r="D4" s="198"/>
+      <c r="E4" s="198"/>
+      <c r="F4" s="198"/>
+      <c r="G4" s="198"/>
+      <c r="H4" s="198"/>
+      <c r="I4" s="198"/>
+      <c r="J4" s="198"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="87" t="s">
@@ -22052,7 +22100,7 @@
       <c r="C5" s="87" t="s">
         <v>591</v>
       </c>
-      <c r="D5" s="242"/>
+      <c r="D5" s="245"/>
       <c r="E5" s="87" t="s">
         <v>593</v>
       </c>
@@ -22062,9 +22110,9 @@
       <c r="G5" s="87" t="s">
         <v>591</v>
       </c>
-      <c r="H5" s="239"/>
-      <c r="I5" s="240"/>
-      <c r="J5" s="240"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="243"/>
+      <c r="J5" s="243"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="89" t="s">
@@ -22076,7 +22124,7 @@
       <c r="C6" s="99">
         <v>50.786999999999999</v>
       </c>
-      <c r="D6" s="242"/>
+      <c r="D6" s="245"/>
       <c r="E6" s="89" t="s">
         <v>588</v>
       </c>
@@ -22086,9 +22134,9 @@
       <c r="G6" s="99">
         <v>63.7</v>
       </c>
-      <c r="H6" s="239"/>
-      <c r="I6" s="240"/>
-      <c r="J6" s="240"/>
+      <c r="H6" s="242"/>
+      <c r="I6" s="243"/>
+      <c r="J6" s="243"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="88" t="s">
@@ -22100,7 +22148,7 @@
       <c r="C7" s="89">
         <v>56.033999999999999</v>
       </c>
-      <c r="D7" s="242"/>
+      <c r="D7" s="245"/>
       <c r="E7" s="88" t="s">
         <v>445</v>
       </c>
@@ -22110,9 +22158,9 @@
       <c r="G7" s="89">
         <v>90.2</v>
       </c>
-      <c r="H7" s="239"/>
-      <c r="I7" s="240"/>
-      <c r="J7" s="240"/>
+      <c r="H7" s="242"/>
+      <c r="I7" s="243"/>
+      <c r="J7" s="243"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="89" t="s">
@@ -22124,7 +22172,7 @@
       <c r="C8" s="89">
         <v>50.786999999999999</v>
       </c>
-      <c r="D8" s="242"/>
+      <c r="D8" s="245"/>
       <c r="E8" s="89" t="s">
         <v>446</v>
       </c>
@@ -22134,9 +22182,9 @@
       <c r="G8" s="89">
         <v>40.1</v>
       </c>
-      <c r="H8" s="239"/>
-      <c r="I8" s="240"/>
-      <c r="J8" s="240"/>
+      <c r="H8" s="242"/>
+      <c r="I8" s="243"/>
+      <c r="J8" s="243"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="88" t="s">
@@ -22148,7 +22196,7 @@
       <c r="C9" s="89">
         <v>55.736999999999995</v>
       </c>
-      <c r="D9" s="242"/>
+      <c r="D9" s="245"/>
       <c r="E9" s="88" t="s">
         <v>447</v>
       </c>
@@ -22158,9 +22206,9 @@
       <c r="G9" s="89">
         <v>64</v>
       </c>
-      <c r="H9" s="239"/>
-      <c r="I9" s="240"/>
-      <c r="J9" s="240"/>
+      <c r="H9" s="242"/>
+      <c r="I9" s="243"/>
+      <c r="J9" s="243"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="89" t="s">
@@ -22172,7 +22220,7 @@
       <c r="C10" s="89">
         <v>51.579000000000001</v>
       </c>
-      <c r="D10" s="242"/>
+      <c r="D10" s="245"/>
       <c r="E10" s="89" t="s">
         <v>448</v>
       </c>
@@ -22182,9 +22230,9 @@
       <c r="G10" s="89">
         <v>65.400000000000006</v>
       </c>
-      <c r="H10" s="239"/>
-      <c r="I10" s="240"/>
-      <c r="J10" s="240"/>
+      <c r="H10" s="242"/>
+      <c r="I10" s="243"/>
+      <c r="J10" s="243"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="88" t="s">
@@ -22196,7 +22244,7 @@
       <c r="C11" s="89">
         <v>56.43</v>
       </c>
-      <c r="D11" s="242"/>
+      <c r="D11" s="245"/>
       <c r="E11" s="88" t="s">
         <v>449</v>
       </c>
@@ -22206,9 +22254,9 @@
       <c r="G11" s="89">
         <v>64.099999999999994</v>
       </c>
-      <c r="H11" s="239"/>
-      <c r="I11" s="240"/>
-      <c r="J11" s="240"/>
+      <c r="H11" s="242"/>
+      <c r="I11" s="243"/>
+      <c r="J11" s="243"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="89" t="s">
@@ -22220,7 +22268,7 @@
       <c r="C12" s="89">
         <v>51.084000000000003</v>
       </c>
-      <c r="D12" s="242"/>
+      <c r="D12" s="245"/>
       <c r="E12" s="89" t="s">
         <v>450</v>
       </c>
@@ -22230,9 +22278,9 @@
       <c r="G12" s="89">
         <v>64.3</v>
       </c>
-      <c r="H12" s="239"/>
-      <c r="I12" s="240"/>
-      <c r="J12" s="240"/>
+      <c r="H12" s="242"/>
+      <c r="I12" s="243"/>
+      <c r="J12" s="243"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="88" t="s">
@@ -22244,7 +22292,7 @@
       <c r="C13" s="89">
         <v>55.736999999999995</v>
       </c>
-      <c r="D13" s="242"/>
+      <c r="D13" s="245"/>
       <c r="E13" s="88" t="s">
         <v>461</v>
       </c>
@@ -22254,9 +22302,9 @@
       <c r="G13" s="89">
         <v>62.8</v>
       </c>
-      <c r="H13" s="239"/>
-      <c r="I13" s="240"/>
-      <c r="J13" s="240"/>
+      <c r="H13" s="242"/>
+      <c r="I13" s="243"/>
+      <c r="J13" s="243"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="89" t="s">
@@ -22268,7 +22316,7 @@
       <c r="C14" s="89">
         <v>74.745000000000005</v>
       </c>
-      <c r="D14" s="242"/>
+      <c r="D14" s="245"/>
       <c r="E14" s="89" t="s">
         <v>462</v>
       </c>
@@ -22278,9 +22326,9 @@
       <c r="G14" s="89">
         <v>89.1</v>
       </c>
-      <c r="H14" s="239"/>
-      <c r="I14" s="240"/>
-      <c r="J14" s="240"/>
+      <c r="H14" s="242"/>
+      <c r="I14" s="243"/>
+      <c r="J14" s="243"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="88" t="s">
@@ -22292,7 +22340,7 @@
       <c r="C15" s="89">
         <v>74.15100000000001</v>
       </c>
-      <c r="D15" s="242"/>
+      <c r="D15" s="245"/>
       <c r="E15" s="88" t="s">
         <v>463</v>
       </c>
@@ -22302,9 +22350,9 @@
       <c r="G15" s="89">
         <v>29.7</v>
       </c>
-      <c r="H15" s="239"/>
-      <c r="I15" s="240"/>
-      <c r="J15" s="240"/>
+      <c r="H15" s="242"/>
+      <c r="I15" s="243"/>
+      <c r="J15" s="243"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="88" t="s">
@@ -22314,7 +22362,7 @@
         <f>SUM(C6:C15)</f>
         <v>577.07099999999991</v>
       </c>
-      <c r="D16" s="242"/>
+      <c r="D16" s="245"/>
       <c r="E16" s="89" t="s">
         <v>464</v>
       </c>
@@ -22324,15 +22372,15 @@
       <c r="G16" s="89">
         <v>64.8</v>
       </c>
-      <c r="H16" s="239"/>
-      <c r="I16" s="240"/>
-      <c r="J16" s="240"/>
+      <c r="H16" s="242"/>
+      <c r="I16" s="243"/>
+      <c r="J16" s="243"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="241"/>
-      <c r="B17" s="241"/>
-      <c r="C17" s="241"/>
-      <c r="D17" s="242"/>
+      <c r="A17" s="244"/>
+      <c r="B17" s="244"/>
+      <c r="C17" s="244"/>
+      <c r="D17" s="245"/>
       <c r="E17" s="88" t="s">
         <v>465</v>
       </c>
@@ -22342,15 +22390,15 @@
       <c r="G17" s="89">
         <v>63.8</v>
       </c>
-      <c r="H17" s="239"/>
-      <c r="I17" s="240"/>
-      <c r="J17" s="240"/>
+      <c r="H17" s="242"/>
+      <c r="I17" s="243"/>
+      <c r="J17" s="243"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="241"/>
-      <c r="B18" s="241"/>
-      <c r="C18" s="241"/>
-      <c r="D18" s="242"/>
+      <c r="A18" s="244"/>
+      <c r="B18" s="244"/>
+      <c r="C18" s="244"/>
+      <c r="D18" s="245"/>
       <c r="E18" s="89" t="s">
         <v>589</v>
       </c>
@@ -22360,15 +22408,15 @@
       <c r="G18" s="89">
         <v>65.5</v>
       </c>
-      <c r="H18" s="239"/>
-      <c r="I18" s="240"/>
-      <c r="J18" s="240"/>
+      <c r="H18" s="242"/>
+      <c r="I18" s="243"/>
+      <c r="J18" s="243"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="241"/>
-      <c r="B19" s="241"/>
-      <c r="C19" s="241"/>
-      <c r="D19" s="242"/>
+      <c r="A19" s="244"/>
+      <c r="B19" s="244"/>
+      <c r="C19" s="244"/>
+      <c r="D19" s="245"/>
       <c r="E19" s="88" t="s">
         <v>590</v>
       </c>
@@ -22378,15 +22426,15 @@
       <c r="G19" s="89">
         <v>63.7</v>
       </c>
-      <c r="H19" s="239"/>
-      <c r="I19" s="240"/>
-      <c r="J19" s="240"/>
+      <c r="H19" s="242"/>
+      <c r="I19" s="243"/>
+      <c r="J19" s="243"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="241"/>
-      <c r="B20" s="241"/>
-      <c r="C20" s="241"/>
-      <c r="D20" s="242"/>
+      <c r="A20" s="244"/>
+      <c r="B20" s="244"/>
+      <c r="C20" s="244"/>
+      <c r="D20" s="245"/>
       <c r="E20" s="89" t="s">
         <v>466</v>
       </c>
@@ -22396,15 +22444,15 @@
       <c r="G20" s="89">
         <v>64.3</v>
       </c>
-      <c r="H20" s="239"/>
-      <c r="I20" s="240"/>
-      <c r="J20" s="240"/>
+      <c r="H20" s="242"/>
+      <c r="I20" s="243"/>
+      <c r="J20" s="243"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="241"/>
-      <c r="B21" s="241"/>
-      <c r="C21" s="241"/>
-      <c r="D21" s="242"/>
+      <c r="A21" s="244"/>
+      <c r="B21" s="244"/>
+      <c r="C21" s="244"/>
+      <c r="D21" s="245"/>
       <c r="F21" s="88" t="s">
         <v>396</v>
       </c>
@@ -22412,9 +22460,9 @@
         <f>SUM(G6:G20)</f>
         <v>955.5</v>
       </c>
-      <c r="H21" s="239"/>
-      <c r="I21" s="240"/>
-      <c r="J21" s="240"/>
+      <c r="H21" s="242"/>
+      <c r="I21" s="243"/>
+      <c r="J21" s="243"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -22454,32 +22502,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="214" t="s">
+      <c r="B2" s="217" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="214"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="207" t="s">
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="210" t="s">
         <v>391</v>
       </c>
-      <c r="G2" s="218"/>
+      <c r="G2" s="221"/>
       <c r="H2" s="16" t="s">
         <v>392</v>
       </c>
@@ -22491,16 +22539,16 @@
       <c r="A3" s="75">
         <v>1</v>
       </c>
-      <c r="B3" s="212" t="s">
+      <c r="B3" s="215" t="s">
         <v>597</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="219" t="s">
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="222" t="s">
         <v>668</v>
       </c>
-      <c r="G3" s="220"/>
+      <c r="G3" s="223"/>
       <c r="H3" s="75" t="s">
         <v>394</v>
       </c>
@@ -22510,15 +22558,15 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="195"/>
-      <c r="B4" s="195"/>
-      <c r="C4" s="195"/>
-      <c r="D4" s="195"/>
-      <c r="E4" s="195"/>
-      <c r="F4" s="195"/>
-      <c r="G4" s="195"/>
-      <c r="H4" s="195"/>
-      <c r="I4" s="195"/>
+      <c r="A4" s="198"/>
+      <c r="B4" s="198"/>
+      <c r="C4" s="198"/>
+      <c r="D4" s="198"/>
+      <c r="E4" s="198"/>
+      <c r="F4" s="198"/>
+      <c r="G4" s="198"/>
+      <c r="H4" s="198"/>
+      <c r="I4" s="198"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="87" t="s">
@@ -22530,7 +22578,7 @@
       <c r="C5" s="87" t="s">
         <v>591</v>
       </c>
-      <c r="D5" s="239"/>
+      <c r="D5" s="242"/>
       <c r="E5" s="87" t="s">
         <v>593</v>
       </c>
@@ -22540,8 +22588,8 @@
       <c r="G5" s="87" t="s">
         <v>591</v>
       </c>
-      <c r="H5" s="196"/>
-      <c r="I5" s="196"/>
+      <c r="H5" s="199"/>
+      <c r="I5" s="199"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="88" t="s">
@@ -22553,7 +22601,7 @@
       <c r="C6" s="98">
         <v>16.8</v>
       </c>
-      <c r="D6" s="239"/>
+      <c r="D6" s="242"/>
       <c r="E6" s="89" t="s">
         <v>574</v>
       </c>
@@ -22563,8 +22611,8 @@
       <c r="G6" s="99">
         <v>79.7</v>
       </c>
-      <c r="H6" s="196"/>
-      <c r="I6" s="196"/>
+      <c r="H6" s="199"/>
+      <c r="I6" s="199"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="89" t="s">
@@ -22576,7 +22624,7 @@
       <c r="C7" s="98">
         <v>41.8</v>
       </c>
-      <c r="D7" s="239"/>
+      <c r="D7" s="242"/>
       <c r="E7" s="88" t="s">
         <v>575</v>
       </c>
@@ -22586,8 +22634,8 @@
       <c r="G7" s="99">
         <v>27</v>
       </c>
-      <c r="H7" s="196"/>
-      <c r="I7" s="196"/>
+      <c r="H7" s="199"/>
+      <c r="I7" s="199"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="88" t="s">
@@ -22599,7 +22647,7 @@
       <c r="C8" s="98">
         <v>60.8</v>
       </c>
-      <c r="D8" s="239"/>
+      <c r="D8" s="242"/>
       <c r="E8" s="89" t="s">
         <v>576</v>
       </c>
@@ -22609,8 +22657,8 @@
       <c r="G8" s="99">
         <v>28</v>
       </c>
-      <c r="H8" s="196"/>
-      <c r="I8" s="196"/>
+      <c r="H8" s="199"/>
+      <c r="I8" s="199"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
@@ -22622,7 +22670,7 @@
       <c r="C9" s="99">
         <v>22</v>
       </c>
-      <c r="D9" s="239"/>
+      <c r="D9" s="242"/>
       <c r="E9" s="88" t="s">
         <v>577</v>
       </c>
@@ -22632,8 +22680,8 @@
       <c r="G9" s="99">
         <v>14</v>
       </c>
-      <c r="H9" s="196"/>
-      <c r="I9" s="196"/>
+      <c r="H9" s="199"/>
+      <c r="I9" s="199"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="88" t="s">
@@ -22645,7 +22693,7 @@
       <c r="C10" s="89">
         <v>63</v>
       </c>
-      <c r="D10" s="239"/>
+      <c r="D10" s="242"/>
       <c r="E10" s="89" t="s">
         <v>578</v>
       </c>
@@ -22655,8 +22703,8 @@
       <c r="G10" s="99">
         <v>19.100000000000001</v>
       </c>
-      <c r="H10" s="196"/>
-      <c r="I10" s="196"/>
+      <c r="H10" s="199"/>
+      <c r="I10" s="199"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="89" t="s">
@@ -22668,7 +22716,7 @@
       <c r="C11" s="89">
         <v>64.3</v>
       </c>
-      <c r="D11" s="239"/>
+      <c r="D11" s="242"/>
       <c r="E11" s="88" t="s">
         <v>579</v>
       </c>
@@ -22678,8 +22726,8 @@
       <c r="G11" s="99">
         <v>201.1</v>
       </c>
-      <c r="H11" s="196"/>
-      <c r="I11" s="196"/>
+      <c r="H11" s="199"/>
+      <c r="I11" s="199"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="88" t="s">
@@ -22691,7 +22739,7 @@
       <c r="C12" s="89">
         <v>64.400000000000006</v>
       </c>
-      <c r="D12" s="239"/>
+      <c r="D12" s="242"/>
       <c r="E12" s="89" t="s">
         <v>580</v>
       </c>
@@ -22701,8 +22749,8 @@
       <c r="G12" s="99">
         <v>115.4</v>
       </c>
-      <c r="H12" s="196"/>
-      <c r="I12" s="196"/>
+      <c r="H12" s="199"/>
+      <c r="I12" s="199"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="89" t="s">
@@ -22714,7 +22762,7 @@
       <c r="C13" s="89">
         <v>131.19999999999999</v>
       </c>
-      <c r="D13" s="239"/>
+      <c r="D13" s="242"/>
       <c r="E13" s="88" t="s">
         <v>581</v>
       </c>
@@ -22724,8 +22772,8 @@
       <c r="G13" s="99">
         <v>76.2</v>
       </c>
-      <c r="H13" s="196"/>
-      <c r="I13" s="196"/>
+      <c r="H13" s="199"/>
+      <c r="I13" s="199"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="88" t="s">
@@ -22737,7 +22785,7 @@
       <c r="C14" s="89">
         <v>22.1</v>
       </c>
-      <c r="D14" s="239"/>
+      <c r="D14" s="242"/>
       <c r="E14" s="89" t="s">
         <v>582</v>
       </c>
@@ -22747,8 +22795,8 @@
       <c r="G14" s="99">
         <v>245.9</v>
       </c>
-      <c r="H14" s="196"/>
-      <c r="I14" s="196"/>
+      <c r="H14" s="199"/>
+      <c r="I14" s="199"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="89" t="s">
@@ -22760,7 +22808,7 @@
       <c r="C15" s="89">
         <v>28.7</v>
       </c>
-      <c r="D15" s="239"/>
+      <c r="D15" s="242"/>
       <c r="E15" s="88" t="s">
         <v>583</v>
       </c>
@@ -22770,8 +22818,8 @@
       <c r="G15" s="99">
         <v>13.3</v>
       </c>
-      <c r="H15" s="196"/>
-      <c r="I15" s="196"/>
+      <c r="H15" s="199"/>
+      <c r="I15" s="199"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="89" t="s">
@@ -22783,7 +22831,7 @@
       <c r="C16" s="89">
         <v>7</v>
       </c>
-      <c r="D16" s="239"/>
+      <c r="D16" s="242"/>
       <c r="E16" s="89" t="s">
         <v>584</v>
       </c>
@@ -22793,8 +22841,8 @@
       <c r="G16" s="99">
         <v>114.5</v>
       </c>
-      <c r="H16" s="196"/>
-      <c r="I16" s="196"/>
+      <c r="H16" s="199"/>
+      <c r="I16" s="199"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="89" t="s">
@@ -22806,7 +22854,7 @@
       <c r="C17" s="89">
         <v>6.2</v>
       </c>
-      <c r="D17" s="239"/>
+      <c r="D17" s="242"/>
       <c r="E17" s="88" t="s">
         <v>585</v>
       </c>
@@ -22816,8 +22864,8 @@
       <c r="G17" s="99">
         <v>113.1</v>
       </c>
-      <c r="H17" s="196"/>
-      <c r="I17" s="196"/>
+      <c r="H17" s="199"/>
+      <c r="I17" s="199"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="88" t="s">
@@ -22829,7 +22877,7 @@
       <c r="C18" s="89">
         <v>6.9</v>
       </c>
-      <c r="D18" s="239"/>
+      <c r="D18" s="242"/>
       <c r="E18" s="89" t="s">
         <v>586</v>
       </c>
@@ -22839,8 +22887,8 @@
       <c r="G18" s="99">
         <v>21.8</v>
       </c>
-      <c r="H18" s="196"/>
-      <c r="I18" s="196"/>
+      <c r="H18" s="199"/>
+      <c r="I18" s="199"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="89" t="s">
@@ -22852,7 +22900,7 @@
       <c r="C19" s="89">
         <v>37.1</v>
       </c>
-      <c r="D19" s="239"/>
+      <c r="D19" s="242"/>
       <c r="E19" s="88" t="s">
         <v>587</v>
       </c>
@@ -22862,8 +22910,8 @@
       <c r="G19" s="99">
         <v>87.5</v>
       </c>
-      <c r="H19" s="196"/>
-      <c r="I19" s="196"/>
+      <c r="H19" s="199"/>
+      <c r="I19" s="199"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="88" t="s">
@@ -22875,7 +22923,7 @@
       <c r="C20" s="89">
         <v>60.7</v>
       </c>
-      <c r="D20" s="239"/>
+      <c r="D20" s="242"/>
       <c r="E20" s="112"/>
       <c r="F20" s="112" t="s">
         <v>474</v>
@@ -22884,8 +22932,8 @@
         <f>SUM(G6:G19)</f>
         <v>1156.5999999999999</v>
       </c>
-      <c r="H20" s="196"/>
-      <c r="I20" s="196"/>
+      <c r="H20" s="199"/>
+      <c r="I20" s="199"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="75"/>
@@ -22896,12 +22944,12 @@
         <f>SUM(C6:C20)</f>
         <v>633.00000000000011</v>
       </c>
-      <c r="D21" s="239"/>
-      <c r="E21" s="244"/>
-      <c r="F21" s="244"/>
-      <c r="G21" s="244"/>
-      <c r="H21" s="196"/>
-      <c r="I21" s="196"/>
+      <c r="D21" s="242"/>
+      <c r="E21" s="247"/>
+      <c r="F21" s="247"/>
+      <c r="G21" s="247"/>
+      <c r="H21" s="199"/>
+      <c r="I21" s="199"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -22942,34 +22990,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
+      <c r="J1" s="187"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="214" t="s">
+      <c r="B2" s="217" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="214"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="207" t="s">
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="210" t="s">
         <v>391</v>
       </c>
-      <c r="G2" s="218"/>
-      <c r="H2" s="208"/>
+      <c r="G2" s="221"/>
+      <c r="H2" s="211"/>
       <c r="I2" s="16" t="s">
         <v>392</v>
       </c>
@@ -22981,17 +23029,17 @@
       <c r="A3" s="75">
         <v>1</v>
       </c>
-      <c r="B3" s="212" t="s">
+      <c r="B3" s="215" t="s">
         <v>597</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="219" t="s">
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="222" t="s">
         <v>670</v>
       </c>
-      <c r="G3" s="220"/>
-      <c r="H3" s="243"/>
+      <c r="G3" s="223"/>
+      <c r="H3" s="246"/>
       <c r="I3" s="75" t="s">
         <v>394</v>
       </c>
@@ -23001,16 +23049,16 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="195"/>
-      <c r="B4" s="195"/>
-      <c r="C4" s="195"/>
-      <c r="D4" s="195"/>
-      <c r="E4" s="195"/>
-      <c r="F4" s="195"/>
-      <c r="G4" s="195"/>
-      <c r="H4" s="195"/>
-      <c r="I4" s="195"/>
-      <c r="J4" s="195"/>
+      <c r="A4" s="198"/>
+      <c r="B4" s="198"/>
+      <c r="C4" s="198"/>
+      <c r="D4" s="198"/>
+      <c r="E4" s="198"/>
+      <c r="F4" s="198"/>
+      <c r="G4" s="198"/>
+      <c r="H4" s="198"/>
+      <c r="I4" s="198"/>
+      <c r="J4" s="198"/>
     </row>
     <row r="5" spans="1:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="67" t="s">
@@ -23022,13 +23070,13 @@
       <c r="C5" s="67" t="s">
         <v>477</v>
       </c>
-      <c r="D5" s="245"/>
-      <c r="E5" s="196"/>
-      <c r="F5" s="196"/>
-      <c r="G5" s="196"/>
-      <c r="H5" s="196"/>
-      <c r="I5" s="196"/>
-      <c r="J5" s="196"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="199"/>
+      <c r="F5" s="199"/>
+      <c r="G5" s="199"/>
+      <c r="H5" s="199"/>
+      <c r="I5" s="199"/>
+      <c r="J5" s="199"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="88" t="s">
@@ -23037,16 +23085,16 @@
       <c r="B6" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="246" t="s">
+      <c r="C6" s="249" t="s">
         <v>592</v>
       </c>
-      <c r="D6" s="245"/>
-      <c r="E6" s="196"/>
-      <c r="F6" s="196"/>
-      <c r="G6" s="196"/>
-      <c r="H6" s="196"/>
-      <c r="I6" s="196"/>
-      <c r="J6" s="196"/>
+      <c r="D6" s="248"/>
+      <c r="E6" s="199"/>
+      <c r="F6" s="199"/>
+      <c r="G6" s="199"/>
+      <c r="H6" s="199"/>
+      <c r="I6" s="199"/>
+      <c r="J6" s="199"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="89" t="s">
@@ -23055,14 +23103,14 @@
       <c r="B7" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="246"/>
-      <c r="D7" s="245"/>
-      <c r="E7" s="196"/>
-      <c r="F7" s="196"/>
-      <c r="G7" s="196"/>
-      <c r="H7" s="196"/>
-      <c r="I7" s="196"/>
-      <c r="J7" s="196"/>
+      <c r="C7" s="249"/>
+      <c r="D7" s="248"/>
+      <c r="E7" s="199"/>
+      <c r="F7" s="199"/>
+      <c r="G7" s="199"/>
+      <c r="H7" s="199"/>
+      <c r="I7" s="199"/>
+      <c r="J7" s="199"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="12"/>
@@ -23073,13 +23121,13 @@
         <f>C6</f>
         <v>431,9</v>
       </c>
-      <c r="D8" s="245"/>
-      <c r="E8" s="196"/>
-      <c r="F8" s="196"/>
-      <c r="G8" s="196"/>
-      <c r="H8" s="196"/>
-      <c r="I8" s="196"/>
-      <c r="J8" s="196"/>
+      <c r="D8" s="248"/>
+      <c r="E8" s="199"/>
+      <c r="F8" s="199"/>
+      <c r="G8" s="199"/>
+      <c r="H8" s="199"/>
+      <c r="I8" s="199"/>
+      <c r="J8" s="199"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -23119,34 +23167,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
+      <c r="J1" s="187"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="214" t="s">
+      <c r="B2" s="217" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="214"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="207" t="s">
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="210" t="s">
         <v>391</v>
       </c>
-      <c r="G2" s="218"/>
-      <c r="H2" s="208"/>
+      <c r="G2" s="221"/>
+      <c r="H2" s="211"/>
       <c r="I2" s="16" t="s">
         <v>392</v>
       </c>
@@ -23158,17 +23206,17 @@
       <c r="A3" s="75">
         <v>1</v>
       </c>
-      <c r="B3" s="212" t="s">
+      <c r="B3" s="215" t="s">
         <v>597</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="219" t="s">
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="222" t="s">
         <v>669</v>
       </c>
-      <c r="G3" s="220"/>
-      <c r="H3" s="243"/>
+      <c r="G3" s="223"/>
+      <c r="H3" s="246"/>
       <c r="I3" s="75" t="s">
         <v>394</v>
       </c>
@@ -23178,16 +23226,16 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="195"/>
-      <c r="B4" s="195"/>
-      <c r="C4" s="195"/>
-      <c r="D4" s="195"/>
-      <c r="E4" s="195"/>
-      <c r="F4" s="195"/>
-      <c r="G4" s="195"/>
-      <c r="H4" s="195"/>
-      <c r="I4" s="195"/>
-      <c r="J4" s="195"/>
+      <c r="A4" s="198"/>
+      <c r="B4" s="198"/>
+      <c r="C4" s="198"/>
+      <c r="D4" s="198"/>
+      <c r="E4" s="198"/>
+      <c r="F4" s="198"/>
+      <c r="G4" s="198"/>
+      <c r="H4" s="198"/>
+      <c r="I4" s="198"/>
+      <c r="J4" s="198"/>
     </row>
     <row r="5" spans="1:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="67" t="s">
@@ -23199,13 +23247,13 @@
       <c r="C5" s="67" t="s">
         <v>477</v>
       </c>
-      <c r="D5" s="245"/>
-      <c r="E5" s="196"/>
-      <c r="F5" s="196"/>
-      <c r="G5" s="196"/>
-      <c r="H5" s="196"/>
-      <c r="I5" s="196"/>
-      <c r="J5" s="196"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="199"/>
+      <c r="F5" s="199"/>
+      <c r="G5" s="199"/>
+      <c r="H5" s="199"/>
+      <c r="I5" s="199"/>
+      <c r="J5" s="199"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="93" t="s">
@@ -23214,16 +23262,16 @@
       <c r="B6" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="247">
+      <c r="C6" s="250">
         <v>248.1</v>
       </c>
-      <c r="D6" s="245"/>
-      <c r="E6" s="196"/>
-      <c r="F6" s="196"/>
-      <c r="G6" s="196"/>
-      <c r="H6" s="196"/>
-      <c r="I6" s="196"/>
-      <c r="J6" s="196"/>
+      <c r="D6" s="248"/>
+      <c r="E6" s="199"/>
+      <c r="F6" s="199"/>
+      <c r="G6" s="199"/>
+      <c r="H6" s="199"/>
+      <c r="I6" s="199"/>
+      <c r="J6" s="199"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="95" t="s">
@@ -23232,14 +23280,14 @@
       <c r="B7" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="248"/>
-      <c r="D7" s="245"/>
-      <c r="E7" s="196"/>
-      <c r="F7" s="196"/>
-      <c r="G7" s="196"/>
-      <c r="H7" s="196"/>
-      <c r="I7" s="196"/>
-      <c r="J7" s="196"/>
+      <c r="C7" s="251"/>
+      <c r="D7" s="248"/>
+      <c r="E7" s="199"/>
+      <c r="F7" s="199"/>
+      <c r="G7" s="199"/>
+      <c r="H7" s="199"/>
+      <c r="I7" s="199"/>
+      <c r="J7" s="199"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="93" t="s">
@@ -23248,14 +23296,14 @@
       <c r="B8" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="248"/>
-      <c r="D8" s="245"/>
-      <c r="E8" s="196"/>
-      <c r="F8" s="196"/>
-      <c r="G8" s="196"/>
-      <c r="H8" s="196"/>
-      <c r="I8" s="196"/>
-      <c r="J8" s="196"/>
+      <c r="C8" s="251"/>
+      <c r="D8" s="248"/>
+      <c r="E8" s="199"/>
+      <c r="F8" s="199"/>
+      <c r="G8" s="199"/>
+      <c r="H8" s="199"/>
+      <c r="I8" s="199"/>
+      <c r="J8" s="199"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="95" t="s">
@@ -23264,14 +23312,14 @@
       <c r="B9" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="248"/>
-      <c r="D9" s="245"/>
-      <c r="E9" s="196"/>
-      <c r="F9" s="196"/>
-      <c r="G9" s="196"/>
-      <c r="H9" s="196"/>
-      <c r="I9" s="196"/>
-      <c r="J9" s="196"/>
+      <c r="C9" s="251"/>
+      <c r="D9" s="248"/>
+      <c r="E9" s="199"/>
+      <c r="F9" s="199"/>
+      <c r="G9" s="199"/>
+      <c r="H9" s="199"/>
+      <c r="I9" s="199"/>
+      <c r="J9" s="199"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="93" t="s">
@@ -23280,14 +23328,14 @@
       <c r="B10" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="248"/>
-      <c r="D10" s="245"/>
-      <c r="E10" s="196"/>
-      <c r="F10" s="196"/>
-      <c r="G10" s="196"/>
-      <c r="H10" s="196"/>
-      <c r="I10" s="196"/>
-      <c r="J10" s="196"/>
+      <c r="C10" s="251"/>
+      <c r="D10" s="248"/>
+      <c r="E10" s="199"/>
+      <c r="F10" s="199"/>
+      <c r="G10" s="199"/>
+      <c r="H10" s="199"/>
+      <c r="I10" s="199"/>
+      <c r="J10" s="199"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="95" t="s">
@@ -23296,14 +23344,14 @@
       <c r="B11" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="249"/>
-      <c r="D11" s="245"/>
-      <c r="E11" s="196"/>
-      <c r="F11" s="196"/>
-      <c r="G11" s="196"/>
-      <c r="H11" s="196"/>
-      <c r="I11" s="196"/>
-      <c r="J11" s="196"/>
+      <c r="C11" s="252"/>
+      <c r="D11" s="248"/>
+      <c r="E11" s="199"/>
+      <c r="F11" s="199"/>
+      <c r="G11" s="199"/>
+      <c r="H11" s="199"/>
+      <c r="I11" s="199"/>
+      <c r="J11" s="199"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="93" t="s">
@@ -23315,13 +23363,13 @@
       <c r="C12" s="97">
         <v>19.8</v>
       </c>
-      <c r="D12" s="245"/>
-      <c r="E12" s="196"/>
-      <c r="F12" s="196"/>
-      <c r="G12" s="196"/>
-      <c r="H12" s="196"/>
-      <c r="I12" s="196"/>
-      <c r="J12" s="196"/>
+      <c r="D12" s="248"/>
+      <c r="E12" s="199"/>
+      <c r="F12" s="199"/>
+      <c r="G12" s="199"/>
+      <c r="H12" s="199"/>
+      <c r="I12" s="199"/>
+      <c r="J12" s="199"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
@@ -23332,13 +23380,13 @@
         <f>SUM(C6:C12)</f>
         <v>267.89999999999998</v>
       </c>
-      <c r="D13" s="245"/>
-      <c r="E13" s="196"/>
-      <c r="F13" s="196"/>
-      <c r="G13" s="196"/>
-      <c r="H13" s="196"/>
-      <c r="I13" s="196"/>
-      <c r="J13" s="196"/>
+      <c r="D13" s="248"/>
+      <c r="E13" s="199"/>
+      <c r="F13" s="199"/>
+      <c r="G13" s="199"/>
+      <c r="H13" s="199"/>
+      <c r="I13" s="199"/>
+      <c r="J13" s="199"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -23370,13 +23418,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="250" t="s">
+      <c r="A1" s="253" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="251"/>
-      <c r="C1" s="251"/>
-      <c r="D1" s="251"/>
-      <c r="E1" s="252"/>
+      <c r="B1" s="254"/>
+      <c r="C1" s="254"/>
+      <c r="D1" s="254"/>
+      <c r="E1" s="255"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
@@ -23850,75 +23898,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="254" t="s">
+      <c r="A1" s="256" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="254"/>
-      <c r="C1" s="254"/>
-      <c r="D1" s="254"/>
-      <c r="E1" s="254"/>
-      <c r="F1" s="254"/>
-      <c r="G1" s="254"/>
-      <c r="H1" s="254"/>
-      <c r="I1" s="254"/>
-      <c r="J1" s="253"/>
-      <c r="K1" s="253"/>
+      <c r="B1" s="256"/>
+      <c r="C1" s="256"/>
+      <c r="D1" s="256"/>
+      <c r="E1" s="256"/>
+      <c r="F1" s="256"/>
+      <c r="G1" s="256"/>
+      <c r="H1" s="256"/>
+      <c r="I1" s="256"/>
+      <c r="J1" s="259"/>
+      <c r="K1" s="259"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="40" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="257" t="s">
+      <c r="B2" s="260" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="257"/>
-      <c r="D2" s="257"/>
-      <c r="E2" s="257"/>
-      <c r="F2" s="257"/>
+      <c r="C2" s="260"/>
+      <c r="D2" s="260"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="260"/>
       <c r="G2" s="41" t="s">
         <v>392</v>
       </c>
-      <c r="H2" s="256" t="s">
+      <c r="H2" s="258" t="s">
         <v>393</v>
       </c>
-      <c r="I2" s="256"/>
-      <c r="J2" s="253"/>
-      <c r="K2" s="253"/>
+      <c r="I2" s="258"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
     </row>
     <row r="3" spans="1:11" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="49">
         <v>1</v>
       </c>
-      <c r="B3" s="258" t="s">
+      <c r="B3" s="261" t="s">
         <v>479</v>
       </c>
-      <c r="C3" s="258"/>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
+      <c r="C3" s="261"/>
+      <c r="D3" s="261"/>
+      <c r="E3" s="261"/>
+      <c r="F3" s="261"/>
       <c r="G3" s="49" t="s">
         <v>394</v>
       </c>
-      <c r="H3" s="255">
+      <c r="H3" s="257">
         <f>C21+G30+K31</f>
         <v>4099.5</v>
       </c>
-      <c r="I3" s="255"/>
-      <c r="J3" s="253"/>
-      <c r="K3" s="253"/>
+      <c r="I3" s="257"/>
+      <c r="J3" s="259"/>
+      <c r="K3" s="259"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="253"/>
-      <c r="B4" s="253"/>
-      <c r="C4" s="253"/>
-      <c r="D4" s="253"/>
-      <c r="E4" s="253"/>
-      <c r="F4" s="253"/>
-      <c r="G4" s="253"/>
-      <c r="H4" s="253"/>
-      <c r="I4" s="253"/>
-      <c r="J4" s="253"/>
-      <c r="K4" s="253"/>
+      <c r="A4" s="259"/>
+      <c r="B4" s="259"/>
+      <c r="C4" s="259"/>
+      <c r="D4" s="259"/>
+      <c r="E4" s="259"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
+      <c r="H4" s="259"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="259"/>
+      <c r="K4" s="259"/>
     </row>
     <row r="5" spans="1:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="39" t="s">
@@ -23930,7 +23978,7 @@
       <c r="C5" s="39" t="s">
         <v>477</v>
       </c>
-      <c r="D5" s="253"/>
+      <c r="D5" s="259"/>
       <c r="E5" s="39" t="s">
         <v>478</v>
       </c>
@@ -23940,7 +23988,7 @@
       <c r="G5" s="39" t="s">
         <v>477</v>
       </c>
-      <c r="H5" s="253"/>
+      <c r="H5" s="259"/>
       <c r="I5" s="39" t="s">
         <v>478</v>
       </c>
@@ -23961,7 +24009,7 @@
       <c r="C6" s="44">
         <v>22.1</v>
       </c>
-      <c r="D6" s="253"/>
+      <c r="D6" s="259"/>
       <c r="E6" s="45">
         <v>2.0099999999999998</v>
       </c>
@@ -23971,7 +24019,7 @@
       <c r="G6" s="46">
         <v>62.6</v>
       </c>
-      <c r="H6" s="253"/>
+      <c r="H6" s="259"/>
       <c r="I6" s="45">
         <v>3.01</v>
       </c>
@@ -23992,7 +24040,7 @@
       <c r="C7" s="46">
         <v>61.9</v>
       </c>
-      <c r="D7" s="253"/>
+      <c r="D7" s="259"/>
       <c r="E7" s="43">
         <v>2.02</v>
       </c>
@@ -24002,7 +24050,7 @@
       <c r="G7" s="44">
         <v>89</v>
       </c>
-      <c r="H7" s="253"/>
+      <c r="H7" s="259"/>
       <c r="I7" s="43">
         <v>3.02</v>
       </c>
@@ -24023,7 +24071,7 @@
       <c r="C8" s="44">
         <v>63.3</v>
       </c>
-      <c r="D8" s="253"/>
+      <c r="D8" s="259"/>
       <c r="E8" s="45">
         <v>2.0299999999999998</v>
       </c>
@@ -24033,7 +24081,7 @@
       <c r="G8" s="46">
         <v>39.4</v>
       </c>
-      <c r="H8" s="253"/>
+      <c r="H8" s="259"/>
       <c r="I8" s="45">
         <v>3.03</v>
       </c>
@@ -24054,7 +24102,7 @@
       <c r="C9" s="46">
         <v>63.4</v>
       </c>
-      <c r="D9" s="253"/>
+      <c r="D9" s="259"/>
       <c r="E9" s="43">
         <v>2.04</v>
       </c>
@@ -24064,7 +24112,7 @@
       <c r="G9" s="44">
         <v>63</v>
       </c>
-      <c r="H9" s="253"/>
+      <c r="H9" s="259"/>
       <c r="I9" s="43">
         <v>3.04</v>
       </c>
@@ -24085,7 +24133,7 @@
       <c r="C10" s="44">
         <v>131.19999999999999</v>
       </c>
-      <c r="D10" s="253"/>
+      <c r="D10" s="259"/>
       <c r="E10" s="45">
         <v>2.0499999999999998</v>
       </c>
@@ -24095,7 +24143,7 @@
       <c r="G10" s="46">
         <v>64.400000000000006</v>
       </c>
-      <c r="H10" s="253"/>
+      <c r="H10" s="259"/>
       <c r="I10" s="45">
         <v>3.05</v>
       </c>
@@ -24116,7 +24164,7 @@
       <c r="C11" s="46">
         <v>20.7</v>
       </c>
-      <c r="D11" s="253"/>
+      <c r="D11" s="259"/>
       <c r="E11" s="43">
         <v>2.06</v>
       </c>
@@ -24126,7 +24174,7 @@
       <c r="G11" s="44">
         <v>63.3</v>
       </c>
-      <c r="H11" s="253"/>
+      <c r="H11" s="259"/>
       <c r="I11" s="43">
         <v>3.06</v>
       </c>
@@ -24147,7 +24195,7 @@
       <c r="C12" s="44">
         <v>16.8</v>
       </c>
-      <c r="D12" s="253"/>
+      <c r="D12" s="259"/>
       <c r="E12" s="45">
         <v>2.0699999999999998</v>
       </c>
@@ -24157,7 +24205,7 @@
       <c r="G12" s="46">
         <v>63.3</v>
       </c>
-      <c r="H12" s="253"/>
+      <c r="H12" s="259"/>
       <c r="I12" s="45">
         <v>3.07</v>
       </c>
@@ -24178,7 +24226,7 @@
       <c r="C13" s="46">
         <v>24</v>
       </c>
-      <c r="D13" s="253"/>
+      <c r="D13" s="259"/>
       <c r="E13" s="43">
         <v>2.08</v>
       </c>
@@ -24188,7 +24236,7 @@
       <c r="G13" s="44">
         <v>78.599999999999994</v>
       </c>
-      <c r="H13" s="253"/>
+      <c r="H13" s="259"/>
       <c r="I13" s="43">
         <v>3.08</v>
       </c>
@@ -24209,7 +24257,7 @@
       <c r="C14" s="44">
         <v>51.3</v>
       </c>
-      <c r="D14" s="253"/>
+      <c r="D14" s="259"/>
       <c r="E14" s="45">
         <v>2.12</v>
       </c>
@@ -24219,7 +24267,7 @@
       <c r="G14" s="46">
         <v>27</v>
       </c>
-      <c r="H14" s="253"/>
+      <c r="H14" s="259"/>
       <c r="I14" s="45">
         <v>3.12</v>
       </c>
@@ -24240,7 +24288,7 @@
       <c r="C15" s="46">
         <v>54.6</v>
       </c>
-      <c r="D15" s="253"/>
+      <c r="D15" s="259"/>
       <c r="E15" s="43">
         <v>2.15</v>
       </c>
@@ -24250,7 +24298,7 @@
       <c r="G15" s="44">
         <v>28</v>
       </c>
-      <c r="H15" s="253"/>
+      <c r="H15" s="259"/>
       <c r="I15" s="43">
         <v>3.13</v>
       </c>
@@ -24271,7 +24319,7 @@
       <c r="C16" s="44">
         <v>18.5</v>
       </c>
-      <c r="D16" s="253"/>
+      <c r="D16" s="259"/>
       <c r="E16" s="45">
         <v>2.19</v>
       </c>
@@ -24281,7 +24329,7 @@
       <c r="G16" s="46">
         <v>359.3</v>
       </c>
-      <c r="H16" s="253"/>
+      <c r="H16" s="259"/>
       <c r="I16" s="45">
         <v>3.18</v>
       </c>
@@ -24302,7 +24350,7 @@
       <c r="C17" s="46">
         <v>51.2</v>
       </c>
-      <c r="D17" s="253"/>
+      <c r="D17" s="259"/>
       <c r="E17" s="43">
         <v>2.21</v>
       </c>
@@ -24312,7 +24360,7 @@
       <c r="G17" s="44">
         <v>14</v>
       </c>
-      <c r="H17" s="253"/>
+      <c r="H17" s="259"/>
       <c r="I17" s="43">
         <v>3.19</v>
       </c>
@@ -24333,7 +24381,7 @@
       <c r="C18" s="44">
         <v>55.3</v>
       </c>
-      <c r="D18" s="253"/>
+      <c r="D18" s="259"/>
       <c r="E18" s="45">
         <v>2.27</v>
       </c>
@@ -24343,7 +24391,7 @@
       <c r="G18" s="46">
         <v>19.100000000000001</v>
       </c>
-      <c r="H18" s="253"/>
+      <c r="H18" s="259"/>
       <c r="I18" s="45">
         <v>3.23</v>
       </c>
@@ -24364,7 +24412,7 @@
       <c r="C19" s="46">
         <v>41.2</v>
       </c>
-      <c r="D19" s="253"/>
+      <c r="D19" s="259"/>
       <c r="E19" s="43">
         <v>2.2799999999999998</v>
       </c>
@@ -24374,7 +24422,7 @@
       <c r="G19" s="44">
         <v>192.9</v>
       </c>
-      <c r="H19" s="253"/>
+      <c r="H19" s="259"/>
       <c r="I19" s="43">
         <v>3.25</v>
       </c>
@@ -24395,7 +24443,7 @@
       <c r="C20" s="44">
         <v>59.3</v>
       </c>
-      <c r="D20" s="253"/>
+      <c r="D20" s="259"/>
       <c r="E20" s="45">
         <v>2.2999999999999998</v>
       </c>
@@ -24405,7 +24453,7 @@
       <c r="G20" s="46">
         <v>115.5</v>
       </c>
-      <c r="H20" s="253"/>
+      <c r="H20" s="259"/>
       <c r="I20" s="45">
         <v>3.26</v>
       </c>
@@ -24424,7 +24472,7 @@
         <f>SUM(C6:C20)</f>
         <v>734.8</v>
       </c>
-      <c r="D21" s="253"/>
+      <c r="D21" s="259"/>
       <c r="E21" s="43">
         <v>2.37</v>
       </c>
@@ -24434,7 +24482,7 @@
       <c r="G21" s="44">
         <v>21.6</v>
       </c>
-      <c r="H21" s="253"/>
+      <c r="H21" s="259"/>
       <c r="I21" s="43">
         <v>3.28</v>
       </c>
@@ -24446,10 +24494,10 @@
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="253"/>
-      <c r="B22" s="253"/>
-      <c r="C22" s="253"/>
-      <c r="D22" s="253"/>
+      <c r="A22" s="259"/>
+      <c r="B22" s="259"/>
+      <c r="C22" s="259"/>
+      <c r="D22" s="259"/>
       <c r="E22" s="45">
         <v>2.4</v>
       </c>
@@ -24459,7 +24507,7 @@
       <c r="G22" s="46">
         <v>51.3</v>
       </c>
-      <c r="H22" s="253"/>
+      <c r="H22" s="259"/>
       <c r="I22" s="45">
         <v>3.29</v>
       </c>
@@ -24471,10 +24519,10 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="253"/>
-      <c r="B23" s="253"/>
-      <c r="C23" s="253"/>
-      <c r="D23" s="253"/>
+      <c r="A23" s="259"/>
+      <c r="B23" s="259"/>
+      <c r="C23" s="259"/>
+      <c r="D23" s="259"/>
       <c r="E23" s="43">
         <v>2.41</v>
       </c>
@@ -24484,7 +24532,7 @@
       <c r="G23" s="44">
         <v>56.6</v>
       </c>
-      <c r="H23" s="253"/>
+      <c r="H23" s="259"/>
       <c r="I23" s="43">
         <v>3.3</v>
       </c>
@@ -24496,10 +24544,10 @@
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="253"/>
-      <c r="B24" s="253"/>
-      <c r="C24" s="253"/>
-      <c r="D24" s="253"/>
+      <c r="A24" s="259"/>
+      <c r="B24" s="259"/>
+      <c r="C24" s="259"/>
+      <c r="D24" s="259"/>
       <c r="E24" s="45">
         <v>2.42</v>
       </c>
@@ -24509,7 +24557,7 @@
       <c r="G24" s="46">
         <v>21.5</v>
       </c>
-      <c r="H24" s="253"/>
+      <c r="H24" s="259"/>
       <c r="I24" s="45">
         <v>3.33</v>
       </c>
@@ -24521,10 +24569,10 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="253"/>
-      <c r="B25" s="253"/>
-      <c r="C25" s="253"/>
-      <c r="D25" s="253"/>
+      <c r="A25" s="259"/>
+      <c r="B25" s="259"/>
+      <c r="C25" s="259"/>
+      <c r="D25" s="259"/>
       <c r="E25" s="43">
         <v>2.44</v>
       </c>
@@ -24534,7 +24582,7 @@
       <c r="G25" s="44">
         <v>51.3</v>
       </c>
-      <c r="H25" s="253"/>
+      <c r="H25" s="259"/>
       <c r="I25" s="43">
         <v>3.34</v>
       </c>
@@ -24546,10 +24594,10 @@
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="253"/>
-      <c r="B26" s="253"/>
-      <c r="C26" s="253"/>
-      <c r="D26" s="253"/>
+      <c r="A26" s="259"/>
+      <c r="B26" s="259"/>
+      <c r="C26" s="259"/>
+      <c r="D26" s="259"/>
       <c r="E26" s="45">
         <v>2.4500000000000002</v>
       </c>
@@ -24559,7 +24607,7 @@
       <c r="G26" s="46">
         <v>56.3</v>
       </c>
-      <c r="H26" s="253"/>
+      <c r="H26" s="259"/>
       <c r="I26" s="45">
         <v>3.35</v>
       </c>
@@ -24571,10 +24619,10 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="253"/>
-      <c r="B27" s="253"/>
-      <c r="C27" s="253"/>
-      <c r="D27" s="253"/>
+      <c r="A27" s="259"/>
+      <c r="B27" s="259"/>
+      <c r="C27" s="259"/>
+      <c r="D27" s="259"/>
       <c r="E27" s="43">
         <v>2.4700000000000002</v>
       </c>
@@ -24584,7 +24632,7 @@
       <c r="G27" s="44">
         <v>75.599999999999994</v>
       </c>
-      <c r="H27" s="253"/>
+      <c r="H27" s="259"/>
       <c r="I27" s="43">
         <v>3.41</v>
       </c>
@@ -24596,10 +24644,10 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="253"/>
-      <c r="B28" s="253"/>
-      <c r="C28" s="253"/>
-      <c r="D28" s="253"/>
+      <c r="A28" s="259"/>
+      <c r="B28" s="259"/>
+      <c r="C28" s="259"/>
+      <c r="D28" s="259"/>
       <c r="E28" s="43">
         <v>2.4900000000000002</v>
       </c>
@@ -24609,7 +24657,7 @@
       <c r="G28" s="44">
         <v>75.2</v>
       </c>
-      <c r="H28" s="253"/>
+      <c r="H28" s="259"/>
       <c r="I28" s="45">
         <v>3.42</v>
       </c>
@@ -24621,10 +24669,10 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="253"/>
-      <c r="B29" s="253"/>
-      <c r="C29" s="253"/>
-      <c r="D29" s="253"/>
+      <c r="A29" s="259"/>
+      <c r="B29" s="259"/>
+      <c r="C29" s="259"/>
+      <c r="D29" s="259"/>
       <c r="E29" s="43">
         <v>2.58</v>
       </c>
@@ -24634,7 +24682,7 @@
       <c r="G29" s="44">
         <v>76.2</v>
       </c>
-      <c r="H29" s="253"/>
+      <c r="H29" s="259"/>
       <c r="I29" s="43">
         <v>3.44</v>
       </c>
@@ -24646,10 +24694,10 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="253"/>
-      <c r="B30" s="253"/>
-      <c r="C30" s="253"/>
-      <c r="D30" s="253"/>
+      <c r="A30" s="259"/>
+      <c r="B30" s="259"/>
+      <c r="C30" s="259"/>
+      <c r="D30" s="259"/>
       <c r="F30" s="50" t="s">
         <v>474</v>
       </c>
@@ -24657,7 +24705,7 @@
         <f>SUM(G6:G29)</f>
         <v>1764.9999999999998</v>
       </c>
-      <c r="H30" s="253"/>
+      <c r="H30" s="259"/>
       <c r="I30" s="47">
         <v>3.45</v>
       </c>
@@ -24669,14 +24717,14 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="253"/>
-      <c r="B31" s="253"/>
-      <c r="C31" s="253"/>
-      <c r="D31" s="253"/>
-      <c r="E31" s="253"/>
-      <c r="F31" s="253"/>
-      <c r="G31" s="253"/>
-      <c r="H31" s="253"/>
+      <c r="A31" s="259"/>
+      <c r="B31" s="259"/>
+      <c r="C31" s="259"/>
+      <c r="D31" s="259"/>
+      <c r="E31" s="259"/>
+      <c r="F31" s="259"/>
+      <c r="G31" s="259"/>
+      <c r="H31" s="259"/>
       <c r="J31" s="50" t="s">
         <v>474</v>
       </c>
@@ -24687,17 +24735,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="H5:H31"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="D5:D31"/>
+    <mergeCell ref="A22:C31"/>
+    <mergeCell ref="A4:K4"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="J1:K3"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="H5:H31"/>
-    <mergeCell ref="E31:G31"/>
-    <mergeCell ref="D5:D31"/>
-    <mergeCell ref="A22:C31"/>
-    <mergeCell ref="A4:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -24715,11 +24763,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="236" t="s">
+      <c r="A1" s="239" t="s">
         <v>395</v>
       </c>
-      <c r="B1" s="237"/>
-      <c r="C1" s="238"/>
+      <c r="B1" s="240"/>
+      <c r="C1" s="241"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
@@ -25013,32 +25061,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="214" t="s">
+      <c r="B2" s="217" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="214"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="207" t="s">
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="210" t="s">
         <v>391</v>
       </c>
-      <c r="G2" s="218"/>
+      <c r="G2" s="221"/>
       <c r="H2" s="16" t="s">
         <v>392</v>
       </c>
@@ -25050,16 +25098,16 @@
       <c r="A3" s="75">
         <v>1</v>
       </c>
-      <c r="B3" s="212" t="s">
+      <c r="B3" s="215" t="s">
         <v>676</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="219" t="s">
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="222" t="s">
         <v>677</v>
       </c>
-      <c r="G3" s="220"/>
+      <c r="G3" s="223"/>
       <c r="H3" s="75" t="s">
         <v>394</v>
       </c>
@@ -25072,16 +25120,16 @@
       <c r="A4" s="75">
         <v>2</v>
       </c>
-      <c r="B4" s="212" t="s">
+      <c r="B4" s="215" t="s">
         <v>676</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="219" t="s">
+      <c r="C4" s="215"/>
+      <c r="D4" s="215"/>
+      <c r="E4" s="215"/>
+      <c r="F4" s="222" t="s">
         <v>678</v>
       </c>
-      <c r="G4" s="220"/>
+      <c r="G4" s="223"/>
       <c r="H4" s="75" t="s">
         <v>394</v>
       </c>
@@ -25091,15 +25139,15 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="195"/>
-      <c r="B5" s="195"/>
-      <c r="C5" s="195"/>
-      <c r="D5" s="195"/>
-      <c r="E5" s="195"/>
-      <c r="F5" s="195"/>
-      <c r="G5" s="195"/>
-      <c r="H5" s="195"/>
-      <c r="I5" s="195"/>
+      <c r="A5" s="198"/>
+      <c r="B5" s="198"/>
+      <c r="C5" s="198"/>
+      <c r="D5" s="198"/>
+      <c r="E5" s="198"/>
+      <c r="F5" s="198"/>
+      <c r="G5" s="198"/>
+      <c r="H5" s="198"/>
+      <c r="I5" s="198"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="87" t="s">
@@ -25111,7 +25159,7 @@
       <c r="C6" s="103" t="s">
         <v>673</v>
       </c>
-      <c r="D6" s="242"/>
+      <c r="D6" s="245"/>
       <c r="E6" s="87" t="s">
         <v>593</v>
       </c>
@@ -25121,8 +25169,8 @@
       <c r="G6" s="87" t="s">
         <v>591</v>
       </c>
-      <c r="H6" s="196"/>
-      <c r="I6" s="196"/>
+      <c r="H6" s="199"/>
+      <c r="I6" s="199"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="104" t="s">
@@ -25134,7 +25182,7 @@
       <c r="C7" s="117">
         <v>21.89</v>
       </c>
-      <c r="D7" s="242"/>
+      <c r="D7" s="245"/>
       <c r="E7" s="106" t="s">
         <v>461</v>
       </c>
@@ -25144,8 +25192,8 @@
       <c r="G7" s="118">
         <v>62.485999999999997</v>
       </c>
-      <c r="H7" s="196"/>
-      <c r="I7" s="196"/>
+      <c r="H7" s="199"/>
+      <c r="I7" s="199"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="106" t="s">
@@ -25157,7 +25205,7 @@
       <c r="C8" s="118">
         <v>62.685000000000002</v>
       </c>
-      <c r="D8" s="242"/>
+      <c r="D8" s="245"/>
       <c r="E8" s="104" t="s">
         <v>462</v>
       </c>
@@ -25167,8 +25215,8 @@
       <c r="G8" s="117">
         <v>88.654499999999999</v>
       </c>
-      <c r="H8" s="196"/>
-      <c r="I8" s="196"/>
+      <c r="H8" s="199"/>
+      <c r="I8" s="199"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="104" t="s">
@@ -25180,7 +25228,7 @@
       <c r="C9" s="117">
         <v>63.978499999999997</v>
       </c>
-      <c r="D9" s="242"/>
+      <c r="D9" s="245"/>
       <c r="E9" s="106" t="s">
         <v>463</v>
       </c>
@@ -25190,8 +25238,8 @@
       <c r="G9" s="118">
         <v>29.551500000000001</v>
       </c>
-      <c r="H9" s="196"/>
-      <c r="I9" s="196"/>
+      <c r="H9" s="199"/>
+      <c r="I9" s="199"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="106" t="s">
@@ -25203,7 +25251,7 @@
       <c r="C10" s="118">
         <v>64.078000000000003</v>
       </c>
-      <c r="D10" s="242"/>
+      <c r="D10" s="245"/>
       <c r="E10" s="104" t="s">
         <v>464</v>
       </c>
@@ -25213,8 +25261,8 @@
       <c r="G10" s="117">
         <v>64.475999999999999</v>
       </c>
-      <c r="H10" s="196"/>
-      <c r="I10" s="196"/>
+      <c r="H10" s="199"/>
+      <c r="I10" s="199"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="104" t="s">
@@ -25226,7 +25274,7 @@
       <c r="C11" s="117">
         <v>130.9</v>
       </c>
-      <c r="D11" s="242"/>
+      <c r="D11" s="245"/>
       <c r="E11" s="106" t="s">
         <v>465</v>
       </c>
@@ -25236,8 +25284,8 @@
       <c r="G11" s="118">
         <v>63.480999999999995</v>
       </c>
-      <c r="H11" s="196"/>
-      <c r="I11" s="196"/>
+      <c r="H11" s="199"/>
+      <c r="I11" s="199"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="104" t="s">
@@ -25249,7 +25297,7 @@
       <c r="C12" s="117">
         <v>63.381500000000003</v>
       </c>
-      <c r="D12" s="242"/>
+      <c r="D12" s="245"/>
       <c r="E12" s="104" t="s">
         <v>589</v>
       </c>
@@ -25259,8 +25307,8 @@
       <c r="G12" s="117">
         <v>65.172499999999999</v>
       </c>
-      <c r="H12" s="196"/>
-      <c r="I12" s="196"/>
+      <c r="H12" s="199"/>
+      <c r="I12" s="199"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="106" t="s">
@@ -25272,7 +25320,7 @@
       <c r="C13" s="118">
         <v>89.749000000000009</v>
       </c>
-      <c r="D13" s="242"/>
+      <c r="D13" s="245"/>
       <c r="E13" s="106" t="s">
         <v>590</v>
       </c>
@@ -25282,8 +25330,8 @@
       <c r="G13" s="118">
         <v>63.381500000000003</v>
       </c>
-      <c r="H13" s="196"/>
-      <c r="I13" s="196"/>
+      <c r="H13" s="199"/>
+      <c r="I13" s="199"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="104" t="s">
@@ -25295,7 +25343,7 @@
       <c r="C14" s="117">
         <v>39.899500000000003</v>
       </c>
-      <c r="D14" s="242"/>
+      <c r="D14" s="245"/>
       <c r="E14" s="104" t="s">
         <v>466</v>
       </c>
@@ -25305,8 +25353,8 @@
       <c r="G14" s="117">
         <v>64.3</v>
       </c>
-      <c r="H14" s="196"/>
-      <c r="I14" s="196"/>
+      <c r="H14" s="199"/>
+      <c r="I14" s="199"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="106" t="s">
@@ -25318,7 +25366,7 @@
       <c r="C15" s="118">
         <v>63.68</v>
       </c>
-      <c r="D15" s="242"/>
+      <c r="D15" s="245"/>
       <c r="E15" s="104" t="s">
         <v>583</v>
       </c>
@@ -25328,8 +25376,8 @@
       <c r="G15" s="117">
         <v>13.233500000000001</v>
       </c>
-      <c r="H15" s="196"/>
-      <c r="I15" s="196"/>
+      <c r="H15" s="199"/>
+      <c r="I15" s="199"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="104" t="s">
@@ -25341,7 +25389,7 @@
       <c r="C16" s="117">
         <v>65.3</v>
       </c>
-      <c r="D16" s="242"/>
+      <c r="D16" s="245"/>
       <c r="E16" s="106" t="s">
         <v>584</v>
       </c>
@@ -25351,8 +25399,8 @@
       <c r="G16" s="118">
         <v>113.92749999999999</v>
       </c>
-      <c r="H16" s="196"/>
-      <c r="I16" s="196"/>
+      <c r="H16" s="199"/>
+      <c r="I16" s="199"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="106" t="s">
@@ -25364,7 +25412,7 @@
       <c r="C17" s="118">
         <v>63.779499999999992</v>
       </c>
-      <c r="D17" s="242"/>
+      <c r="D17" s="245"/>
       <c r="E17" s="104" t="s">
         <v>585</v>
       </c>
@@ -25374,8 +25422,8 @@
       <c r="G17" s="117">
         <v>112.53449999999999</v>
       </c>
-      <c r="H17" s="196"/>
-      <c r="I17" s="196"/>
+      <c r="H17" s="199"/>
+      <c r="I17" s="199"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="104" t="s">
@@ -25387,7 +25435,7 @@
       <c r="C18" s="117">
         <v>64.2</v>
       </c>
-      <c r="D18" s="242"/>
+      <c r="D18" s="245"/>
       <c r="E18" s="106" t="s">
         <v>586</v>
       </c>
@@ -25397,8 +25445,8 @@
       <c r="G18" s="118">
         <v>21.690999999999999</v>
       </c>
-      <c r="H18" s="196"/>
-      <c r="I18" s="196"/>
+      <c r="H18" s="199"/>
+      <c r="I18" s="199"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="106" t="s">
@@ -25410,7 +25458,7 @@
       <c r="C19" s="118">
         <v>79.301500000000004</v>
       </c>
-      <c r="D19" s="242"/>
+      <c r="D19" s="245"/>
       <c r="E19" s="110" t="s">
         <v>587</v>
       </c>
@@ -25420,8 +25468,8 @@
       <c r="G19" s="119">
         <v>87.0625</v>
       </c>
-      <c r="H19" s="196"/>
-      <c r="I19" s="196"/>
+      <c r="H19" s="199"/>
+      <c r="I19" s="199"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="104" t="s">
@@ -25433,7 +25481,7 @@
       <c r="C20" s="117">
         <v>26.864999999999998</v>
       </c>
-      <c r="D20" s="242"/>
+      <c r="D20" s="245"/>
       <c r="F20" s="105" t="s">
         <v>474</v>
       </c>
@@ -25441,8 +25489,8 @@
         <f>SUM(G7:G19)</f>
         <v>849.95200000000011</v>
       </c>
-      <c r="H20" s="196"/>
-      <c r="I20" s="196"/>
+      <c r="H20" s="199"/>
+      <c r="I20" s="199"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="106" t="s">
@@ -25454,12 +25502,12 @@
       <c r="C21" s="118">
         <v>27.86</v>
       </c>
-      <c r="D21" s="242"/>
-      <c r="E21" s="196"/>
-      <c r="F21" s="196"/>
-      <c r="G21" s="196"/>
-      <c r="H21" s="196"/>
-      <c r="I21" s="196"/>
+      <c r="D21" s="245"/>
+      <c r="E21" s="199"/>
+      <c r="F21" s="199"/>
+      <c r="G21" s="199"/>
+      <c r="H21" s="199"/>
+      <c r="I21" s="199"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="104" t="s">
@@ -25471,12 +25519,12 @@
       <c r="C22" s="117">
         <v>13.93</v>
       </c>
-      <c r="D22" s="242"/>
-      <c r="E22" s="196"/>
-      <c r="F22" s="196"/>
-      <c r="G22" s="196"/>
-      <c r="H22" s="196"/>
-      <c r="I22" s="196"/>
+      <c r="D22" s="245"/>
+      <c r="E22" s="199"/>
+      <c r="F22" s="199"/>
+      <c r="G22" s="199"/>
+      <c r="H22" s="199"/>
+      <c r="I22" s="199"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="106" t="s">
@@ -25488,12 +25536,12 @@
       <c r="C23" s="118">
         <v>19.0045</v>
       </c>
-      <c r="D23" s="242"/>
-      <c r="E23" s="196"/>
-      <c r="F23" s="196"/>
-      <c r="G23" s="196"/>
-      <c r="H23" s="196"/>
-      <c r="I23" s="196"/>
+      <c r="D23" s="245"/>
+      <c r="E23" s="199"/>
+      <c r="F23" s="199"/>
+      <c r="G23" s="199"/>
+      <c r="H23" s="199"/>
+      <c r="I23" s="199"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="104" t="s">
@@ -25505,12 +25553,12 @@
       <c r="C24" s="117">
         <v>200.09449999999998</v>
       </c>
-      <c r="D24" s="242"/>
-      <c r="E24" s="196"/>
-      <c r="F24" s="196"/>
-      <c r="G24" s="196"/>
-      <c r="H24" s="196"/>
-      <c r="I24" s="196"/>
+      <c r="D24" s="245"/>
+      <c r="E24" s="199"/>
+      <c r="F24" s="199"/>
+      <c r="G24" s="199"/>
+      <c r="H24" s="199"/>
+      <c r="I24" s="199"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="106" t="s">
@@ -25522,12 +25570,12 @@
       <c r="C25" s="118">
         <v>114.82300000000001</v>
       </c>
-      <c r="D25" s="242"/>
-      <c r="E25" s="259"/>
-      <c r="F25" s="259"/>
-      <c r="G25" s="259"/>
-      <c r="H25" s="196"/>
-      <c r="I25" s="196"/>
+      <c r="D25" s="245"/>
+      <c r="E25" s="262"/>
+      <c r="F25" s="262"/>
+      <c r="G25" s="262"/>
+      <c r="H25" s="199"/>
+      <c r="I25" s="199"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="104" t="s">
@@ -25539,7 +25587,7 @@
       <c r="C26" s="117">
         <v>75.819000000000003</v>
       </c>
-      <c r="D26" s="242"/>
+      <c r="D26" s="245"/>
       <c r="E26" s="87" t="s">
         <v>593</v>
       </c>
@@ -25549,8 +25597,8 @@
       <c r="G26" s="87" t="s">
         <v>591</v>
       </c>
-      <c r="H26" s="196"/>
-      <c r="I26" s="196"/>
+      <c r="H26" s="199"/>
+      <c r="I26" s="199"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B27" s="105" t="s">
@@ -25560,7 +25608,7 @@
         <f>SUM(C7:C26)</f>
         <v>1351.2184999999999</v>
       </c>
-      <c r="D27" s="242"/>
+      <c r="D27" s="245"/>
       <c r="E27" s="89" t="s">
         <v>582</v>
       </c>
@@ -25570,8 +25618,8 @@
       <c r="G27" s="115">
         <v>244.7</v>
       </c>
-      <c r="H27" s="196"/>
-      <c r="I27" s="196"/>
+      <c r="H27" s="199"/>
+      <c r="I27" s="199"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -25614,25 +25662,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="188" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="186"/>
-      <c r="D2" s="187"/>
+      <c r="C2" s="189"/>
+      <c r="D2" s="190"/>
       <c r="E2" s="175" t="s">
         <v>391</v>
       </c>
@@ -25647,11 +25695,11 @@
       <c r="A3" s="173">
         <v>1</v>
       </c>
-      <c r="B3" s="188" t="s">
+      <c r="B3" s="191" t="s">
         <v>682</v>
       </c>
-      <c r="C3" s="189"/>
-      <c r="D3" s="190"/>
+      <c r="C3" s="192"/>
+      <c r="D3" s="193"/>
       <c r="E3" s="174" t="s">
         <v>748</v>
       </c>
@@ -25670,11 +25718,11 @@
       <c r="B4" s="169" t="s">
         <v>393</v>
       </c>
-      <c r="C4" s="191"/>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
+      <c r="C4" s="194"/>
+      <c r="D4" s="195"/>
+      <c r="E4" s="195"/>
+      <c r="F4" s="195"/>
+      <c r="G4" s="195"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="170" t="s">
@@ -25683,11 +25731,11 @@
       <c r="B5" s="171">
         <v>24</v>
       </c>
-      <c r="C5" s="193"/>
-      <c r="D5" s="194"/>
-      <c r="E5" s="194"/>
-      <c r="F5" s="194"/>
-      <c r="G5" s="194"/>
+      <c r="C5" s="196"/>
+      <c r="D5" s="197"/>
+      <c r="E5" s="197"/>
+      <c r="F5" s="197"/>
+      <c r="G5" s="197"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="170" t="s">
@@ -25696,11 +25744,11 @@
       <c r="B6" s="171">
         <v>51.3</v>
       </c>
-      <c r="C6" s="193"/>
-      <c r="D6" s="194"/>
-      <c r="E6" s="194"/>
-      <c r="F6" s="194"/>
-      <c r="G6" s="194"/>
+      <c r="C6" s="196"/>
+      <c r="D6" s="197"/>
+      <c r="E6" s="197"/>
+      <c r="F6" s="197"/>
+      <c r="G6" s="197"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="170" t="s">
@@ -25709,11 +25757,11 @@
       <c r="B7" s="171">
         <v>56.6</v>
       </c>
-      <c r="C7" s="193"/>
-      <c r="D7" s="194"/>
-      <c r="E7" s="194"/>
-      <c r="F7" s="194"/>
-      <c r="G7" s="194"/>
+      <c r="C7" s="196"/>
+      <c r="D7" s="197"/>
+      <c r="E7" s="197"/>
+      <c r="F7" s="197"/>
+      <c r="G7" s="197"/>
     </row>
     <row r="8" spans="1:7" s="180" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="170" t="s">
@@ -25722,11 +25770,11 @@
       <c r="B8" s="171">
         <v>18.5</v>
       </c>
-      <c r="C8" s="193"/>
-      <c r="D8" s="194"/>
-      <c r="E8" s="194"/>
-      <c r="F8" s="194"/>
-      <c r="G8" s="194"/>
+      <c r="C8" s="196"/>
+      <c r="D8" s="197"/>
+      <c r="E8" s="197"/>
+      <c r="F8" s="197"/>
+      <c r="G8" s="197"/>
     </row>
     <row r="9" spans="1:7" s="180" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="170" t="s">
@@ -25735,11 +25783,11 @@
       <c r="B9" s="171">
         <v>51.3</v>
       </c>
-      <c r="C9" s="193"/>
-      <c r="D9" s="194"/>
-      <c r="E9" s="194"/>
-      <c r="F9" s="194"/>
-      <c r="G9" s="194"/>
+      <c r="C9" s="196"/>
+      <c r="D9" s="197"/>
+      <c r="E9" s="197"/>
+      <c r="F9" s="197"/>
+      <c r="G9" s="197"/>
     </row>
     <row r="10" spans="1:7" s="180" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="170" t="s">
@@ -25748,11 +25796,11 @@
       <c r="B10" s="171">
         <v>56.3</v>
       </c>
-      <c r="C10" s="193"/>
-      <c r="D10" s="194"/>
-      <c r="E10" s="194"/>
-      <c r="F10" s="194"/>
-      <c r="G10" s="194"/>
+      <c r="C10" s="196"/>
+      <c r="D10" s="197"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="197"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="172" t="s">
@@ -25762,11 +25810,11 @@
         <f>SUM(B5:B10)</f>
         <v>258</v>
       </c>
-      <c r="C11" s="193"/>
-      <c r="D11" s="194"/>
-      <c r="E11" s="194"/>
-      <c r="F11" s="194"/>
-      <c r="G11" s="194"/>
+      <c r="C11" s="196"/>
+      <c r="D11" s="197"/>
+      <c r="E11" s="197"/>
+      <c r="F11" s="197"/>
+      <c r="G11" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -25806,36 +25854,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="260" t="s">
+      <c r="A1" s="265" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="261"/>
-      <c r="C1" s="261"/>
-      <c r="D1" s="261"/>
-      <c r="E1" s="261"/>
-      <c r="F1" s="261"/>
-      <c r="G1" s="261"/>
-      <c r="H1" s="261"/>
-      <c r="I1" s="261"/>
-      <c r="J1" s="261"/>
-      <c r="K1" s="261"/>
+      <c r="B1" s="266"/>
+      <c r="C1" s="266"/>
+      <c r="D1" s="266"/>
+      <c r="E1" s="266"/>
+      <c r="F1" s="266"/>
+      <c r="G1" s="266"/>
+      <c r="H1" s="266"/>
+      <c r="I1" s="266"/>
+      <c r="J1" s="266"/>
+      <c r="K1" s="266"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="40" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="257" t="s">
+      <c r="B2" s="260" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="257"/>
-      <c r="D2" s="257"/>
-      <c r="E2" s="257"/>
-      <c r="F2" s="257"/>
-      <c r="G2" s="262" t="s">
+      <c r="C2" s="260"/>
+      <c r="D2" s="260"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="260"/>
+      <c r="G2" s="267" t="s">
         <v>391</v>
       </c>
-      <c r="H2" s="263"/>
-      <c r="I2" s="264"/>
+      <c r="H2" s="268"/>
+      <c r="I2" s="269"/>
       <c r="J2" s="41" t="s">
         <v>392</v>
       </c>
@@ -25847,18 +25895,18 @@
       <c r="A3" s="83">
         <v>1</v>
       </c>
-      <c r="B3" s="258" t="s">
+      <c r="B3" s="261" t="s">
         <v>679</v>
       </c>
-      <c r="C3" s="258"/>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
-      <c r="G3" s="265" t="s">
+      <c r="C3" s="261"/>
+      <c r="D3" s="261"/>
+      <c r="E3" s="261"/>
+      <c r="F3" s="261"/>
+      <c r="G3" s="270" t="s">
         <v>488</v>
       </c>
-      <c r="H3" s="266"/>
-      <c r="I3" s="267"/>
+      <c r="H3" s="271"/>
+      <c r="I3" s="272"/>
       <c r="J3" s="83" t="s">
         <v>394</v>
       </c>
@@ -25868,17 +25916,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="253"/>
-      <c r="B4" s="253"/>
-      <c r="C4" s="253"/>
-      <c r="D4" s="253"/>
-      <c r="E4" s="253"/>
-      <c r="F4" s="253"/>
-      <c r="G4" s="253"/>
-      <c r="H4" s="253"/>
-      <c r="I4" s="253"/>
-      <c r="J4" s="253"/>
-      <c r="K4" s="253"/>
+      <c r="A4" s="259"/>
+      <c r="B4" s="259"/>
+      <c r="C4" s="259"/>
+      <c r="D4" s="259"/>
+      <c r="E4" s="259"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
+      <c r="H4" s="259"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="259"/>
+      <c r="K4" s="259"/>
     </row>
     <row r="5" spans="1:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="59" t="s">
@@ -25890,7 +25938,7 @@
       <c r="C5" s="59" t="s">
         <v>477</v>
       </c>
-      <c r="D5" s="253"/>
+      <c r="D5" s="259"/>
       <c r="E5" s="59" t="s">
         <v>478</v>
       </c>
@@ -25900,7 +25948,7 @@
       <c r="G5" s="59" t="s">
         <v>477</v>
       </c>
-      <c r="H5" s="268"/>
+      <c r="H5" s="263"/>
       <c r="I5" s="59" t="s">
         <v>478</v>
       </c>
@@ -25921,7 +25969,7 @@
       <c r="C6" s="61">
         <v>20.7</v>
       </c>
-      <c r="D6" s="253"/>
+      <c r="D6" s="259"/>
       <c r="E6" s="62" t="s">
         <v>451</v>
       </c>
@@ -25931,7 +25979,7 @@
       <c r="G6" s="122">
         <v>23.4</v>
       </c>
-      <c r="H6" s="268"/>
+      <c r="H6" s="263"/>
       <c r="I6" s="60">
         <v>3.23</v>
       </c>
@@ -25952,7 +26000,7 @@
       <c r="C7" s="63">
         <v>16.8</v>
       </c>
-      <c r="D7" s="253"/>
+      <c r="D7" s="259"/>
       <c r="E7" s="60" t="s">
         <v>452</v>
       </c>
@@ -25962,7 +26010,7 @@
       <c r="G7" s="123">
         <v>50.9</v>
       </c>
-      <c r="H7" s="268"/>
+      <c r="H7" s="263"/>
       <c r="I7" s="62">
         <v>3.25</v>
       </c>
@@ -25983,7 +26031,7 @@
       <c r="C8" s="61">
         <v>24</v>
       </c>
-      <c r="D8" s="253"/>
+      <c r="D8" s="259"/>
       <c r="E8" s="62" t="s">
         <v>453</v>
       </c>
@@ -25993,7 +26041,7 @@
       <c r="G8" s="122">
         <v>55.8</v>
       </c>
-      <c r="H8" s="268"/>
+      <c r="H8" s="263"/>
       <c r="I8" s="60">
         <v>3.26</v>
       </c>
@@ -26014,7 +26062,7 @@
       <c r="C9" s="63">
         <v>51.3</v>
       </c>
-      <c r="D9" s="253"/>
+      <c r="D9" s="259"/>
       <c r="E9" s="60" t="s">
         <v>454</v>
       </c>
@@ -26024,7 +26072,7 @@
       <c r="G9" s="123">
         <v>23.01</v>
       </c>
-      <c r="H9" s="268"/>
+      <c r="H9" s="263"/>
       <c r="I9" s="62">
         <v>3.28</v>
       </c>
@@ -26045,7 +26093,7 @@
       <c r="C10" s="61">
         <v>54.6</v>
       </c>
-      <c r="D10" s="253"/>
+      <c r="D10" s="259"/>
       <c r="E10" s="62" t="s">
         <v>455</v>
       </c>
@@ -26055,7 +26103,7 @@
       <c r="G10" s="122">
         <v>50.45</v>
       </c>
-      <c r="H10" s="268"/>
+      <c r="H10" s="263"/>
       <c r="I10" s="60">
         <v>3.29</v>
       </c>
@@ -26076,7 +26124,7 @@
       <c r="C11" s="63">
         <v>18.5</v>
       </c>
-      <c r="D11" s="253"/>
+      <c r="D11" s="259"/>
       <c r="E11" s="60" t="s">
         <v>456</v>
       </c>
@@ -26086,7 +26134,7 @@
       <c r="G11" s="123">
         <v>54.22</v>
       </c>
-      <c r="H11" s="268"/>
+      <c r="H11" s="263"/>
       <c r="I11" s="62">
         <v>3.3</v>
       </c>
@@ -26107,7 +26155,7 @@
       <c r="C12" s="61">
         <v>51.2</v>
       </c>
-      <c r="D12" s="253"/>
+      <c r="D12" s="259"/>
       <c r="E12" s="62" t="s">
         <v>458</v>
       </c>
@@ -26117,7 +26165,7 @@
       <c r="G12" s="122">
         <v>73</v>
       </c>
-      <c r="H12" s="268"/>
+      <c r="H12" s="263"/>
       <c r="I12" s="60">
         <v>3.33</v>
       </c>
@@ -26138,7 +26186,7 @@
       <c r="C13" s="63">
         <v>55.3</v>
       </c>
-      <c r="D13" s="253"/>
+      <c r="D13" s="259"/>
       <c r="E13" s="60" t="s">
         <v>569</v>
       </c>
@@ -26148,7 +26196,7 @@
       <c r="G13" s="123">
         <v>6</v>
       </c>
-      <c r="H13" s="268"/>
+      <c r="H13" s="263"/>
       <c r="I13" s="62">
         <v>3.34</v>
       </c>
@@ -26169,7 +26217,7 @@
       <c r="C14" s="61">
         <v>41.2</v>
       </c>
-      <c r="D14" s="253"/>
+      <c r="D14" s="259"/>
       <c r="E14" s="62" t="s">
         <v>459</v>
       </c>
@@ -26179,7 +26227,7 @@
       <c r="G14" s="122">
         <v>42.4</v>
       </c>
-      <c r="H14" s="268"/>
+      <c r="H14" s="263"/>
       <c r="I14" s="60">
         <v>3.35</v>
       </c>
@@ -26200,7 +26248,7 @@
       <c r="C15" s="63">
         <v>59.3</v>
       </c>
-      <c r="D15" s="253"/>
+      <c r="D15" s="259"/>
       <c r="E15" s="60" t="s">
         <v>460</v>
       </c>
@@ -26210,7 +26258,7 @@
       <c r="G15" s="123">
         <v>59.6</v>
       </c>
-      <c r="H15" s="268"/>
+      <c r="H15" s="263"/>
       <c r="I15" s="62">
         <v>3.41</v>
       </c>
@@ -26230,7 +26278,7 @@
         <f>SUM(C6:C15)</f>
         <v>392.90000000000003</v>
       </c>
-      <c r="D16" s="253"/>
+      <c r="D16" s="259"/>
       <c r="E16" s="64"/>
       <c r="F16" s="65" t="s">
         <v>474</v>
@@ -26239,7 +26287,7 @@
         <f>SUM(G6:G15)</f>
         <v>438.78</v>
       </c>
-      <c r="H16" s="268"/>
+      <c r="H16" s="263"/>
       <c r="I16" s="60">
         <v>3.42</v>
       </c>
@@ -26251,14 +26299,14 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="269"/>
-      <c r="B17" s="269"/>
-      <c r="C17" s="269"/>
-      <c r="D17" s="253"/>
-      <c r="E17" s="269"/>
-      <c r="F17" s="269"/>
-      <c r="G17" s="269"/>
-      <c r="H17" s="268"/>
+      <c r="A17" s="264"/>
+      <c r="B17" s="264"/>
+      <c r="C17" s="264"/>
+      <c r="D17" s="259"/>
+      <c r="E17" s="264"/>
+      <c r="F17" s="264"/>
+      <c r="G17" s="264"/>
+      <c r="H17" s="263"/>
       <c r="I17" s="64"/>
       <c r="J17" s="65" t="s">
         <v>474</v>
@@ -26270,16 +26318,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
     <mergeCell ref="D5:D17"/>
     <mergeCell ref="H5:H17"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="E17:G17"/>
     <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -26300,14 +26348,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
@@ -26316,10 +26364,10 @@
       <c r="B2" s="16" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="207" t="s">
+      <c r="C2" s="210" t="s">
         <v>391</v>
       </c>
-      <c r="D2" s="208"/>
+      <c r="D2" s="211"/>
       <c r="E2" s="16" t="s">
         <v>392</v>
       </c>
@@ -26334,10 +26382,10 @@
       <c r="B3" s="52" t="s">
         <v>487</v>
       </c>
-      <c r="C3" s="270" t="s">
+      <c r="C3" s="273" t="s">
         <v>483</v>
       </c>
-      <c r="D3" s="271"/>
+      <c r="D3" s="274"/>
       <c r="E3" s="53" t="s">
         <v>394</v>
       </c>
@@ -26347,16 +26395,16 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="274"/>
-      <c r="B4" s="274"/>
-      <c r="C4" s="274"/>
-      <c r="D4" s="274"/>
-      <c r="E4" s="274"/>
-      <c r="F4" s="274"/>
+      <c r="A4" s="277"/>
+      <c r="B4" s="277"/>
+      <c r="C4" s="277"/>
+      <c r="D4" s="277"/>
+      <c r="E4" s="277"/>
+      <c r="F4" s="277"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="272"/>
-      <c r="B5" s="273"/>
+      <c r="A5" s="275"/>
+      <c r="B5" s="276"/>
       <c r="C5" s="17" t="s">
         <v>486</v>
       </c>
@@ -26371,8 +26419,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="272"/>
-      <c r="B6" s="273"/>
+      <c r="A6" s="275"/>
+      <c r="B6" s="276"/>
       <c r="C6" s="17">
         <v>1</v>
       </c>
@@ -26387,8 +26435,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="272"/>
-      <c r="B7" s="273"/>
+      <c r="A7" s="275"/>
+      <c r="B7" s="276"/>
       <c r="C7" s="17">
         <v>2</v>
       </c>
@@ -26435,36 +26483,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="260" t="s">
+      <c r="A1" s="265" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="261"/>
-      <c r="C1" s="261"/>
-      <c r="D1" s="261"/>
-      <c r="E1" s="261"/>
-      <c r="F1" s="261"/>
-      <c r="G1" s="261"/>
-      <c r="H1" s="261"/>
-      <c r="I1" s="261"/>
-      <c r="J1" s="261"/>
-      <c r="K1" s="261"/>
+      <c r="B1" s="266"/>
+      <c r="C1" s="266"/>
+      <c r="D1" s="266"/>
+      <c r="E1" s="266"/>
+      <c r="F1" s="266"/>
+      <c r="G1" s="266"/>
+      <c r="H1" s="266"/>
+      <c r="I1" s="266"/>
+      <c r="J1" s="266"/>
+      <c r="K1" s="266"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="40" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="257" t="s">
+      <c r="B2" s="260" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="257"/>
-      <c r="D2" s="257"/>
-      <c r="E2" s="257"/>
-      <c r="F2" s="257"/>
-      <c r="G2" s="262" t="s">
+      <c r="C2" s="260"/>
+      <c r="D2" s="260"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="260"/>
+      <c r="G2" s="267" t="s">
         <v>391</v>
       </c>
-      <c r="H2" s="263"/>
-      <c r="I2" s="264"/>
+      <c r="H2" s="268"/>
+      <c r="I2" s="269"/>
       <c r="J2" s="41" t="s">
         <v>392</v>
       </c>
@@ -26476,18 +26524,18 @@
       <c r="A3" s="51">
         <v>1</v>
       </c>
-      <c r="B3" s="258" t="s">
+      <c r="B3" s="261" t="s">
         <v>479</v>
       </c>
-      <c r="C3" s="258"/>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
-      <c r="G3" s="265" t="s">
+      <c r="C3" s="261"/>
+      <c r="D3" s="261"/>
+      <c r="E3" s="261"/>
+      <c r="F3" s="261"/>
+      <c r="G3" s="270" t="s">
         <v>488</v>
       </c>
-      <c r="H3" s="266"/>
-      <c r="I3" s="267"/>
+      <c r="H3" s="271"/>
+      <c r="I3" s="272"/>
       <c r="J3" s="55" t="s">
         <v>394</v>
       </c>
@@ -26497,17 +26545,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="253"/>
-      <c r="B4" s="253"/>
-      <c r="C4" s="253"/>
-      <c r="D4" s="253"/>
-      <c r="E4" s="253"/>
-      <c r="F4" s="253"/>
-      <c r="G4" s="253"/>
-      <c r="H4" s="253"/>
-      <c r="I4" s="253"/>
-      <c r="J4" s="253"/>
-      <c r="K4" s="253"/>
+      <c r="A4" s="259"/>
+      <c r="B4" s="259"/>
+      <c r="C4" s="259"/>
+      <c r="D4" s="259"/>
+      <c r="E4" s="259"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
+      <c r="H4" s="259"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="259"/>
+      <c r="K4" s="259"/>
     </row>
     <row r="5" spans="1:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="59" t="s">
@@ -26519,7 +26567,7 @@
       <c r="C5" s="59" t="s">
         <v>477</v>
       </c>
-      <c r="D5" s="253"/>
+      <c r="D5" s="259"/>
       <c r="E5" s="59" t="s">
         <v>478</v>
       </c>
@@ -26529,7 +26577,7 @@
       <c r="G5" s="59" t="s">
         <v>477</v>
       </c>
-      <c r="H5" s="268"/>
+      <c r="H5" s="263"/>
       <c r="I5" s="59" t="s">
         <v>478</v>
       </c>
@@ -26550,7 +26598,7 @@
       <c r="C6" s="61">
         <v>20.7</v>
       </c>
-      <c r="D6" s="253"/>
+      <c r="D6" s="259"/>
       <c r="E6" s="62">
         <v>2.37</v>
       </c>
@@ -26560,7 +26608,7 @@
       <c r="G6" s="63">
         <v>21.6</v>
       </c>
-      <c r="H6" s="268"/>
+      <c r="H6" s="263"/>
       <c r="I6" s="60">
         <v>3.23</v>
       </c>
@@ -26581,7 +26629,7 @@
       <c r="C7" s="63">
         <v>16.8</v>
       </c>
-      <c r="D7" s="253"/>
+      <c r="D7" s="259"/>
       <c r="E7" s="60">
         <v>2.4</v>
       </c>
@@ -26591,7 +26639,7 @@
       <c r="G7" s="61">
         <v>51.3</v>
       </c>
-      <c r="H7" s="268"/>
+      <c r="H7" s="263"/>
       <c r="I7" s="62">
         <v>3.25</v>
       </c>
@@ -26612,7 +26660,7 @@
       <c r="C8" s="61">
         <v>24</v>
       </c>
-      <c r="D8" s="253"/>
+      <c r="D8" s="259"/>
       <c r="E8" s="62">
         <v>2.41</v>
       </c>
@@ -26622,7 +26670,7 @@
       <c r="G8" s="63">
         <v>56.6</v>
       </c>
-      <c r="H8" s="268"/>
+      <c r="H8" s="263"/>
       <c r="I8" s="60">
         <v>3.26</v>
       </c>
@@ -26643,7 +26691,7 @@
       <c r="C9" s="63">
         <v>51.3</v>
       </c>
-      <c r="D9" s="253"/>
+      <c r="D9" s="259"/>
       <c r="E9" s="60">
         <v>2.42</v>
       </c>
@@ -26653,7 +26701,7 @@
       <c r="G9" s="61">
         <v>21.5</v>
       </c>
-      <c r="H9" s="268"/>
+      <c r="H9" s="263"/>
       <c r="I9" s="62">
         <v>3.28</v>
       </c>
@@ -26674,7 +26722,7 @@
       <c r="C10" s="61">
         <v>54.6</v>
       </c>
-      <c r="D10" s="253"/>
+      <c r="D10" s="259"/>
       <c r="E10" s="62">
         <v>2.44</v>
       </c>
@@ -26684,7 +26732,7 @@
       <c r="G10" s="63">
         <v>51.3</v>
       </c>
-      <c r="H10" s="268"/>
+      <c r="H10" s="263"/>
       <c r="I10" s="60">
         <v>3.29</v>
       </c>
@@ -26705,7 +26753,7 @@
       <c r="C11" s="63">
         <v>18.5</v>
       </c>
-      <c r="D11" s="253"/>
+      <c r="D11" s="259"/>
       <c r="E11" s="60">
         <v>2.4500000000000002</v>
       </c>
@@ -26715,7 +26763,7 @@
       <c r="G11" s="61">
         <v>56.3</v>
       </c>
-      <c r="H11" s="268"/>
+      <c r="H11" s="263"/>
       <c r="I11" s="62">
         <v>3.3</v>
       </c>
@@ -26736,7 +26784,7 @@
       <c r="C12" s="61">
         <v>51.2</v>
       </c>
-      <c r="D12" s="253"/>
+      <c r="D12" s="259"/>
       <c r="E12" s="64"/>
       <c r="F12" s="65" t="s">
         <v>474</v>
@@ -26745,7 +26793,7 @@
         <f>SUM(G6:G11)</f>
         <v>258.60000000000002</v>
       </c>
-      <c r="H12" s="268"/>
+      <c r="H12" s="263"/>
       <c r="I12" s="60">
         <v>3.33</v>
       </c>
@@ -26766,11 +26814,11 @@
       <c r="C13" s="63">
         <v>55.3</v>
       </c>
-      <c r="D13" s="253"/>
-      <c r="E13" s="269"/>
-      <c r="F13" s="269"/>
-      <c r="G13" s="269"/>
-      <c r="H13" s="268"/>
+      <c r="D13" s="259"/>
+      <c r="E13" s="264"/>
+      <c r="F13" s="264"/>
+      <c r="G13" s="264"/>
+      <c r="H13" s="263"/>
       <c r="I13" s="62">
         <v>3.34</v>
       </c>
@@ -26791,11 +26839,11 @@
       <c r="C14" s="61">
         <v>41.2</v>
       </c>
-      <c r="D14" s="253"/>
-      <c r="E14" s="275"/>
-      <c r="F14" s="275"/>
-      <c r="G14" s="275"/>
-      <c r="H14" s="268"/>
+      <c r="D14" s="259"/>
+      <c r="E14" s="278"/>
+      <c r="F14" s="278"/>
+      <c r="G14" s="278"/>
+      <c r="H14" s="263"/>
       <c r="I14" s="60">
         <v>3.35</v>
       </c>
@@ -26816,11 +26864,11 @@
       <c r="C15" s="63">
         <v>59.3</v>
       </c>
-      <c r="D15" s="253"/>
-      <c r="E15" s="275"/>
-      <c r="F15" s="275"/>
-      <c r="G15" s="275"/>
-      <c r="H15" s="268"/>
+      <c r="D15" s="259"/>
+      <c r="E15" s="278"/>
+      <c r="F15" s="278"/>
+      <c r="G15" s="278"/>
+      <c r="H15" s="263"/>
       <c r="I15" s="62">
         <v>3.41</v>
       </c>
@@ -26840,11 +26888,11 @@
         <f>SUM(C6:C15)</f>
         <v>392.90000000000003</v>
       </c>
-      <c r="D16" s="253"/>
-      <c r="E16" s="275"/>
-      <c r="F16" s="275"/>
-      <c r="G16" s="275"/>
-      <c r="H16" s="268"/>
+      <c r="D16" s="259"/>
+      <c r="E16" s="278"/>
+      <c r="F16" s="278"/>
+      <c r="G16" s="278"/>
+      <c r="H16" s="263"/>
       <c r="I16" s="60">
         <v>3.42</v>
       </c>
@@ -26856,14 +26904,14 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="269"/>
-      <c r="B17" s="269"/>
-      <c r="C17" s="269"/>
-      <c r="D17" s="253"/>
-      <c r="E17" s="275"/>
-      <c r="F17" s="275"/>
-      <c r="G17" s="275"/>
-      <c r="H17" s="268"/>
+      <c r="A17" s="264"/>
+      <c r="B17" s="264"/>
+      <c r="C17" s="264"/>
+      <c r="D17" s="259"/>
+      <c r="E17" s="278"/>
+      <c r="F17" s="278"/>
+      <c r="G17" s="278"/>
+      <c r="H17" s="263"/>
       <c r="I17" s="64"/>
       <c r="J17" s="65" t="s">
         <v>474</v>
@@ -26928,7 +26976,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="54" x14ac:dyDescent="0.3">
       <c r="A3" s="58">
         <v>1</v>
       </c>
@@ -26971,36 +27019,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="276" t="s">
+      <c r="A1" s="282" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="259"/>
-      <c r="C1" s="259"/>
-      <c r="D1" s="259"/>
-      <c r="E1" s="259"/>
-      <c r="F1" s="259"/>
-      <c r="G1" s="259"/>
-      <c r="H1" s="259"/>
-      <c r="I1" s="259"/>
-      <c r="J1" s="259"/>
-      <c r="K1" s="259"/>
+      <c r="B1" s="262"/>
+      <c r="C1" s="262"/>
+      <c r="D1" s="262"/>
+      <c r="E1" s="262"/>
+      <c r="F1" s="262"/>
+      <c r="G1" s="262"/>
+      <c r="H1" s="262"/>
+      <c r="I1" s="262"/>
+      <c r="J1" s="262"/>
+      <c r="K1" s="262"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="214" t="s">
+      <c r="B2" s="217" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="214"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="214"/>
-      <c r="G2" s="207" t="s">
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="217"/>
+      <c r="G2" s="210" t="s">
         <v>391</v>
       </c>
-      <c r="H2" s="218"/>
-      <c r="I2" s="208"/>
+      <c r="H2" s="221"/>
+      <c r="I2" s="211"/>
       <c r="J2" s="16" t="s">
         <v>392</v>
       </c>
@@ -27012,18 +27060,18 @@
       <c r="A3" s="58">
         <v>1</v>
       </c>
-      <c r="B3" s="212" t="s">
+      <c r="B3" s="215" t="s">
         <v>438</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="212"/>
-      <c r="G3" s="209" t="s">
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="215"/>
+      <c r="G3" s="212" t="s">
         <v>428</v>
       </c>
-      <c r="H3" s="251"/>
-      <c r="I3" s="252"/>
+      <c r="H3" s="254"/>
+      <c r="I3" s="255"/>
       <c r="J3" s="58" t="s">
         <v>394</v>
       </c>
@@ -27036,18 +27084,18 @@
       <c r="A4" s="66">
         <v>1</v>
       </c>
-      <c r="B4" s="212" t="s">
+      <c r="B4" s="215" t="s">
         <v>438</v>
       </c>
-      <c r="C4" s="212"/>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="212"/>
-      <c r="G4" s="209" t="s">
+      <c r="C4" s="215"/>
+      <c r="D4" s="215"/>
+      <c r="E4" s="215"/>
+      <c r="F4" s="215"/>
+      <c r="G4" s="212" t="s">
         <v>533</v>
       </c>
-      <c r="H4" s="251"/>
-      <c r="I4" s="252"/>
+      <c r="H4" s="254"/>
+      <c r="I4" s="255"/>
       <c r="J4" s="66" t="s">
         <v>394</v>
       </c>
@@ -27057,17 +27105,17 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="274"/>
-      <c r="B5" s="274"/>
-      <c r="C5" s="274"/>
-      <c r="D5" s="274"/>
-      <c r="E5" s="274"/>
-      <c r="F5" s="274"/>
-      <c r="G5" s="274"/>
-      <c r="H5" s="274"/>
-      <c r="I5" s="274"/>
-      <c r="J5" s="274"/>
-      <c r="K5" s="274"/>
+      <c r="A5" s="277"/>
+      <c r="B5" s="277"/>
+      <c r="C5" s="277"/>
+      <c r="D5" s="277"/>
+      <c r="E5" s="277"/>
+      <c r="F5" s="277"/>
+      <c r="G5" s="277"/>
+      <c r="H5" s="277"/>
+      <c r="I5" s="277"/>
+      <c r="J5" s="277"/>
+      <c r="K5" s="277"/>
     </row>
     <row r="6" spans="1:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="67" t="s">
@@ -27079,7 +27127,7 @@
       <c r="C6" s="67" t="s">
         <v>477</v>
       </c>
-      <c r="D6" s="273"/>
+      <c r="D6" s="276"/>
       <c r="E6" s="67" t="s">
         <v>478</v>
       </c>
@@ -27089,7 +27137,7 @@
       <c r="G6" s="67" t="s">
         <v>477</v>
       </c>
-      <c r="H6" s="279"/>
+      <c r="H6" s="281"/>
       <c r="I6" s="67" t="s">
         <v>478</v>
       </c>
@@ -27110,7 +27158,7 @@
       <c r="C7" s="69">
         <v>5.01</v>
       </c>
-      <c r="D7" s="273"/>
+      <c r="D7" s="276"/>
       <c r="E7" s="70" t="s">
         <v>494</v>
       </c>
@@ -27120,7 +27168,7 @@
       <c r="G7" s="71">
         <v>6.47</v>
       </c>
-      <c r="H7" s="279"/>
+      <c r="H7" s="281"/>
       <c r="I7" s="68" t="s">
         <v>506</v>
       </c>
@@ -27141,7 +27189,7 @@
       <c r="C8" s="71">
         <v>3.76</v>
       </c>
-      <c r="D8" s="273"/>
+      <c r="D8" s="276"/>
       <c r="E8" s="68" t="s">
         <v>497</v>
       </c>
@@ -27151,7 +27199,7 @@
       <c r="G8" s="69">
         <v>10.18</v>
       </c>
-      <c r="H8" s="279"/>
+      <c r="H8" s="281"/>
       <c r="I8" s="70" t="s">
         <v>507</v>
       </c>
@@ -27172,7 +27220,7 @@
       <c r="C9" s="69">
         <v>10.18</v>
       </c>
-      <c r="D9" s="273"/>
+      <c r="D9" s="276"/>
       <c r="E9" s="70" t="s">
         <v>495</v>
       </c>
@@ -27182,7 +27230,7 @@
       <c r="G9" s="71">
         <v>10.23</v>
       </c>
-      <c r="H9" s="279"/>
+      <c r="H9" s="281"/>
       <c r="I9" s="68" t="s">
         <v>508</v>
       </c>
@@ -27203,7 +27251,7 @@
       <c r="C10" s="71">
         <v>5.14</v>
       </c>
-      <c r="D10" s="273"/>
+      <c r="D10" s="276"/>
       <c r="E10" s="68" t="s">
         <v>496</v>
       </c>
@@ -27213,7 +27261,7 @@
       <c r="G10" s="69">
         <v>5.24</v>
       </c>
-      <c r="H10" s="279"/>
+      <c r="H10" s="281"/>
       <c r="I10" s="70" t="s">
         <v>509</v>
       </c>
@@ -27234,7 +27282,7 @@
       <c r="C11" s="69">
         <v>10.23</v>
       </c>
-      <c r="D11" s="273"/>
+      <c r="D11" s="276"/>
       <c r="E11" s="70" t="s">
         <v>498</v>
       </c>
@@ -27244,7 +27292,7 @@
       <c r="G11" s="71">
         <v>5.1100000000000003</v>
       </c>
-      <c r="H11" s="279"/>
+      <c r="H11" s="281"/>
       <c r="I11" s="68" t="s">
         <v>510</v>
       </c>
@@ -27264,7 +27312,7 @@
         <f>SUM(C7:C11)</f>
         <v>34.32</v>
       </c>
-      <c r="D12" s="273"/>
+      <c r="D12" s="276"/>
       <c r="E12" s="68" t="s">
         <v>499</v>
       </c>
@@ -27274,7 +27322,7 @@
       <c r="G12" s="69">
         <v>11.06</v>
       </c>
-      <c r="H12" s="279"/>
+      <c r="H12" s="281"/>
       <c r="I12" s="70" t="s">
         <v>511</v>
       </c>
@@ -27286,10 +27334,10 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="274"/>
-      <c r="B13" s="274"/>
-      <c r="C13" s="274"/>
-      <c r="D13" s="273"/>
+      <c r="A13" s="277"/>
+      <c r="B13" s="277"/>
+      <c r="C13" s="277"/>
+      <c r="D13" s="276"/>
       <c r="E13" s="70" t="s">
         <v>500</v>
       </c>
@@ -27299,7 +27347,7 @@
       <c r="G13" s="71">
         <v>11.17</v>
       </c>
-      <c r="H13" s="279"/>
+      <c r="H13" s="281"/>
       <c r="I13" s="68" t="s">
         <v>512</v>
       </c>
@@ -27311,10 +27359,10 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="278"/>
-      <c r="B14" s="278"/>
-      <c r="C14" s="278"/>
-      <c r="D14" s="273"/>
+      <c r="A14" s="280"/>
+      <c r="B14" s="280"/>
+      <c r="C14" s="280"/>
+      <c r="D14" s="276"/>
       <c r="E14" s="68" t="s">
         <v>501</v>
       </c>
@@ -27324,7 +27372,7 @@
       <c r="G14" s="69">
         <v>13.28</v>
       </c>
-      <c r="H14" s="279"/>
+      <c r="H14" s="281"/>
       <c r="I14" s="70" t="s">
         <v>513</v>
       </c>
@@ -27336,10 +27384,10 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="278"/>
-      <c r="B15" s="278"/>
-      <c r="C15" s="278"/>
-      <c r="D15" s="273"/>
+      <c r="A15" s="280"/>
+      <c r="B15" s="280"/>
+      <c r="C15" s="280"/>
+      <c r="D15" s="276"/>
       <c r="E15" s="70" t="s">
         <v>502</v>
       </c>
@@ -27349,7 +27397,7 @@
       <c r="G15" s="71">
         <v>8.24</v>
       </c>
-      <c r="H15" s="279"/>
+      <c r="H15" s="281"/>
       <c r="I15" s="72"/>
       <c r="J15" s="73" t="s">
         <v>474</v>
@@ -27360,10 +27408,10 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="278"/>
-      <c r="B16" s="278"/>
-      <c r="C16" s="278"/>
-      <c r="D16" s="273"/>
+      <c r="A16" s="280"/>
+      <c r="B16" s="280"/>
+      <c r="C16" s="280"/>
+      <c r="D16" s="276"/>
       <c r="E16" s="68" t="s">
         <v>503</v>
       </c>
@@ -27373,16 +27421,16 @@
       <c r="G16" s="69">
         <v>10.49</v>
       </c>
-      <c r="H16" s="279"/>
-      <c r="I16" s="274"/>
-      <c r="J16" s="274"/>
-      <c r="K16" s="274"/>
+      <c r="H16" s="281"/>
+      <c r="I16" s="277"/>
+      <c r="J16" s="277"/>
+      <c r="K16" s="277"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A17" s="278"/>
-      <c r="B17" s="278"/>
-      <c r="C17" s="278"/>
-      <c r="D17" s="273"/>
+      <c r="A17" s="280"/>
+      <c r="B17" s="280"/>
+      <c r="C17" s="280"/>
+      <c r="D17" s="276"/>
       <c r="E17" s="70" t="s">
         <v>504</v>
       </c>
@@ -27392,16 +27440,16 @@
       <c r="G17" s="71">
         <v>11.84</v>
       </c>
-      <c r="H17" s="279"/>
-      <c r="I17" s="278"/>
-      <c r="J17" s="278"/>
-      <c r="K17" s="278"/>
+      <c r="H17" s="281"/>
+      <c r="I17" s="280"/>
+      <c r="J17" s="280"/>
+      <c r="K17" s="280"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A18" s="278"/>
-      <c r="B18" s="278"/>
-      <c r="C18" s="278"/>
-      <c r="D18" s="273"/>
+      <c r="A18" s="280"/>
+      <c r="B18" s="280"/>
+      <c r="C18" s="280"/>
+      <c r="D18" s="276"/>
       <c r="E18" s="68" t="s">
         <v>505</v>
       </c>
@@ -27411,16 +27459,16 @@
       <c r="G18" s="69">
         <v>30.78</v>
       </c>
-      <c r="H18" s="279"/>
-      <c r="I18" s="278"/>
-      <c r="J18" s="278"/>
-      <c r="K18" s="278"/>
+      <c r="H18" s="281"/>
+      <c r="I18" s="280"/>
+      <c r="J18" s="280"/>
+      <c r="K18" s="280"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A19" s="278"/>
-      <c r="B19" s="278"/>
-      <c r="C19" s="278"/>
-      <c r="D19" s="273"/>
+      <c r="A19" s="280"/>
+      <c r="B19" s="280"/>
+      <c r="C19" s="280"/>
+      <c r="D19" s="276"/>
       <c r="E19" s="72"/>
       <c r="F19" s="73" t="s">
         <v>474</v>
@@ -27429,23 +27477,23 @@
         <f>SUM(G7:G18)</f>
         <v>134.08999999999997</v>
       </c>
-      <c r="H19" s="279"/>
-      <c r="I19" s="278"/>
-      <c r="J19" s="278"/>
-      <c r="K19" s="278"/>
+      <c r="H19" s="281"/>
+      <c r="I19" s="280"/>
+      <c r="J19" s="280"/>
+      <c r="K19" s="280"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A20" s="272"/>
-      <c r="B20" s="272"/>
-      <c r="C20" s="272"/>
-      <c r="D20" s="272"/>
-      <c r="E20" s="272"/>
-      <c r="F20" s="272"/>
-      <c r="G20" s="272"/>
-      <c r="H20" s="272"/>
-      <c r="I20" s="272"/>
-      <c r="J20" s="272"/>
-      <c r="K20" s="272"/>
+      <c r="A20" s="275"/>
+      <c r="B20" s="275"/>
+      <c r="C20" s="275"/>
+      <c r="D20" s="275"/>
+      <c r="E20" s="275"/>
+      <c r="F20" s="275"/>
+      <c r="G20" s="275"/>
+      <c r="H20" s="275"/>
+      <c r="I20" s="275"/>
+      <c r="J20" s="275"/>
+      <c r="K20" s="275"/>
     </row>
     <row r="21" spans="1:11" ht="46.8" x14ac:dyDescent="0.35">
       <c r="A21" s="59" t="s">
@@ -27457,7 +27505,7 @@
       <c r="C21" s="59" t="s">
         <v>477</v>
       </c>
-      <c r="D21" s="277"/>
+      <c r="D21" s="279"/>
       <c r="E21" s="59" t="s">
         <v>478</v>
       </c>
@@ -27467,7 +27515,7 @@
       <c r="G21" s="59" t="s">
         <v>477</v>
       </c>
-      <c r="H21" s="277"/>
+      <c r="H21" s="279"/>
       <c r="I21" s="59" t="s">
         <v>478</v>
       </c>
@@ -27488,7 +27536,7 @@
       <c r="C22" s="61">
         <v>4.7300000000000004</v>
       </c>
-      <c r="D22" s="277"/>
+      <c r="D22" s="279"/>
       <c r="E22" s="81" t="s">
         <v>497</v>
       </c>
@@ -27498,7 +27546,7 @@
       <c r="G22" s="61">
         <v>4.58</v>
       </c>
-      <c r="H22" s="277"/>
+      <c r="H22" s="279"/>
       <c r="I22" s="81" t="s">
         <v>511</v>
       </c>
@@ -27519,7 +27567,7 @@
       <c r="C23" s="61">
         <v>4.62</v>
       </c>
-      <c r="D23" s="277"/>
+      <c r="D23" s="279"/>
       <c r="E23" s="81" t="s">
         <v>495</v>
       </c>
@@ -27529,7 +27577,7 @@
       <c r="G23" s="61">
         <v>4.62</v>
       </c>
-      <c r="H23" s="277"/>
+      <c r="H23" s="279"/>
       <c r="I23" s="81" t="s">
         <v>512</v>
       </c>
@@ -27549,7 +27597,7 @@
         <f>SUM(C22:C23)</f>
         <v>9.3500000000000014</v>
       </c>
-      <c r="D24" s="277"/>
+      <c r="D24" s="279"/>
       <c r="E24" s="82"/>
       <c r="F24" s="65" t="s">
         <v>474</v>
@@ -27558,7 +27606,7 @@
         <f>SUM(G22:G23)</f>
         <v>9.1999999999999993</v>
       </c>
-      <c r="H24" s="277"/>
+      <c r="H24" s="279"/>
       <c r="I24" s="82"/>
       <c r="J24" s="65" t="s">
         <v>474</v>
@@ -27570,6 +27618,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="A20:K20"/>
@@ -27580,11 +27633,6 @@
     <mergeCell ref="D6:D19"/>
     <mergeCell ref="H6:H19"/>
     <mergeCell ref="I16:K19"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -27611,36 +27659,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="276" t="s">
+      <c r="A1" s="282" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="259"/>
-      <c r="C1" s="259"/>
-      <c r="D1" s="259"/>
-      <c r="E1" s="259"/>
-      <c r="F1" s="259"/>
-      <c r="G1" s="259"/>
-      <c r="H1" s="259"/>
-      <c r="I1" s="259"/>
-      <c r="J1" s="259"/>
-      <c r="K1" s="259"/>
+      <c r="B1" s="262"/>
+      <c r="C1" s="262"/>
+      <c r="D1" s="262"/>
+      <c r="E1" s="262"/>
+      <c r="F1" s="262"/>
+      <c r="G1" s="262"/>
+      <c r="H1" s="262"/>
+      <c r="I1" s="262"/>
+      <c r="J1" s="262"/>
+      <c r="K1" s="262"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="214" t="s">
+      <c r="B2" s="217" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="214"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="214"/>
-      <c r="G2" s="207" t="s">
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="217"/>
+      <c r="G2" s="210" t="s">
         <v>391</v>
       </c>
-      <c r="H2" s="218"/>
-      <c r="I2" s="208"/>
+      <c r="H2" s="221"/>
+      <c r="I2" s="211"/>
       <c r="J2" s="16" t="s">
         <v>392</v>
       </c>
@@ -27652,18 +27700,18 @@
       <c r="A3" s="66">
         <v>1</v>
       </c>
-      <c r="B3" s="212" t="s">
+      <c r="B3" s="215" t="s">
         <v>438</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="212"/>
-      <c r="G3" s="209" t="s">
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="215"/>
+      <c r="G3" s="212" t="s">
         <v>534</v>
       </c>
-      <c r="H3" s="251"/>
-      <c r="I3" s="252"/>
+      <c r="H3" s="254"/>
+      <c r="I3" s="255"/>
       <c r="J3" s="66" t="s">
         <v>394</v>
       </c>
@@ -27673,17 +27721,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="274"/>
-      <c r="B4" s="274"/>
-      <c r="C4" s="274"/>
-      <c r="D4" s="274"/>
-      <c r="E4" s="274"/>
-      <c r="F4" s="274"/>
-      <c r="G4" s="274"/>
-      <c r="H4" s="274"/>
-      <c r="I4" s="274"/>
-      <c r="J4" s="274"/>
-      <c r="K4" s="274"/>
+      <c r="A4" s="277"/>
+      <c r="B4" s="277"/>
+      <c r="C4" s="277"/>
+      <c r="D4" s="277"/>
+      <c r="E4" s="277"/>
+      <c r="F4" s="277"/>
+      <c r="G4" s="277"/>
+      <c r="H4" s="277"/>
+      <c r="I4" s="277"/>
+      <c r="J4" s="277"/>
+      <c r="K4" s="277"/>
     </row>
     <row r="5" spans="1:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="67" t="s">
@@ -27695,7 +27743,7 @@
       <c r="C5" s="67" t="s">
         <v>477</v>
       </c>
-      <c r="D5" s="279"/>
+      <c r="D5" s="281"/>
       <c r="E5" s="67" t="s">
         <v>478</v>
       </c>
@@ -27705,10 +27753,10 @@
       <c r="G5" s="67" t="s">
         <v>477</v>
       </c>
-      <c r="H5" s="279"/>
-      <c r="I5" s="278"/>
-      <c r="J5" s="278"/>
-      <c r="K5" s="278"/>
+      <c r="H5" s="281"/>
+      <c r="I5" s="280"/>
+      <c r="J5" s="280"/>
+      <c r="K5" s="280"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="70" t="s">
@@ -27718,7 +27766,7 @@
       <c r="C6" s="77">
         <v>257.98</v>
       </c>
-      <c r="D6" s="279"/>
+      <c r="D6" s="281"/>
       <c r="E6" s="70" t="s">
         <v>514</v>
       </c>
@@ -27726,10 +27774,10 @@
       <c r="G6" s="77">
         <v>57.94</v>
       </c>
-      <c r="H6" s="279"/>
-      <c r="I6" s="278"/>
-      <c r="J6" s="278"/>
-      <c r="K6" s="278"/>
+      <c r="H6" s="281"/>
+      <c r="I6" s="280"/>
+      <c r="J6" s="280"/>
+      <c r="K6" s="280"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="68" t="s">
@@ -27739,7 +27787,7 @@
       <c r="C7" s="78">
         <v>98.23</v>
       </c>
-      <c r="D7" s="279"/>
+      <c r="D7" s="281"/>
       <c r="E7" s="68" t="s">
         <v>532</v>
       </c>
@@ -27747,10 +27795,10 @@
       <c r="G7" s="78">
         <v>14.96</v>
       </c>
-      <c r="H7" s="279"/>
-      <c r="I7" s="278"/>
-      <c r="J7" s="278"/>
-      <c r="K7" s="278"/>
+      <c r="H7" s="281"/>
+      <c r="I7" s="280"/>
+      <c r="J7" s="280"/>
+      <c r="K7" s="280"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="70" t="s">
@@ -27760,7 +27808,7 @@
       <c r="C8" s="77">
         <v>10.039999999999999</v>
       </c>
-      <c r="D8" s="279"/>
+      <c r="D8" s="281"/>
       <c r="E8" s="79"/>
       <c r="F8" s="80" t="s">
         <v>474</v>
@@ -27769,10 +27817,10 @@
         <f>SUM(G6:G7)</f>
         <v>72.900000000000006</v>
       </c>
-      <c r="H8" s="279"/>
-      <c r="I8" s="278"/>
-      <c r="J8" s="278"/>
-      <c r="K8" s="278"/>
+      <c r="H8" s="281"/>
+      <c r="I8" s="280"/>
+      <c r="J8" s="280"/>
+      <c r="K8" s="280"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="68" t="s">
@@ -27782,14 +27830,14 @@
       <c r="C9" s="78">
         <v>10.51</v>
       </c>
-      <c r="D9" s="279"/>
-      <c r="E9" s="278"/>
-      <c r="F9" s="278"/>
-      <c r="G9" s="278"/>
-      <c r="H9" s="278"/>
-      <c r="I9" s="278"/>
-      <c r="J9" s="278"/>
-      <c r="K9" s="278"/>
+      <c r="D9" s="281"/>
+      <c r="E9" s="280"/>
+      <c r="F9" s="280"/>
+      <c r="G9" s="280"/>
+      <c r="H9" s="280"/>
+      <c r="I9" s="280"/>
+      <c r="J9" s="280"/>
+      <c r="K9" s="280"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="70" t="s">
@@ -27799,14 +27847,14 @@
       <c r="C10" s="77">
         <v>10.06</v>
       </c>
-      <c r="D10" s="279"/>
-      <c r="E10" s="278"/>
-      <c r="F10" s="278"/>
-      <c r="G10" s="278"/>
-      <c r="H10" s="278"/>
-      <c r="I10" s="278"/>
-      <c r="J10" s="278"/>
-      <c r="K10" s="278"/>
+      <c r="D10" s="281"/>
+      <c r="E10" s="280"/>
+      <c r="F10" s="280"/>
+      <c r="G10" s="280"/>
+      <c r="H10" s="280"/>
+      <c r="I10" s="280"/>
+      <c r="J10" s="280"/>
+      <c r="K10" s="280"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="68" t="s">
@@ -27816,14 +27864,14 @@
       <c r="C11" s="78">
         <v>98.59</v>
       </c>
-      <c r="D11" s="279"/>
-      <c r="E11" s="278"/>
-      <c r="F11" s="278"/>
-      <c r="G11" s="278"/>
-      <c r="H11" s="278"/>
-      <c r="I11" s="278"/>
-      <c r="J11" s="278"/>
-      <c r="K11" s="278"/>
+      <c r="D11" s="281"/>
+      <c r="E11" s="280"/>
+      <c r="F11" s="280"/>
+      <c r="G11" s="280"/>
+      <c r="H11" s="280"/>
+      <c r="I11" s="280"/>
+      <c r="J11" s="280"/>
+      <c r="K11" s="280"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="70" t="s">
@@ -27833,14 +27881,14 @@
       <c r="C12" s="77">
         <v>7.25</v>
       </c>
-      <c r="D12" s="279"/>
-      <c r="E12" s="278"/>
-      <c r="F12" s="278"/>
-      <c r="G12" s="278"/>
-      <c r="H12" s="278"/>
-      <c r="I12" s="278"/>
-      <c r="J12" s="278"/>
-      <c r="K12" s="278"/>
+      <c r="D12" s="281"/>
+      <c r="E12" s="280"/>
+      <c r="F12" s="280"/>
+      <c r="G12" s="280"/>
+      <c r="H12" s="280"/>
+      <c r="I12" s="280"/>
+      <c r="J12" s="280"/>
+      <c r="K12" s="280"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="68" t="s">
@@ -27850,14 +27898,14 @@
       <c r="C13" s="78">
         <v>5.76</v>
       </c>
-      <c r="D13" s="279"/>
-      <c r="E13" s="278"/>
-      <c r="F13" s="278"/>
-      <c r="G13" s="278"/>
-      <c r="H13" s="278"/>
-      <c r="I13" s="278"/>
-      <c r="J13" s="278"/>
-      <c r="K13" s="278"/>
+      <c r="D13" s="281"/>
+      <c r="E13" s="280"/>
+      <c r="F13" s="280"/>
+      <c r="G13" s="280"/>
+      <c r="H13" s="280"/>
+      <c r="I13" s="280"/>
+      <c r="J13" s="280"/>
+      <c r="K13" s="280"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="70" t="s">
@@ -27867,14 +27915,14 @@
       <c r="C14" s="77">
         <v>20</v>
       </c>
-      <c r="D14" s="279"/>
-      <c r="E14" s="278"/>
-      <c r="F14" s="278"/>
-      <c r="G14" s="278"/>
-      <c r="H14" s="278"/>
-      <c r="I14" s="278"/>
-      <c r="J14" s="278"/>
-      <c r="K14" s="278"/>
+      <c r="D14" s="281"/>
+      <c r="E14" s="280"/>
+      <c r="F14" s="280"/>
+      <c r="G14" s="280"/>
+      <c r="H14" s="280"/>
+      <c r="I14" s="280"/>
+      <c r="J14" s="280"/>
+      <c r="K14" s="280"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="68" t="s">
@@ -27884,14 +27932,14 @@
       <c r="C15" s="78">
         <v>13.53</v>
       </c>
-      <c r="D15" s="279"/>
-      <c r="E15" s="278"/>
-      <c r="F15" s="278"/>
-      <c r="G15" s="278"/>
-      <c r="H15" s="278"/>
-      <c r="I15" s="278"/>
-      <c r="J15" s="278"/>
-      <c r="K15" s="278"/>
+      <c r="D15" s="281"/>
+      <c r="E15" s="280"/>
+      <c r="F15" s="280"/>
+      <c r="G15" s="280"/>
+      <c r="H15" s="280"/>
+      <c r="I15" s="280"/>
+      <c r="J15" s="280"/>
+      <c r="K15" s="280"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="70" t="s">
@@ -27901,14 +27949,14 @@
       <c r="C16" s="77">
         <v>13.3</v>
       </c>
-      <c r="D16" s="279"/>
-      <c r="E16" s="278"/>
-      <c r="F16" s="278"/>
-      <c r="G16" s="278"/>
-      <c r="H16" s="278"/>
-      <c r="I16" s="278"/>
-      <c r="J16" s="278"/>
-      <c r="K16" s="278"/>
+      <c r="D16" s="281"/>
+      <c r="E16" s="280"/>
+      <c r="F16" s="280"/>
+      <c r="G16" s="280"/>
+      <c r="H16" s="280"/>
+      <c r="I16" s="280"/>
+      <c r="J16" s="280"/>
+      <c r="K16" s="280"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="68" t="s">
@@ -27918,14 +27966,14 @@
       <c r="C17" s="78">
         <v>11.67</v>
       </c>
-      <c r="D17" s="279"/>
-      <c r="E17" s="278"/>
-      <c r="F17" s="278"/>
-      <c r="G17" s="278"/>
-      <c r="H17" s="278"/>
-      <c r="I17" s="278"/>
-      <c r="J17" s="278"/>
-      <c r="K17" s="278"/>
+      <c r="D17" s="281"/>
+      <c r="E17" s="280"/>
+      <c r="F17" s="280"/>
+      <c r="G17" s="280"/>
+      <c r="H17" s="280"/>
+      <c r="I17" s="280"/>
+      <c r="J17" s="280"/>
+      <c r="K17" s="280"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="70" t="s">
@@ -27935,14 +27983,14 @@
       <c r="C18" s="77">
         <v>9.7200000000000006</v>
       </c>
-      <c r="D18" s="279"/>
-      <c r="E18" s="278"/>
-      <c r="F18" s="278"/>
-      <c r="G18" s="278"/>
-      <c r="H18" s="278"/>
-      <c r="I18" s="278"/>
-      <c r="J18" s="278"/>
-      <c r="K18" s="278"/>
+      <c r="D18" s="281"/>
+      <c r="E18" s="280"/>
+      <c r="F18" s="280"/>
+      <c r="G18" s="280"/>
+      <c r="H18" s="280"/>
+      <c r="I18" s="280"/>
+      <c r="J18" s="280"/>
+      <c r="K18" s="280"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="68" t="s">
@@ -27952,14 +28000,14 @@
       <c r="C19" s="78">
         <v>3.38</v>
       </c>
-      <c r="D19" s="279"/>
-      <c r="E19" s="278"/>
-      <c r="F19" s="278"/>
-      <c r="G19" s="278"/>
-      <c r="H19" s="278"/>
-      <c r="I19" s="278"/>
-      <c r="J19" s="278"/>
-      <c r="K19" s="278"/>
+      <c r="D19" s="281"/>
+      <c r="E19" s="280"/>
+      <c r="F19" s="280"/>
+      <c r="G19" s="280"/>
+      <c r="H19" s="280"/>
+      <c r="I19" s="280"/>
+      <c r="J19" s="280"/>
+      <c r="K19" s="280"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="70" t="s">
@@ -27969,14 +28017,14 @@
       <c r="C20" s="77">
         <v>3.04</v>
       </c>
-      <c r="D20" s="279"/>
-      <c r="E20" s="278"/>
-      <c r="F20" s="278"/>
-      <c r="G20" s="278"/>
-      <c r="H20" s="278"/>
-      <c r="I20" s="278"/>
-      <c r="J20" s="278"/>
-      <c r="K20" s="278"/>
+      <c r="D20" s="281"/>
+      <c r="E20" s="280"/>
+      <c r="F20" s="280"/>
+      <c r="G20" s="280"/>
+      <c r="H20" s="280"/>
+      <c r="I20" s="280"/>
+      <c r="J20" s="280"/>
+      <c r="K20" s="280"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="68" t="s">
@@ -27986,14 +28034,14 @@
       <c r="C21" s="78">
         <v>2.85</v>
       </c>
-      <c r="D21" s="279"/>
-      <c r="E21" s="278"/>
-      <c r="F21" s="278"/>
-      <c r="G21" s="278"/>
-      <c r="H21" s="278"/>
-      <c r="I21" s="278"/>
-      <c r="J21" s="278"/>
-      <c r="K21" s="278"/>
+      <c r="D21" s="281"/>
+      <c r="E21" s="280"/>
+      <c r="F21" s="280"/>
+      <c r="G21" s="280"/>
+      <c r="H21" s="280"/>
+      <c r="I21" s="280"/>
+      <c r="J21" s="280"/>
+      <c r="K21" s="280"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="70" t="s">
@@ -28003,14 +28051,14 @@
       <c r="C22" s="77">
         <v>9.0399999999999991</v>
       </c>
-      <c r="D22" s="279"/>
-      <c r="E22" s="278"/>
-      <c r="F22" s="278"/>
-      <c r="G22" s="278"/>
-      <c r="H22" s="278"/>
-      <c r="I22" s="278"/>
-      <c r="J22" s="278"/>
-      <c r="K22" s="278"/>
+      <c r="D22" s="281"/>
+      <c r="E22" s="280"/>
+      <c r="F22" s="280"/>
+      <c r="G22" s="280"/>
+      <c r="H22" s="280"/>
+      <c r="I22" s="280"/>
+      <c r="J22" s="280"/>
+      <c r="K22" s="280"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="68" t="s">
@@ -28020,14 +28068,14 @@
       <c r="C23" s="78">
         <v>16.38</v>
       </c>
-      <c r="D23" s="279"/>
-      <c r="E23" s="278"/>
-      <c r="F23" s="278"/>
-      <c r="G23" s="278"/>
-      <c r="H23" s="278"/>
-      <c r="I23" s="278"/>
-      <c r="J23" s="278"/>
-      <c r="K23" s="278"/>
+      <c r="D23" s="281"/>
+      <c r="E23" s="280"/>
+      <c r="F23" s="280"/>
+      <c r="G23" s="280"/>
+      <c r="H23" s="280"/>
+      <c r="I23" s="280"/>
+      <c r="J23" s="280"/>
+      <c r="K23" s="280"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="70" t="s">
@@ -28037,14 +28085,14 @@
       <c r="C24" s="77">
         <v>4.63</v>
       </c>
-      <c r="D24" s="279"/>
-      <c r="E24" s="278"/>
-      <c r="F24" s="278"/>
-      <c r="G24" s="278"/>
-      <c r="H24" s="278"/>
-      <c r="I24" s="278"/>
-      <c r="J24" s="278"/>
-      <c r="K24" s="278"/>
+      <c r="D24" s="281"/>
+      <c r="E24" s="280"/>
+      <c r="F24" s="280"/>
+      <c r="G24" s="280"/>
+      <c r="H24" s="280"/>
+      <c r="I24" s="280"/>
+      <c r="J24" s="280"/>
+      <c r="K24" s="280"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="72"/>
@@ -28055,14 +28103,14 @@
         <f>SUM(C6:C24)</f>
         <v>605.95999999999992</v>
       </c>
-      <c r="D25" s="279"/>
-      <c r="E25" s="278"/>
-      <c r="F25" s="278"/>
-      <c r="G25" s="278"/>
-      <c r="H25" s="278"/>
-      <c r="I25" s="278"/>
-      <c r="J25" s="278"/>
-      <c r="K25" s="278"/>
+      <c r="D25" s="281"/>
+      <c r="E25" s="280"/>
+      <c r="F25" s="280"/>
+      <c r="G25" s="280"/>
+      <c r="H25" s="280"/>
+      <c r="I25" s="280"/>
+      <c r="J25" s="280"/>
+      <c r="K25" s="280"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -28100,25 +28148,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="188" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="186"/>
-      <c r="D2" s="187"/>
+      <c r="C2" s="189"/>
+      <c r="D2" s="190"/>
       <c r="E2" s="166" t="s">
         <v>391</v>
       </c>
@@ -28133,11 +28181,11 @@
       <c r="A3" s="164">
         <v>1</v>
       </c>
-      <c r="B3" s="197" t="s">
+      <c r="B3" s="200" t="s">
         <v>740</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="199"/>
+      <c r="C3" s="201"/>
+      <c r="D3" s="202"/>
       <c r="E3" s="165" t="s">
         <v>747</v>
       </c>
@@ -28156,11 +28204,11 @@
       <c r="B4" s="169" t="s">
         <v>393</v>
       </c>
-      <c r="C4" s="191"/>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
+      <c r="C4" s="194"/>
+      <c r="D4" s="195"/>
+      <c r="E4" s="195"/>
+      <c r="F4" s="195"/>
+      <c r="G4" s="195"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="170" t="s">
@@ -28169,11 +28217,11 @@
       <c r="B5" s="171">
         <v>8.39</v>
       </c>
-      <c r="C5" s="193"/>
-      <c r="D5" s="194"/>
-      <c r="E5" s="194"/>
-      <c r="F5" s="194"/>
-      <c r="G5" s="194"/>
+      <c r="C5" s="196"/>
+      <c r="D5" s="197"/>
+      <c r="E5" s="197"/>
+      <c r="F5" s="197"/>
+      <c r="G5" s="197"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="170" t="s">
@@ -28182,11 +28230,11 @@
       <c r="B6" s="171">
         <v>8.1999999999999993</v>
       </c>
-      <c r="C6" s="193"/>
-      <c r="D6" s="194"/>
-      <c r="E6" s="194"/>
-      <c r="F6" s="194"/>
-      <c r="G6" s="194"/>
+      <c r="C6" s="196"/>
+      <c r="D6" s="197"/>
+      <c r="E6" s="197"/>
+      <c r="F6" s="197"/>
+      <c r="G6" s="197"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="170" t="s">
@@ -28195,11 +28243,11 @@
       <c r="B7" s="171">
         <v>8.4</v>
       </c>
-      <c r="C7" s="193"/>
-      <c r="D7" s="194"/>
-      <c r="E7" s="194"/>
-      <c r="F7" s="194"/>
-      <c r="G7" s="194"/>
+      <c r="C7" s="196"/>
+      <c r="D7" s="197"/>
+      <c r="E7" s="197"/>
+      <c r="F7" s="197"/>
+      <c r="G7" s="197"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="170" t="s">
@@ -28208,11 +28256,11 @@
       <c r="B8" s="171">
         <v>12.1</v>
       </c>
-      <c r="C8" s="193"/>
-      <c r="D8" s="194"/>
-      <c r="E8" s="194"/>
-      <c r="F8" s="194"/>
-      <c r="G8" s="194"/>
+      <c r="C8" s="196"/>
+      <c r="D8" s="197"/>
+      <c r="E8" s="197"/>
+      <c r="F8" s="197"/>
+      <c r="G8" s="197"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="172" t="s">
@@ -28222,11 +28270,11 @@
         <f>SUM(B5:B8)</f>
         <v>37.090000000000003</v>
       </c>
-      <c r="C9" s="193"/>
-      <c r="D9" s="194"/>
-      <c r="E9" s="194"/>
-      <c r="F9" s="194"/>
-      <c r="G9" s="194"/>
+      <c r="C9" s="196"/>
+      <c r="D9" s="197"/>
+      <c r="E9" s="197"/>
+      <c r="F9" s="197"/>
+      <c r="G9" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -28262,25 +28310,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="188" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="186"/>
-      <c r="D2" s="187"/>
+      <c r="C2" s="189"/>
+      <c r="D2" s="190"/>
       <c r="E2" s="161" t="s">
         <v>391</v>
       </c>
@@ -28295,11 +28343,11 @@
       <c r="A3" s="159">
         <v>1</v>
       </c>
-      <c r="B3" s="197" t="s">
+      <c r="B3" s="200" t="s">
         <v>712</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="199"/>
+      <c r="C3" s="201"/>
+      <c r="D3" s="202"/>
       <c r="E3" s="160" t="s">
         <v>739</v>
       </c>
@@ -28318,11 +28366,11 @@
       <c r="B4" s="169" t="s">
         <v>393</v>
       </c>
-      <c r="C4" s="191"/>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
+      <c r="C4" s="194"/>
+      <c r="D4" s="195"/>
+      <c r="E4" s="195"/>
+      <c r="F4" s="195"/>
+      <c r="G4" s="195"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="170" t="s">
@@ -28331,11 +28379,11 @@
       <c r="B5" s="171">
         <v>10.25</v>
       </c>
-      <c r="C5" s="193"/>
-      <c r="D5" s="194"/>
-      <c r="E5" s="194"/>
-      <c r="F5" s="194"/>
-      <c r="G5" s="194"/>
+      <c r="C5" s="196"/>
+      <c r="D5" s="197"/>
+      <c r="E5" s="197"/>
+      <c r="F5" s="197"/>
+      <c r="G5" s="197"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="170" t="s">
@@ -28344,11 +28392,11 @@
       <c r="B6" s="171">
         <v>10.17</v>
       </c>
-      <c r="C6" s="193"/>
-      <c r="D6" s="194"/>
-      <c r="E6" s="194"/>
-      <c r="F6" s="194"/>
-      <c r="G6" s="194"/>
+      <c r="C6" s="196"/>
+      <c r="D6" s="197"/>
+      <c r="E6" s="197"/>
+      <c r="F6" s="197"/>
+      <c r="G6" s="197"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="172" t="s">
@@ -28358,11 +28406,11 @@
         <f>SUM(B5:B6)</f>
         <v>20.420000000000002</v>
       </c>
-      <c r="C7" s="193"/>
-      <c r="D7" s="194"/>
-      <c r="E7" s="194"/>
-      <c r="F7" s="194"/>
-      <c r="G7" s="194"/>
+      <c r="C7" s="196"/>
+      <c r="D7" s="197"/>
+      <c r="E7" s="197"/>
+      <c r="F7" s="197"/>
+      <c r="G7" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -28398,23 +28446,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="202" t="s">
+      <c r="B2" s="205" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="203"/>
+      <c r="C2" s="206"/>
       <c r="D2" s="161" t="s">
         <v>391</v>
       </c>
@@ -28429,10 +28477,10 @@
       <c r="A3" s="159">
         <v>1</v>
       </c>
-      <c r="B3" s="204" t="s">
+      <c r="B3" s="207" t="s">
         <v>737</v>
       </c>
-      <c r="C3" s="205"/>
+      <c r="C3" s="208"/>
       <c r="D3" s="160" t="s">
         <v>738</v>
       </c>
@@ -28445,12 +28493,12 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="195"/>
-      <c r="B4" s="195"/>
-      <c r="C4" s="195"/>
-      <c r="D4" s="195"/>
-      <c r="E4" s="195"/>
-      <c r="F4" s="195"/>
+      <c r="A4" s="198"/>
+      <c r="B4" s="198"/>
+      <c r="C4" s="198"/>
+      <c r="D4" s="198"/>
+      <c r="E4" s="198"/>
+      <c r="F4" s="198"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="168" t="s">
@@ -28459,10 +28507,10 @@
       <c r="B5" s="169" t="s">
         <v>393</v>
       </c>
-      <c r="C5" s="200"/>
-      <c r="D5" s="201"/>
-      <c r="E5" s="201"/>
-      <c r="F5" s="201"/>
+      <c r="C5" s="203"/>
+      <c r="D5" s="204"/>
+      <c r="E5" s="204"/>
+      <c r="F5" s="204"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="170" t="s">
@@ -28471,10 +28519,10 @@
       <c r="B6" s="171">
         <v>371.2</v>
       </c>
-      <c r="C6" s="200"/>
-      <c r="D6" s="201"/>
-      <c r="E6" s="201"/>
-      <c r="F6" s="201"/>
+      <c r="C6" s="203"/>
+      <c r="D6" s="204"/>
+      <c r="E6" s="204"/>
+      <c r="F6" s="204"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="170" t="s">
@@ -28483,10 +28531,10 @@
       <c r="B7" s="171">
         <v>590.25</v>
       </c>
-      <c r="C7" s="200"/>
-      <c r="D7" s="201"/>
-      <c r="E7" s="201"/>
-      <c r="F7" s="201"/>
+      <c r="C7" s="203"/>
+      <c r="D7" s="204"/>
+      <c r="E7" s="204"/>
+      <c r="F7" s="204"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="170" t="s">
@@ -28495,10 +28543,10 @@
       <c r="B8" s="171">
         <v>591.67999999999995</v>
       </c>
-      <c r="C8" s="200"/>
-      <c r="D8" s="201"/>
-      <c r="E8" s="201"/>
-      <c r="F8" s="201"/>
+      <c r="C8" s="203"/>
+      <c r="D8" s="204"/>
+      <c r="E8" s="204"/>
+      <c r="F8" s="204"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="172" t="s">
@@ -28508,10 +28556,10 @@
         <f>SUM(B6:B8)</f>
         <v>1553.13</v>
       </c>
-      <c r="C9" s="200"/>
-      <c r="D9" s="201"/>
-      <c r="E9" s="201"/>
-      <c r="F9" s="201"/>
+      <c r="C9" s="203"/>
+      <c r="D9" s="204"/>
+      <c r="E9" s="204"/>
+      <c r="F9" s="204"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -28546,34 +28594,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="187" t="s">
         <v>692</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
+      <c r="J1" s="187"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="188" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="186"/>
-      <c r="D2" s="186"/>
-      <c r="E2" s="186"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="207" t="s">
+      <c r="C2" s="189"/>
+      <c r="D2" s="189"/>
+      <c r="E2" s="189"/>
+      <c r="F2" s="190"/>
+      <c r="G2" s="210" t="s">
         <v>391</v>
       </c>
-      <c r="H2" s="208"/>
+      <c r="H2" s="211"/>
       <c r="I2" s="161" t="s">
         <v>392</v>
       </c>
@@ -28585,17 +28633,17 @@
       <c r="A3" s="159">
         <v>1</v>
       </c>
-      <c r="B3" s="197" t="s">
+      <c r="B3" s="200" t="s">
         <v>597</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="199"/>
-      <c r="G3" s="209" t="s">
+      <c r="C3" s="201"/>
+      <c r="D3" s="201"/>
+      <c r="E3" s="201"/>
+      <c r="F3" s="202"/>
+      <c r="G3" s="212" t="s">
         <v>741</v>
       </c>
-      <c r="H3" s="210"/>
+      <c r="H3" s="213"/>
       <c r="I3" s="159" t="s">
         <v>394</v>
       </c>
@@ -28605,16 +28653,16 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="195"/>
-      <c r="B4" s="195"/>
-      <c r="C4" s="195"/>
-      <c r="D4" s="195"/>
-      <c r="E4" s="195"/>
-      <c r="F4" s="195"/>
-      <c r="G4" s="195"/>
-      <c r="H4" s="195"/>
-      <c r="I4" s="195"/>
-      <c r="J4" s="195"/>
+      <c r="A4" s="198"/>
+      <c r="B4" s="198"/>
+      <c r="C4" s="198"/>
+      <c r="D4" s="198"/>
+      <c r="E4" s="198"/>
+      <c r="F4" s="198"/>
+      <c r="G4" s="198"/>
+      <c r="H4" s="198"/>
+      <c r="I4" s="198"/>
+      <c r="J4" s="198"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="168" t="s">
@@ -28623,18 +28671,18 @@
       <c r="B5" s="169" t="s">
         <v>393</v>
       </c>
-      <c r="C5" s="211"/>
+      <c r="C5" s="214"/>
       <c r="D5" s="168" t="s">
         <v>593</v>
       </c>
       <c r="E5" s="169" t="s">
         <v>393</v>
       </c>
-      <c r="F5" s="193"/>
-      <c r="G5" s="194"/>
-      <c r="H5" s="194"/>
-      <c r="I5" s="194"/>
-      <c r="J5" s="194"/>
+      <c r="F5" s="196"/>
+      <c r="G5" s="197"/>
+      <c r="H5" s="197"/>
+      <c r="I5" s="197"/>
+      <c r="J5" s="197"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="170" t="s">
@@ -28643,18 +28691,18 @@
       <c r="B6" s="171">
         <v>23.5</v>
       </c>
-      <c r="C6" s="211"/>
+      <c r="C6" s="214"/>
       <c r="D6" s="170" t="s">
         <v>467</v>
       </c>
       <c r="E6" s="171">
         <v>23.4</v>
       </c>
-      <c r="F6" s="193"/>
-      <c r="G6" s="194"/>
-      <c r="H6" s="194"/>
-      <c r="I6" s="194"/>
-      <c r="J6" s="194"/>
+      <c r="F6" s="196"/>
+      <c r="G6" s="197"/>
+      <c r="H6" s="197"/>
+      <c r="I6" s="197"/>
+      <c r="J6" s="197"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="170" t="s">
@@ -28663,18 +28711,18 @@
       <c r="B7" s="171">
         <v>23.1</v>
       </c>
-      <c r="C7" s="211"/>
+      <c r="C7" s="214"/>
       <c r="D7" s="170" t="s">
         <v>469</v>
       </c>
       <c r="E7" s="171">
         <v>23.2</v>
       </c>
-      <c r="F7" s="193"/>
-      <c r="G7" s="194"/>
-      <c r="H7" s="194"/>
-      <c r="I7" s="194"/>
-      <c r="J7" s="194"/>
+      <c r="F7" s="196"/>
+      <c r="G7" s="197"/>
+      <c r="H7" s="197"/>
+      <c r="I7" s="197"/>
+      <c r="J7" s="197"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="170" t="s">
@@ -28683,7 +28731,7 @@
       <c r="B8" s="171">
         <v>72.5</v>
       </c>
-      <c r="C8" s="211"/>
+      <c r="C8" s="214"/>
       <c r="D8" s="172" t="s">
         <v>474</v>
       </c>
@@ -28691,11 +28739,11 @@
         <f>SUM(E6:E7)</f>
         <v>46.599999999999994</v>
       </c>
-      <c r="F8" s="193"/>
-      <c r="G8" s="194"/>
-      <c r="H8" s="194"/>
-      <c r="I8" s="194"/>
-      <c r="J8" s="194"/>
+      <c r="F8" s="196"/>
+      <c r="G8" s="197"/>
+      <c r="H8" s="197"/>
+      <c r="I8" s="197"/>
+      <c r="J8" s="197"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="170" t="s">
@@ -28704,14 +28752,14 @@
       <c r="B9" s="171">
         <v>41.9</v>
       </c>
-      <c r="C9" s="193"/>
-      <c r="D9" s="206"/>
-      <c r="E9" s="206"/>
-      <c r="F9" s="194"/>
-      <c r="G9" s="194"/>
-      <c r="H9" s="194"/>
-      <c r="I9" s="194"/>
-      <c r="J9" s="194"/>
+      <c r="C9" s="196"/>
+      <c r="D9" s="209"/>
+      <c r="E9" s="209"/>
+      <c r="F9" s="197"/>
+      <c r="G9" s="197"/>
+      <c r="H9" s="197"/>
+      <c r="I9" s="197"/>
+      <c r="J9" s="197"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="170" t="s">
@@ -28720,14 +28768,14 @@
       <c r="B10" s="171">
         <v>57.2</v>
       </c>
-      <c r="C10" s="193"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="206"/>
-      <c r="F10" s="194"/>
-      <c r="G10" s="194"/>
-      <c r="H10" s="194"/>
-      <c r="I10" s="194"/>
-      <c r="J10" s="194"/>
+      <c r="C10" s="196"/>
+      <c r="D10" s="209"/>
+      <c r="E10" s="209"/>
+      <c r="F10" s="197"/>
+      <c r="G10" s="197"/>
+      <c r="H10" s="197"/>
+      <c r="I10" s="197"/>
+      <c r="J10" s="197"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="172" t="s">
@@ -28737,14 +28785,14 @@
         <f>SUM(B6:B10)</f>
         <v>218.2</v>
       </c>
-      <c r="C11" s="193"/>
-      <c r="D11" s="206"/>
-      <c r="E11" s="206"/>
-      <c r="F11" s="194"/>
-      <c r="G11" s="194"/>
-      <c r="H11" s="194"/>
-      <c r="I11" s="194"/>
-      <c r="J11" s="194"/>
+      <c r="C11" s="196"/>
+      <c r="D11" s="209"/>
+      <c r="E11" s="209"/>
+      <c r="F11" s="197"/>
+      <c r="G11" s="197"/>
+      <c r="H11" s="197"/>
+      <c r="I11" s="197"/>
+      <c r="J11" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="9">
